--- a/data_u1/LSR3_H_2025-08-15.xlsx
+++ b/data_u1/LSR3_H_2025-08-15.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sksiafis/Documents/GitHub/LSR3_taar1_H/data_u1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{050CB7A7-1598-3043-9DD0-BDE25D49FAD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47F303FA-2E16-574B-9674-72BEB83A960A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22300" yWindow="-21100" windowWidth="38400" windowHeight="19840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -931,16 +931,16 @@
     <t>schizophrenia_n</t>
   </si>
   <si>
+    <t>Schizophrenia spectrum (acute episode, adolescents)</t>
+  </si>
+  <si>
+    <t>NCT03669640 (2018)</t>
+  </si>
+  <si>
     <t>NCT03669640 (2018, addon)</t>
   </si>
   <si>
-    <t>NCT03669640 (2018, monotherapy)</t>
-  </si>
-  <si>
-    <t>NCT04072354 (2019, adolescents)</t>
-  </si>
-  <si>
-    <t>Schizophrenia spectrum (acute episode, adolescents)</t>
+    <t>NCT04072354 (2019, adolescent)</t>
   </si>
 </sst>
 </file>
@@ -3217,7 +3217,7 @@
         <v>-5.7</v>
       </c>
       <c r="AW6" s="19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX6" s="8" t="s">
         <v>129</v>
@@ -3244,7 +3244,7 @@
         <v>-5.5</v>
       </c>
       <c r="BF6" s="19">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BG6" s="8" t="s">
         <v>129</v>
@@ -3468,7 +3468,7 @@
         <v>-7</v>
       </c>
       <c r="AW7" s="19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX7" s="8" t="s">
         <v>129</v>
@@ -3495,7 +3495,7 @@
         <v>-7.3</v>
       </c>
       <c r="BF7" s="19">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BG7" s="8" t="s">
         <v>129</v>
@@ -3719,7 +3719,7 @@
         <v>-6.4</v>
       </c>
       <c r="AW8" s="19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX8" s="8" t="s">
         <v>129</v>
@@ -3746,7 +3746,7 @@
         <v>-6.2</v>
       </c>
       <c r="BF8" s="19">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BG8" s="8" t="s">
         <v>129</v>
@@ -3838,7 +3838,7 @@
         <v>282</v>
       </c>
       <c r="B9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C9" s="16">
         <v>2023</v>
@@ -3857,7 +3857,7 @@
         <v>177</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="J9" s="10" t="s">
         <v>146</v>
@@ -4011,7 +4011,7 @@
         <v>283</v>
       </c>
       <c r="B10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C10" s="16">
         <v>2023</v>
@@ -4030,7 +4030,7 @@
         <v>180</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="J10" s="10" t="s">
         <v>146</v>
@@ -4184,7 +4184,7 @@
         <v>284</v>
       </c>
       <c r="B11" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C11" s="16">
         <v>2023</v>
@@ -4203,7 +4203,7 @@
         <v>127</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="J11" s="10" t="s">
         <v>146</v>
@@ -4489,7 +4489,7 @@
         <v>-5.2</v>
       </c>
       <c r="AW12" s="19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX12" s="8" t="s">
         <v>129</v>
@@ -4516,7 +4516,7 @@
         <v>-6</v>
       </c>
       <c r="BF12" s="19">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BG12" s="8" t="s">
         <v>129</v>
@@ -4543,6 +4543,12 @@
         <v>18</v>
       </c>
       <c r="DK12" s="8">
+        <v>155</v>
+      </c>
+      <c r="DL12" s="8">
+        <v>6</v>
+      </c>
+      <c r="DM12" s="8">
         <v>155</v>
       </c>
       <c r="DT12" s="8">
@@ -4716,7 +4722,7 @@
         <v>-5.5</v>
       </c>
       <c r="AW13" s="19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX13" s="8" t="s">
         <v>129</v>
@@ -4743,7 +4749,7 @@
         <v>-6.4</v>
       </c>
       <c r="BF13" s="19">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BG13" s="8" t="s">
         <v>129</v>
@@ -4770,6 +4776,12 @@
         <v>17</v>
       </c>
       <c r="DK13" s="8">
+        <v>154</v>
+      </c>
+      <c r="DL13" s="8">
+        <v>5</v>
+      </c>
+      <c r="DM13" s="8">
         <v>154</v>
       </c>
       <c r="DT13" s="8">
@@ -4943,7 +4955,7 @@
         <v>-4.5999999999999996</v>
       </c>
       <c r="AW14" s="19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX14" s="8" t="s">
         <v>129</v>
@@ -4970,7 +4982,7 @@
         <v>-4.5</v>
       </c>
       <c r="BF14" s="19">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BG14" s="8" t="s">
         <v>129</v>
@@ -4997,6 +5009,12 @@
         <v>14</v>
       </c>
       <c r="DK14" s="8">
+        <v>155</v>
+      </c>
+      <c r="DL14" s="8">
+        <v>2</v>
+      </c>
+      <c r="DM14" s="8">
         <v>155</v>
       </c>
       <c r="DT14" s="8">
@@ -8184,7 +8202,7 @@
         <v>250</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C34" s="16">
         <v>2024</v>
@@ -8423,7 +8441,7 @@
         <v>251</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C35" s="16">
         <v>2024</v>
@@ -8662,7 +8680,7 @@
         <v>252</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C36" s="16">
         <v>2024</v>
@@ -8901,7 +8919,7 @@
         <v>248</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C37" s="16">
         <v>2024</v>

--- a/data_u1/LSR3_H_2025-08-15.xlsx
+++ b/data_u1/LSR3_H_2025-08-15.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sksiafis/Documents/GitHub/LSR3_taar1_H/data_u1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47F303FA-2E16-574B-9674-72BEB83A960A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5C3E97F-3700-B843-AD78-6C7E99EEDC33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,12 +34,22 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>tc={ABE74129-5B9A-A84D-A4C6-C683DD24160B}</author>
     <author>tc={F49B5693-3906-8543-B427-4EC42AF420FE}</author>
     <author>tc={5B87CDAA-9B3C-2740-B825-05967E84E211}</author>
+    <author>tc={0971AB22-BB3D-6E44-92EF-19F7F720FCF8}</author>
     <author>tc={63125C18-1CF7-5340-80AF-3F079B6ADA33}</author>
   </authors>
   <commentList>
-    <comment ref="BA4" authorId="0" shapeId="0" xr:uid="{F49B5693-3906-8543-B427-4EC42AF420FE}">
+    <comment ref="EF3" authorId="0" shapeId="0" xr:uid="{ABE74129-5B9A-A84D-A4C6-C683DD24160B}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    hallucinations</t>
+      </text>
+    </comment>
+    <comment ref="BA4" authorId="1" shapeId="0" xr:uid="{F49B5693-3906-8543-B427-4EC42AF420FE}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -47,7 +57,7 @@
     Changed from first version because BNSS total has been recently been show that has a better validity compared to PANSS negative (Weigel et al)</t>
       </text>
     </comment>
-    <comment ref="DD6" authorId="1" shapeId="0" xr:uid="{5B87CDAA-9B3C-2740-B825-05967E84E211}">
+    <comment ref="DD6" authorId="2" shapeId="0" xr:uid="{5B87CDAA-9B3C-2740-B825-05967E84E211}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -55,7 +65,15 @@
     dry mouth, constipation, dry eye</t>
       </text>
     </comment>
-    <comment ref="Q32" authorId="2" shapeId="0" xr:uid="{63125C18-1CF7-5340-80AF-3F079B6ADA33}">
+    <comment ref="S30" authorId="3" shapeId="0" xr:uid="{0971AB22-BB3D-6E44-92EF-19F7F720FCF8}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    SAE schizophrenia / not dropout due to inefficacy</t>
+      </text>
+    </comment>
+    <comment ref="Q32" authorId="4" shapeId="0" xr:uid="{63125C18-1CF7-5340-80AF-3F079B6ADA33}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -925,12 +943,6 @@
     <t>placebo (adolescents)</t>
   </si>
   <si>
-    <t>schizophrenia_e</t>
-  </si>
-  <si>
-    <t>schizophrenia_n</t>
-  </si>
-  <si>
     <t>Schizophrenia spectrum (acute episode, adolescents)</t>
   </si>
   <si>
@@ -941,6 +953,12 @@
   </si>
   <si>
     <t>NCT04072354 (2019, adolescent)</t>
+  </si>
+  <si>
+    <t>psychosis_e</t>
+  </si>
+  <si>
+    <t>psychosis_n</t>
   </si>
 </sst>
 </file>
@@ -1404,11 +1422,17 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="EF3" dT="2025-08-16T12:39:23.35" personId="{9C02175C-AB95-C54D-8A67-708063150B15}" id="{ABE74129-5B9A-A84D-A4C6-C683DD24160B}">
+    <text>hallucinations</text>
+  </threadedComment>
   <threadedComment ref="BA4" dT="2025-01-16T13:52:36.05" personId="{9C02175C-AB95-C54D-8A67-708063150B15}" id="{F49B5693-3906-8543-B427-4EC42AF420FE}">
     <text>Changed from first version because BNSS total has been recently been show that has a better validity compared to PANSS negative (Weigel et al)</text>
   </threadedComment>
   <threadedComment ref="DD6" dT="2025-08-15T21:16:55.84" personId="{9C02175C-AB95-C54D-8A67-708063150B15}" id="{5B87CDAA-9B3C-2740-B825-05967E84E211}">
     <text>dry mouth, constipation, dry eye</text>
+  </threadedComment>
+  <threadedComment ref="S30" dT="2025-08-16T13:49:55.55" personId="{9C02175C-AB95-C54D-8A67-708063150B15}" id="{0971AB22-BB3D-6E44-92EF-19F7F720FCF8}">
+    <text>SAE schizophrenia / not dropout due to inefficacy</text>
   </threadedComment>
   <threadedComment ref="Q32" dT="2025-01-16T13:52:04.57" personId="{9C02175C-AB95-C54D-8A67-708063150B15}" id="{63125C18-1CF7-5340-80AF-3F079B6ADA33}">
     <text>Imputed from panss total</text>
@@ -1946,10 +1970,10 @@
         <v>122</v>
       </c>
       <c r="EF1" s="1" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="EG1" s="1" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="EH1" s="1" t="s">
         <v>123</v>
@@ -2170,6 +2194,15 @@
       <c r="DX2" s="8">
         <v>2</v>
       </c>
+      <c r="DY2" s="8">
+        <v>25</v>
+      </c>
+      <c r="EF2" s="8">
+        <v>6</v>
+      </c>
+      <c r="EG2" s="8">
+        <v>25</v>
+      </c>
       <c r="EH2" t="s">
         <v>137</v>
       </c>
@@ -2400,6 +2433,12 @@
       <c r="DY3">
         <v>14</v>
       </c>
+      <c r="EF3" s="8">
+        <v>2</v>
+      </c>
+      <c r="EG3" s="8">
+        <v>14</v>
+      </c>
       <c r="EH3" t="s">
         <v>161</v>
       </c>
@@ -3838,7 +3877,7 @@
         <v>282</v>
       </c>
       <c r="B9" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C9" s="16">
         <v>2023</v>
@@ -3857,7 +3896,7 @@
         <v>177</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="J9" s="10" t="s">
         <v>146</v>
@@ -4011,7 +4050,7 @@
         <v>283</v>
       </c>
       <c r="B10" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C10" s="16">
         <v>2023</v>
@@ -4030,7 +4069,7 @@
         <v>180</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="J10" s="10" t="s">
         <v>146</v>
@@ -4184,7 +4223,7 @@
         <v>284</v>
       </c>
       <c r="B11" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C11" s="16">
         <v>2023</v>
@@ -4203,7 +4242,7 @@
         <v>127</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="J11" s="10" t="s">
         <v>146</v>
@@ -6687,7 +6726,7 @@
       <c r="C24" s="16">
         <v>2021</v>
       </c>
-      <c r="D24" s="16" t="s">
+      <c r="D24" s="17" t="s">
         <v>268</v>
       </c>
       <c r="E24">
@@ -7276,7 +7315,7 @@
         <v>276</v>
       </c>
       <c r="S30" s="8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T30" s="10">
         <v>201</v>
@@ -7521,7 +7560,7 @@
         <v>276</v>
       </c>
       <c r="S31" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T31" s="10">
         <v>102</v>
@@ -7724,7 +7763,7 @@
         <v>253</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C32" s="16">
         <v>2024</v>
@@ -7963,7 +8002,7 @@
         <v>246</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C33" s="16">
         <v>2024</v>
@@ -8202,7 +8241,7 @@
         <v>250</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C34" s="16">
         <v>2024</v>
@@ -8441,7 +8480,7 @@
         <v>251</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C35" s="16">
         <v>2024</v>
@@ -8680,7 +8719,7 @@
         <v>252</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C36" s="16">
         <v>2024</v>
@@ -8919,7 +8958,7 @@
         <v>248</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C37" s="16">
         <v>2024</v>
@@ -9364,8 +9403,9 @@
     <hyperlink ref="D23" r:id="rId8" xr:uid="{3FCDDBD9-56BC-C749-BB76-D0B15C422E37}"/>
     <hyperlink ref="D38" r:id="rId9" xr:uid="{A31C1C9D-E44E-7E45-B744-61D3C3B6A050}"/>
     <hyperlink ref="D39" r:id="rId10" xr:uid="{75DC2334-CE5B-D44A-BEF6-C0CB14654AA3}"/>
+    <hyperlink ref="D24" r:id="rId11" xr:uid="{DE5B0F9C-F318-6F43-AE00-59FC43E75394}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId11"/>
+  <legacyDrawing r:id="rId12"/>
 </worksheet>
 </file>
--- a/data_u1/LSR3_H_2025-08-15.xlsx
+++ b/data_u1/LSR3_H_2025-08-15.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sksiafis/Documents/GitHub/LSR3_taar1_H/data_u1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5C3E97F-3700-B843-AD78-6C7E99EEDC33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBBD1E01-6C57-854E-8F18-08FB54809119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16680" yWindow="-21100" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,8 +37,10 @@
     <author>tc={ABE74129-5B9A-A84D-A4C6-C683DD24160B}</author>
     <author>tc={F49B5693-3906-8543-B427-4EC42AF420FE}</author>
     <author>tc={5B87CDAA-9B3C-2740-B825-05967E84E211}</author>
-    <author>tc={0971AB22-BB3D-6E44-92EF-19F7F720FCF8}</author>
+    <author>tc={9C13DC03-74BA-9F44-B4A7-E9BF90B96B62}</author>
+    <author>tc={C74A172F-8133-EE4C-A9EF-A5408B33064F}</author>
     <author>tc={63125C18-1CF7-5340-80AF-3F079B6ADA33}</author>
+    <author>tc={E49234FE-6618-9C41-BBEF-153C57A2EE59}</author>
   </authors>
   <commentList>
     <comment ref="EF3" authorId="0" shapeId="0" xr:uid="{ABE74129-5B9A-A84D-A4C6-C683DD24160B}">
@@ -65,15 +67,23 @@
     dry mouth, constipation, dry eye</t>
       </text>
     </comment>
-    <comment ref="S30" authorId="3" shapeId="0" xr:uid="{0971AB22-BB3D-6E44-92EF-19F7F720FCF8}">
+    <comment ref="S30" authorId="3" shapeId="0" xr:uid="{9C13DC03-74BA-9F44-B4A7-E9BF90B96B62}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    SAE schizophrenia / not dropout due to inefficacy</t>
+    imputed as PANSS+12</t>
       </text>
     </comment>
-    <comment ref="Q32" authorId="4" shapeId="0" xr:uid="{63125C18-1CF7-5340-80AF-3F079B6ADA33}">
+    <comment ref="EF30" authorId="4" shapeId="0" xr:uid="{C74A172F-8133-EE4C-A9EF-A5408B33064F}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    poster: both SAE and non-SAE</t>
+      </text>
+    </comment>
+    <comment ref="Q32" authorId="5" shapeId="0" xr:uid="{63125C18-1CF7-5340-80AF-3F079B6ADA33}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -81,12 +91,20 @@
     Imputed from panss total</t>
       </text>
     </comment>
+    <comment ref="S32" authorId="6" shapeId="0" xr:uid="{E49234FE-6618-9C41-BBEF-153C57A2EE59}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    same as imputed from PANSS total </t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1209" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1201" uniqueCount="288">
   <si>
     <t>arm_name</t>
   </si>
@@ -532,9 +550,6 @@
     <t>39</t>
   </si>
   <si>
-    <t>70.7</t>
-  </si>
-  <si>
     <t>6</t>
   </si>
   <si>
@@ -592,9 +607,6 @@
     <t>245</t>
   </si>
   <si>
-    <t>30.3</t>
-  </si>
-  <si>
     <t>120</t>
   </si>
   <si>
@@ -616,349 +628,346 @@
     <t>ulotaront 50mg/d (adults)</t>
   </si>
   <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>435</t>
+  </si>
+  <si>
+    <t>ulotaront 75mg/d (adults)</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>placebo (adults)</t>
+  </si>
+  <si>
+    <t>ulotaront 75mg/d</t>
+  </si>
+  <si>
+    <t>NCT04092686 (2019)</t>
+  </si>
+  <si>
+    <t>464</t>
+  </si>
+  <si>
+    <t>ulotaront 100mg/d</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>placebo (P2; 4 weeks)</t>
+  </si>
+  <si>
+    <t>NCT04512066 (2020)</t>
+  </si>
+  <si>
+    <t>287</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>endpoint</t>
+  </si>
+  <si>
+    <t>PANSS anxiety/depression</t>
+  </si>
+  <si>
+    <t>ralmitaront 45mg (P2; 4 weeks)</t>
+  </si>
+  <si>
+    <t>ralmitaront</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>ralmitaront 150mg (P2; 4 weeks)</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>risperidone (P2; 4 weeks)</t>
+  </si>
+  <si>
+    <t>risperidone</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>D2 antipsychotic</t>
+  </si>
+  <si>
+    <t>placebo (LS and HS)</t>
+  </si>
+  <si>
+    <t>Perini (2023)</t>
+  </si>
+  <si>
+    <t>Healthy volunteers</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>29.2</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>1 day-2 weeks</t>
+  </si>
+  <si>
+    <t>ulotaront (LS and HS)</t>
+  </si>
+  <si>
+    <t>27.4</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>amisulpride (LS and HS)</t>
+  </si>
+  <si>
+    <t>amisulpride</t>
+  </si>
+  <si>
+    <t>400</t>
+  </si>
+  <si>
+    <t>27.6</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>Tsukada (2023)</t>
+  </si>
+  <si>
+    <t>crossover-RCT</t>
+  </si>
+  <si>
+    <t>stable</t>
+  </si>
+  <si>
+    <t>48.3</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>ulotaront 150mg</t>
+  </si>
+  <si>
+    <t>ulotaront 10mg</t>
+  </si>
+  <si>
+    <t>Hopkins (2021)</t>
+  </si>
+  <si>
+    <t>25.1</t>
+  </si>
+  <si>
+    <t>ulotaront 50mg</t>
+  </si>
+  <si>
+    <t>Szabo (2023)</t>
+  </si>
+  <si>
+    <t>Narcolepsy-cataplexy</t>
+  </si>
+  <si>
+    <t>32.9</t>
+  </si>
+  <si>
+    <t>ulotaront 25mg</t>
+  </si>
+  <si>
+    <t>anticholinergic_symptom_e</t>
+  </si>
+  <si>
+    <t>anticholinergic_symptom_n</t>
+  </si>
+  <si>
+    <t>NCT04115319 (2019)</t>
+  </si>
+  <si>
+    <t>quetiapine XR</t>
+  </si>
+  <si>
+    <t>50-100</t>
+  </si>
+  <si>
+    <t>quetiapine</t>
+  </si>
+  <si>
+    <t>400-800</t>
+  </si>
+  <si>
+    <t>placebo (monotherapy)</t>
+  </si>
+  <si>
+    <t>negative symptoms</t>
+  </si>
+  <si>
+    <t>placebo (add-on)</t>
+  </si>
+  <si>
+    <t>BNSS total</t>
+  </si>
+  <si>
+    <t>ralmitaront 45mg (add-on)</t>
+  </si>
+  <si>
+    <t>ralmitaront 150mg (add-on)</t>
+  </si>
+  <si>
+    <t>ralmitaront 350mg (add-on)</t>
+  </si>
+  <si>
+    <t>ralmitaront 150mg  (monotherapy)</t>
+  </si>
+  <si>
+    <t>TAAR1 agonist (add-on)</t>
+  </si>
+  <si>
+    <t>antipsychotic (aripiprazole, olanzapine, quetiapine, risperidone)</t>
+  </si>
+  <si>
+    <t>NCT05402111 (2022)</t>
+  </si>
+  <si>
+    <t>Schizophrenia spectrum (negative symptoms)</t>
+  </si>
+  <si>
+    <t>Schizophrenia spectrum (clinically stable)</t>
+  </si>
+  <si>
+    <t>Schizophrenia spectrum (acute episode)</t>
+  </si>
+  <si>
+    <t>&gt;13 weeks</t>
+  </si>
+  <si>
+    <t>ralmitaront (addon)</t>
+  </si>
+  <si>
+    <t>placebo (addon)</t>
+  </si>
+  <si>
+    <t>Schizophrenia spectrum (clinically stable, MetS)</t>
+  </si>
+  <si>
+    <t>study_year</t>
+  </si>
+  <si>
+    <t>study_doi</t>
+  </si>
+  <si>
+    <t>10.1212/CPJ.0000000000200175</t>
+  </si>
+  <si>
+    <t>https://dx.doi.org/10.1016/j.sleep.2023.04.019</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1038/s41398-021-01331-9</t>
+  </si>
+  <si>
+    <t>overall_baseline_n</t>
+  </si>
+  <si>
+    <t>depression_baseline_n</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1056/nejmoa1911772</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1038/s41537-023-00385-6</t>
+  </si>
+  <si>
+    <t>https://dx.doi.org/10.1111/cts.13512</t>
+  </si>
+  <si>
+    <t>https://dx.doi.org/10.1111/dom.15569</t>
+  </si>
+  <si>
+    <t>duration_unit</t>
+  </si>
+  <si>
+    <t>weeks</t>
+  </si>
+  <si>
+    <t>positive_baseline_n</t>
+  </si>
+  <si>
+    <t>negative_baseline_n</t>
+  </si>
+  <si>
+    <t>cognition_baseline_n</t>
+  </si>
+  <si>
+    <t>weight_baseline_n</t>
+  </si>
+  <si>
+    <t>prolactin_baseline_n</t>
+  </si>
+  <si>
+    <t>ulotaront 50mg/d (adolescents)</t>
+  </si>
+  <si>
+    <t>ulotaront 75mg/d (adolescents)</t>
+  </si>
+  <si>
+    <t>placebo (adolescents)</t>
+  </si>
+  <si>
+    <t>Schizophrenia spectrum (acute episode, adolescents)</t>
+  </si>
+  <si>
+    <t>psychosis_e</t>
+  </si>
+  <si>
+    <t>psychosis_n</t>
+  </si>
+  <si>
     <t>NCT04072354 (2019)</t>
   </si>
   <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>435</t>
-  </si>
-  <si>
-    <t>ulotaront 75mg/d (adults)</t>
-  </si>
-  <si>
-    <t>75</t>
-  </si>
-  <si>
-    <t>placebo (adults)</t>
-  </si>
-  <si>
-    <t>ulotaront 75mg/d</t>
-  </si>
-  <si>
-    <t>NCT04092686 (2019)</t>
-  </si>
-  <si>
-    <t>464</t>
-  </si>
-  <si>
-    <t>ulotaront 100mg/d</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>placebo (P2; 4 weeks)</t>
-  </si>
-  <si>
-    <t>NCT04512066 (2020)</t>
-  </si>
-  <si>
-    <t>287</t>
-  </si>
-  <si>
-    <t>33.1</t>
-  </si>
-  <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>endpoint</t>
-  </si>
-  <si>
-    <t>PANSS anxiety/depression</t>
-  </si>
-  <si>
-    <t>ralmitaront 45mg (P2; 4 weeks)</t>
-  </si>
-  <si>
-    <t>ralmitaront</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>ralmitaront 150mg (P2; 4 weeks)</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>68</t>
-  </si>
-  <si>
-    <t>69</t>
-  </si>
-  <si>
-    <t>risperidone (P2; 4 weeks)</t>
-  </si>
-  <si>
-    <t>risperidone</t>
-  </si>
-  <si>
-    <t>74</t>
-  </si>
-  <si>
-    <t>D2 antipsychotic</t>
-  </si>
-  <si>
-    <t>placebo (LS and HS)</t>
-  </si>
-  <si>
-    <t>Perini (2023)</t>
-  </si>
-  <si>
-    <t>Healthy volunteers</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>29.2</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>1 day-2 weeks</t>
-  </si>
-  <si>
-    <t>ulotaront (LS and HS)</t>
-  </si>
-  <si>
-    <t>27.4</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>amisulpride (LS and HS)</t>
-  </si>
-  <si>
-    <t>amisulpride</t>
-  </si>
-  <si>
-    <t>400</t>
-  </si>
-  <si>
-    <t>27.6</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>Tsukada (2023)</t>
-  </si>
-  <si>
-    <t>crossover-RCT</t>
-  </si>
-  <si>
-    <t>stable</t>
-  </si>
-  <si>
-    <t>48.3</t>
-  </si>
-  <si>
-    <t>63</t>
-  </si>
-  <si>
-    <t>ulotaront 150mg</t>
-  </si>
-  <si>
-    <t>ulotaront 10mg</t>
-  </si>
-  <si>
-    <t>Hopkins (2021)</t>
-  </si>
-  <si>
-    <t>25.1</t>
-  </si>
-  <si>
-    <t>ulotaront 50mg</t>
-  </si>
-  <si>
-    <t>Szabo (2023)</t>
-  </si>
-  <si>
-    <t>Narcolepsy-cataplexy</t>
-  </si>
-  <si>
-    <t>32.9</t>
-  </si>
-  <si>
-    <t>ulotaront 25mg</t>
-  </si>
-  <si>
-    <t>anticholinergic_symptom_e</t>
-  </si>
-  <si>
-    <t>anticholinergic_symptom_n</t>
-  </si>
-  <si>
-    <t>NCT04115319 (2019)</t>
-  </si>
-  <si>
-    <t>quetiapine XR</t>
-  </si>
-  <si>
-    <t>50-100</t>
-  </si>
-  <si>
-    <t>quetiapine</t>
-  </si>
-  <si>
-    <t>400-800</t>
-  </si>
-  <si>
-    <t>placebo (monotherapy)</t>
-  </si>
-  <si>
-    <t>negative symptoms</t>
-  </si>
-  <si>
-    <t>placebo (add-on)</t>
-  </si>
-  <si>
-    <t>BNSS total</t>
-  </si>
-  <si>
-    <t>ralmitaront 45mg (add-on)</t>
-  </si>
-  <si>
-    <t>ralmitaront 150mg (add-on)</t>
-  </si>
-  <si>
-    <t>ralmitaront 350mg (add-on)</t>
-  </si>
-  <si>
-    <t>ralmitaront 150mg  (monotherapy)</t>
-  </si>
-  <si>
-    <t>TAAR1 agonist (add-on)</t>
-  </si>
-  <si>
-    <t>antipsychotic (aripiprazole, olanzapine, quetiapine, risperidone)</t>
-  </si>
-  <si>
-    <t>NCT05402111 (2022)</t>
-  </si>
-  <si>
-    <t>Schizophrenia spectrum (negative symptoms)</t>
-  </si>
-  <si>
-    <t>Schizophrenia spectrum (clinically stable)</t>
-  </si>
-  <si>
-    <t>Schizophrenia spectrum (acute episode)</t>
-  </si>
-  <si>
-    <t>&gt;13 weeks</t>
-  </si>
-  <si>
-    <t>ralmitaront (addon)</t>
-  </si>
-  <si>
-    <t>placebo (addon)</t>
-  </si>
-  <si>
-    <t>Schizophrenia spectrum (clinically stable, MetS)</t>
-  </si>
-  <si>
-    <t>study_year</t>
-  </si>
-  <si>
-    <t>study_doi</t>
-  </si>
-  <si>
-    <t>10.1212/CPJ.0000000000200175</t>
-  </si>
-  <si>
-    <t>https://dx.doi.org/10.1016/j.sleep.2023.04.019</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1038/s41398-021-01331-9</t>
-  </si>
-  <si>
-    <t>overall_baseline_n</t>
-  </si>
-  <si>
-    <t>depression_baseline_n</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1056/nejmoa1911772</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1038/s41537-023-00385-6</t>
-  </si>
-  <si>
-    <t>https://dx.doi.org/10.1111/cts.13512</t>
-  </si>
-  <si>
-    <t>https://dx.doi.org/10.1111/dom.15569</t>
-  </si>
-  <si>
-    <t>duration_unit</t>
-  </si>
-  <si>
-    <t>weeks</t>
-  </si>
-  <si>
-    <t>positive_baseline_n</t>
-  </si>
-  <si>
-    <t>negative_baseline_n</t>
-  </si>
-  <si>
-    <t>cognition_baseline_n</t>
-  </si>
-  <si>
-    <t>weight_baseline_n</t>
-  </si>
-  <si>
-    <t>prolactin_baseline_n</t>
-  </si>
-  <si>
-    <t>ulotaront 50mg/d (adolescents)</t>
-  </si>
-  <si>
-    <t>ulotaront 75mg/d (adolescents)</t>
-  </si>
-  <si>
-    <t>placebo (adolescents)</t>
-  </si>
-  <si>
-    <t>Schizophrenia spectrum (acute episode, adolescents)</t>
-  </si>
-  <si>
     <t>NCT03669640 (2018)</t>
   </si>
   <si>
-    <t>NCT03669640 (2018, addon)</t>
-  </si>
-  <si>
-    <t>NCT04072354 (2019, adolescent)</t>
-  </si>
-  <si>
-    <t>psychosis_e</t>
-  </si>
-  <si>
-    <t>psychosis_n</t>
+    <t>NCT03669640 (2018):addon</t>
+  </si>
+  <si>
+    <t>NCT04072354 (2019):adolescents</t>
   </si>
 </sst>
 </file>
@@ -1003,7 +1012,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1064,12 +1073,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1084,7 +1087,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1110,7 +1113,6 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1431,11 +1433,17 @@
   <threadedComment ref="DD6" dT="2025-08-15T21:16:55.84" personId="{9C02175C-AB95-C54D-8A67-708063150B15}" id="{5B87CDAA-9B3C-2740-B825-05967E84E211}">
     <text>dry mouth, constipation, dry eye</text>
   </threadedComment>
-  <threadedComment ref="S30" dT="2025-08-16T13:49:55.55" personId="{9C02175C-AB95-C54D-8A67-708063150B15}" id="{0971AB22-BB3D-6E44-92EF-19F7F720FCF8}">
-    <text>SAE schizophrenia / not dropout due to inefficacy</text>
+  <threadedComment ref="S30" dT="2025-08-18T07:46:21.71" personId="{9C02175C-AB95-C54D-8A67-708063150B15}" id="{9C13DC03-74BA-9F44-B4A7-E9BF90B96B62}">
+    <text>imputed as PANSS+12</text>
+  </threadedComment>
+  <threadedComment ref="EF30" dT="2025-08-18T08:35:15.00" personId="{9C02175C-AB95-C54D-8A67-708063150B15}" id="{C74A172F-8133-EE4C-A9EF-A5408B33064F}">
+    <text>poster: both SAE and non-SAE</text>
   </threadedComment>
   <threadedComment ref="Q32" dT="2025-01-16T13:52:04.57" personId="{9C02175C-AB95-C54D-8A67-708063150B15}" id="{63125C18-1CF7-5340-80AF-3F079B6ADA33}">
     <text>Imputed from panss total</text>
+  </threadedComment>
+  <threadedComment ref="S32" dT="2025-08-18T08:01:58.59" personId="{9C02175C-AB95-C54D-8A67-708063150B15}" id="{E49234FE-6618-9C41-BBEF-153C57A2EE59}">
+    <text xml:space="preserve">same as imputed from PANSS total </text>
   </threadedComment>
 </ThreadedComments>
 </file>
@@ -1446,7 +1454,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="50.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.5" customWidth="1"/>
     <col min="3" max="3" width="9.5" style="16" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.83203125" style="16" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="5" bestFit="1" customWidth="1"/>
@@ -1571,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
@@ -1610,7 +1618,7 @@
         <v>12</v>
       </c>
       <c r="P1" s="15" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>13</v>
@@ -1673,7 +1681,7 @@
         <v>32</v>
       </c>
       <c r="AK1" s="15" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="AL1" s="1" t="s">
         <v>33</v>
@@ -1700,7 +1708,7 @@
         <v>40</v>
       </c>
       <c r="AT1" s="15" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="AU1" s="1" t="s">
         <v>41</v>
@@ -1727,7 +1735,7 @@
         <v>48</v>
       </c>
       <c r="BC1" s="15" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="BD1" s="1" t="s">
         <v>49</v>
@@ -1778,7 +1786,7 @@
         <v>64</v>
       </c>
       <c r="BT1" s="15" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="BU1" s="1" t="s">
         <v>65</v>
@@ -1805,7 +1813,7 @@
         <v>72</v>
       </c>
       <c r="CC1" s="15" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="CD1" s="1" t="s">
         <v>73</v>
@@ -1832,7 +1840,7 @@
         <v>80</v>
       </c>
       <c r="CL1" s="15" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="CM1" s="1" t="s">
         <v>81</v>
@@ -1859,7 +1867,7 @@
         <v>88</v>
       </c>
       <c r="CU1" s="15" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="CV1" s="1" t="s">
         <v>89</v>
@@ -1886,10 +1894,10 @@
         <v>96</v>
       </c>
       <c r="DD1" s="7" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="DE1" s="7" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="DF1" s="1" t="s">
         <v>97</v>
@@ -1970,10 +1978,10 @@
         <v>122</v>
       </c>
       <c r="EF1" s="1" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="EG1" s="1" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="EH1" s="1" t="s">
         <v>123</v>
@@ -1996,7 +2004,7 @@
         <v>2023</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -2022,8 +2030,8 @@
       <c r="L2">
         <v>25</v>
       </c>
-      <c r="M2" t="s">
-        <v>148</v>
+      <c r="M2" s="8">
+        <v>70.400000000000006</v>
       </c>
       <c r="N2">
         <v>4</v>
@@ -2032,22 +2040,22 @@
         <v>6</v>
       </c>
       <c r="P2" s="16" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="Q2" t="s">
+        <v>148</v>
+      </c>
+      <c r="R2" t="s">
         <v>149</v>
       </c>
-      <c r="R2" t="s">
+      <c r="U2" t="s">
         <v>150</v>
-      </c>
-      <c r="U2" t="s">
-        <v>151</v>
       </c>
       <c r="V2" t="s">
         <v>140</v>
       </c>
       <c r="W2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="X2" t="s">
         <v>140</v>
@@ -2059,31 +2067,31 @@
         <v>140</v>
       </c>
       <c r="AA2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AB2" t="s">
         <v>140</v>
       </c>
       <c r="AC2" t="s">
+        <v>153</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>153</v>
+      </c>
+      <c r="AE2" t="s">
         <v>154</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AF2" t="s">
+        <v>153</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>153</v>
+      </c>
+      <c r="AH2" t="s">
         <v>154</v>
       </c>
-      <c r="AE2" t="s">
-        <v>155</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>154</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>154</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>155</v>
-      </c>
       <c r="AI2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AJ2">
         <v>23</v>
@@ -2104,7 +2112,7 @@
         <v>131</v>
       </c>
       <c r="AR2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AS2">
         <v>24</v>
@@ -2131,7 +2139,7 @@
         <v>131</v>
       </c>
       <c r="BR2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="BS2">
         <v>23</v>
@@ -2207,7 +2215,7 @@
         <v>137</v>
       </c>
       <c r="EI2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="EJ2" t="s">
         <v>131</v>
@@ -2215,7 +2223,7 @@
     </row>
     <row r="3" spans="1:140" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B3" t="s">
         <v>142</v>
@@ -2224,7 +2232,7 @@
         <v>2023</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -2233,7 +2241,7 @@
         <v>143</v>
       </c>
       <c r="G3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H3" t="s">
         <v>127</v>
@@ -2250,8 +2258,8 @@
       <c r="L3">
         <v>14</v>
       </c>
-      <c r="M3" t="s">
-        <v>148</v>
+      <c r="M3" s="8">
+        <v>71.8</v>
       </c>
       <c r="N3">
         <v>1</v>
@@ -2260,58 +2268,58 @@
         <v>6</v>
       </c>
       <c r="P3" s="16" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="Q3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="R3" t="s">
         <v>141</v>
       </c>
       <c r="U3" t="s">
+        <v>161</v>
+      </c>
+      <c r="V3" t="s">
         <v>162</v>
       </c>
-      <c r="V3" t="s">
+      <c r="W3" t="s">
         <v>163</v>
       </c>
-      <c r="W3" t="s">
-        <v>164</v>
-      </c>
       <c r="X3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Y3" t="s">
         <v>127</v>
       </c>
       <c r="Z3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AA3" t="s">
         <v>127</v>
       </c>
       <c r="AB3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AC3" t="s">
+        <v>153</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>153</v>
+      </c>
+      <c r="AE3" t="s">
         <v>154</v>
       </c>
-      <c r="AD3" t="s">
+      <c r="AF3" t="s">
+        <v>153</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>153</v>
+      </c>
+      <c r="AH3" t="s">
         <v>154</v>
       </c>
-      <c r="AE3" t="s">
-        <v>155</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>154</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>154</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>155</v>
-      </c>
       <c r="AI3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AJ3">
         <v>14</v>
@@ -2332,7 +2340,7 @@
         <v>131</v>
       </c>
       <c r="AR3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AS3">
         <v>14</v>
@@ -2359,7 +2367,7 @@
         <v>131</v>
       </c>
       <c r="BR3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="BS3">
         <v>14</v>
@@ -2440,10 +2448,10 @@
         <v>14</v>
       </c>
       <c r="EH3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="EI3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="EJ3" t="s">
         <v>131</v>
@@ -2454,13 +2462,13 @@
         <v>126</v>
       </c>
       <c r="B4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C4" s="16">
         <v>2020</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -2472,22 +2480,22 @@
         <v>126</v>
       </c>
       <c r="H4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="J4" t="s">
         <v>146</v>
       </c>
       <c r="K4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L4">
         <v>120</v>
       </c>
-      <c r="M4" t="s">
-        <v>168</v>
+      <c r="M4" s="8">
+        <v>30</v>
       </c>
       <c r="N4">
         <v>43</v>
@@ -2496,55 +2504,55 @@
         <v>4</v>
       </c>
       <c r="P4" s="16" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="Q4" t="s">
         <v>138</v>
       </c>
       <c r="R4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="U4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="V4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="W4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="X4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Y4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Z4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="AA4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AB4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="AC4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AD4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AE4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AF4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AG4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AH4" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AI4" t="s">
         <v>128</v>
@@ -2601,7 +2609,7 @@
         <v>131</v>
       </c>
       <c r="BA4" s="9" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="BB4">
         <v>120</v>
@@ -2778,7 +2786,7 @@
         <v>137</v>
       </c>
       <c r="EI4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="EJ4" t="s">
         <v>131</v>
@@ -2786,16 +2794,16 @@
     </row>
     <row r="5" spans="1:140" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C5" s="16">
         <v>2020</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -2804,25 +2812,25 @@
         <v>143</v>
       </c>
       <c r="G5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H5" t="s">
         <v>127</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="J5" t="s">
         <v>146</v>
       </c>
       <c r="K5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L5">
         <v>125</v>
       </c>
-      <c r="M5" t="s">
-        <v>168</v>
+      <c r="M5" s="8">
+        <v>30.6</v>
       </c>
       <c r="N5">
         <v>46</v>
@@ -2831,55 +2839,55 @@
         <v>4</v>
       </c>
       <c r="P5" s="16" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="Q5" t="s">
+        <v>169</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="U5" t="s">
+        <v>168</v>
+      </c>
+      <c r="V5" t="s">
+        <v>170</v>
+      </c>
+      <c r="W5" t="s">
         <v>171</v>
       </c>
-      <c r="R5" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="U5" t="s">
+      <c r="X5" t="s">
         <v>170</v>
-      </c>
-      <c r="V5" t="s">
-        <v>172</v>
-      </c>
-      <c r="W5" t="s">
-        <v>173</v>
-      </c>
-      <c r="X5" t="s">
-        <v>172</v>
       </c>
       <c r="Y5" t="s">
         <v>127</v>
       </c>
       <c r="Z5" t="s">
+        <v>170</v>
+      </c>
+      <c r="AA5" t="s">
         <v>172</v>
       </c>
-      <c r="AA5" t="s">
-        <v>174</v>
-      </c>
       <c r="AB5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AC5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AD5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AE5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AF5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AG5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AH5" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AI5" t="s">
         <v>128</v>
@@ -2936,7 +2944,7 @@
         <v>131</v>
       </c>
       <c r="BA5" s="9" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="BB5">
         <v>125</v>
@@ -3110,10 +3118,10 @@
         <v>125</v>
       </c>
       <c r="EH5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="EI5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="EJ5" t="s">
         <v>131</v>
@@ -3121,10 +3129,10 @@
     </row>
     <row r="6" spans="1:140" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B6" t="s">
-        <v>176</v>
+        <v>284</v>
       </c>
       <c r="C6" s="16">
         <v>2023</v>
@@ -3139,10 +3147,10 @@
         <v>126</v>
       </c>
       <c r="H6" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="J6" t="s">
         <v>146</v>
@@ -3163,7 +3171,7 @@
         <v>6</v>
       </c>
       <c r="P6" s="16" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="Q6" s="2">
         <v>22</v>
@@ -3196,22 +3204,22 @@
         <v>144</v>
       </c>
       <c r="AC6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AD6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AE6" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AF6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AG6" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AH6" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AI6" t="s">
         <v>128</v>
@@ -3255,8 +3263,8 @@
       <c r="AV6" s="8">
         <v>-5.7</v>
       </c>
-      <c r="AW6" s="19">
-        <v>6</v>
+      <c r="AW6" s="8">
+        <v>5</v>
       </c>
       <c r="AX6" s="8" t="s">
         <v>129</v>
@@ -3268,7 +3276,7 @@
         <v>130</v>
       </c>
       <c r="BA6" s="8" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="BB6" s="16">
         <v>142</v>
@@ -3282,8 +3290,8 @@
       <c r="BE6" s="8">
         <v>-5.5</v>
       </c>
-      <c r="BF6" s="19">
-        <v>15</v>
+      <c r="BF6" s="8">
+        <v>12</v>
       </c>
       <c r="BG6" s="8" t="s">
         <v>129</v>
@@ -3364,7 +3372,7 @@
         <v>137</v>
       </c>
       <c r="EI6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="EJ6" t="s">
         <v>131</v>
@@ -3372,10 +3380,10 @@
     </row>
     <row r="7" spans="1:140" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B7" t="s">
-        <v>176</v>
+        <v>284</v>
       </c>
       <c r="C7" s="16">
         <v>2023</v>
@@ -3390,10 +3398,10 @@
         <v>126</v>
       </c>
       <c r="H7" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="J7" t="s">
         <v>146</v>
@@ -3414,7 +3422,7 @@
         <v>6</v>
       </c>
       <c r="P7" s="16" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="Q7" s="2">
         <v>29</v>
@@ -3447,22 +3455,22 @@
         <v>145</v>
       </c>
       <c r="AC7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AD7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AE7" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AF7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AG7" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AH7" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AI7" t="s">
         <v>128</v>
@@ -3506,8 +3514,8 @@
       <c r="AV7" s="8">
         <v>-7</v>
       </c>
-      <c r="AW7" s="19">
-        <v>6</v>
+      <c r="AW7" s="8">
+        <v>5</v>
       </c>
       <c r="AX7" s="8" t="s">
         <v>129</v>
@@ -3519,7 +3527,7 @@
         <v>130</v>
       </c>
       <c r="BA7" s="8" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="BB7" s="16">
         <v>145</v>
@@ -3533,8 +3541,8 @@
       <c r="BE7" s="8">
         <v>-7.3</v>
       </c>
-      <c r="BF7" s="19">
-        <v>15</v>
+      <c r="BF7" s="8">
+        <v>12</v>
       </c>
       <c r="BG7" s="8" t="s">
         <v>129</v>
@@ -3615,7 +3623,7 @@
         <v>137</v>
       </c>
       <c r="EI7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="EJ7" t="s">
         <v>131</v>
@@ -3623,10 +3631,10 @@
     </row>
     <row r="8" spans="1:140" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B8" t="s">
-        <v>176</v>
+        <v>284</v>
       </c>
       <c r="C8" s="16">
         <v>2023</v>
@@ -3638,19 +3646,19 @@
         <v>143</v>
       </c>
       <c r="G8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H8" t="s">
         <v>127</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="J8" t="s">
         <v>146</v>
       </c>
       <c r="K8" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="L8" s="3">
         <v>146</v>
@@ -3665,7 +3673,7 @@
         <v>6</v>
       </c>
       <c r="P8" s="16" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="Q8" s="2">
         <v>26</v>
@@ -3692,28 +3700,28 @@
         <v>146</v>
       </c>
       <c r="AA8" s="8">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AB8" s="8">
         <v>146</v>
       </c>
       <c r="AC8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AD8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AE8" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AF8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AG8" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AH8" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AI8" t="s">
         <v>128</v>
@@ -3757,8 +3765,8 @@
       <c r="AV8" s="8">
         <v>-6.4</v>
       </c>
-      <c r="AW8" s="19">
-        <v>6</v>
+      <c r="AW8" s="8">
+        <v>5</v>
       </c>
       <c r="AX8" s="8" t="s">
         <v>129</v>
@@ -3770,7 +3778,7 @@
         <v>130</v>
       </c>
       <c r="BA8" s="8" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="BB8" s="16">
         <v>145</v>
@@ -3784,8 +3792,8 @@
       <c r="BE8" s="8">
         <v>-6.2</v>
       </c>
-      <c r="BF8" s="19">
-        <v>15</v>
+      <c r="BF8" s="8">
+        <v>12</v>
       </c>
       <c r="BG8" s="8" t="s">
         <v>129</v>
@@ -3863,10 +3871,10 @@
         <v>146</v>
       </c>
       <c r="EH8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="EI8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="EJ8" t="s">
         <v>131</v>
@@ -3874,10 +3882,10 @@
     </row>
     <row r="9" spans="1:140" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B9" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C9" s="16">
         <v>2023</v>
@@ -3893,10 +3901,10 @@
         <v>126</v>
       </c>
       <c r="H9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="J9" s="10" t="s">
         <v>146</v>
@@ -3917,10 +3925,11 @@
         <v>6</v>
       </c>
       <c r="P9" s="16" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="Q9" s="8"/>
       <c r="R9" s="18"/>
+      <c r="T9"/>
       <c r="U9" s="8">
         <v>1</v>
       </c>
@@ -3946,22 +3955,22 @@
         <v>9</v>
       </c>
       <c r="AC9" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AD9" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AE9" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AF9" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AG9" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AH9" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AI9" t="s">
         <v>128</v>
@@ -4039,7 +4048,7 @@
         <v>137</v>
       </c>
       <c r="EI9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="EJ9" t="s">
         <v>131</v>
@@ -4047,10 +4056,10 @@
     </row>
     <row r="10" spans="1:140" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C10" s="16">
         <v>2023</v>
@@ -4066,10 +4075,10 @@
         <v>126</v>
       </c>
       <c r="H10" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="J10" s="10" t="s">
         <v>146</v>
@@ -4090,10 +4099,11 @@
         <v>6</v>
       </c>
       <c r="P10" s="16" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="Q10" s="8"/>
       <c r="R10" s="18"/>
+      <c r="T10"/>
       <c r="U10" s="8">
         <v>1</v>
       </c>
@@ -4119,22 +4129,22 @@
         <v>9</v>
       </c>
       <c r="AC10" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AD10" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AE10" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AF10" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AG10" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AH10" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AI10" t="s">
         <v>128</v>
@@ -4212,7 +4222,7 @@
         <v>137</v>
       </c>
       <c r="EI10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="EJ10" t="s">
         <v>131</v>
@@ -4220,10 +4230,10 @@
     </row>
     <row r="11" spans="1:140" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B11" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C11" s="16">
         <v>2023</v>
@@ -4236,13 +4246,13 @@
         <v>143</v>
       </c>
       <c r="G11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H11" t="s">
         <v>127</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="J11" s="10" t="s">
         <v>146</v>
@@ -4263,10 +4273,11 @@
         <v>6</v>
       </c>
       <c r="P11" s="16" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="Q11" s="8"/>
       <c r="R11" s="18"/>
+      <c r="T11"/>
       <c r="U11" s="8">
         <v>0</v>
       </c>
@@ -4292,22 +4303,22 @@
         <v>10</v>
       </c>
       <c r="AC11" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AD11" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AE11" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AF11" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AG11" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AH11" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AI11" t="s">
         <v>128</v>
@@ -4382,10 +4393,10 @@
         <v>10</v>
       </c>
       <c r="EH11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="EI11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="EJ11" t="s">
         <v>131</v>
@@ -4393,10 +4404,10 @@
     </row>
     <row r="12" spans="1:140" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B12" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C12" s="16">
         <v>2023</v>
@@ -4411,16 +4422,16 @@
         <v>126</v>
       </c>
       <c r="H12" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="J12" t="s">
         <v>146</v>
       </c>
       <c r="K12" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="L12" s="2">
         <v>155</v>
@@ -4435,7 +4446,7 @@
         <v>6</v>
       </c>
       <c r="P12" s="16" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="Q12" s="2">
         <v>23</v>
@@ -4468,22 +4479,22 @@
         <v>155</v>
       </c>
       <c r="AC12" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AD12" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AE12" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AF12" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AG12" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AH12" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AI12" t="s">
         <v>128</v>
@@ -4527,8 +4538,8 @@
       <c r="AV12" s="8">
         <v>-5.2</v>
       </c>
-      <c r="AW12" s="19">
-        <v>6</v>
+      <c r="AW12" s="8">
+        <v>5</v>
       </c>
       <c r="AX12" s="8" t="s">
         <v>129</v>
@@ -4540,7 +4551,7 @@
         <v>130</v>
       </c>
       <c r="BA12" s="8" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="BB12" s="8">
         <v>153</v>
@@ -4554,8 +4565,8 @@
       <c r="BE12" s="8">
         <v>-6</v>
       </c>
-      <c r="BF12" s="19">
-        <v>15</v>
+      <c r="BF12" s="8">
+        <v>12</v>
       </c>
       <c r="BG12" s="8" t="s">
         <v>129</v>
@@ -4618,7 +4629,7 @@
         <v>137</v>
       </c>
       <c r="EI12" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="EJ12" t="s">
         <v>131</v>
@@ -4626,10 +4637,10 @@
     </row>
     <row r="13" spans="1:140" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B13" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C13" s="16">
         <v>2023</v>
@@ -4644,16 +4655,16 @@
         <v>126</v>
       </c>
       <c r="H13" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="J13" t="s">
         <v>146</v>
       </c>
       <c r="K13" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="L13" s="2">
         <v>154</v>
@@ -4668,7 +4679,7 @@
         <v>6</v>
       </c>
       <c r="P13" s="16" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="Q13" s="2">
         <v>27</v>
@@ -4701,22 +4712,22 @@
         <v>154</v>
       </c>
       <c r="AC13" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AD13" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AE13" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AF13" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AG13" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AH13" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AI13" t="s">
         <v>128</v>
@@ -4760,8 +4771,8 @@
       <c r="AV13" s="8">
         <v>-5.5</v>
       </c>
-      <c r="AW13" s="19">
-        <v>6</v>
+      <c r="AW13" s="8">
+        <v>5</v>
       </c>
       <c r="AX13" s="8" t="s">
         <v>129</v>
@@ -4773,7 +4784,7 @@
         <v>130</v>
       </c>
       <c r="BA13" s="8" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="BB13" s="8">
         <v>152</v>
@@ -4787,8 +4798,8 @@
       <c r="BE13" s="8">
         <v>-6.4</v>
       </c>
-      <c r="BF13" s="19">
-        <v>15</v>
+      <c r="BF13" s="8">
+        <v>12</v>
       </c>
       <c r="BG13" s="8" t="s">
         <v>129</v>
@@ -4851,7 +4862,7 @@
         <v>137</v>
       </c>
       <c r="EI13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="EJ13" t="s">
         <v>131</v>
@@ -4859,10 +4870,10 @@
     </row>
     <row r="14" spans="1:140" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B14" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C14" s="16">
         <v>2023</v>
@@ -4874,19 +4885,19 @@
         <v>143</v>
       </c>
       <c r="G14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H14" t="s">
         <v>127</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="J14" t="s">
         <v>146</v>
       </c>
       <c r="K14" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="L14" s="2">
         <v>155</v>
@@ -4901,7 +4912,7 @@
         <v>6</v>
       </c>
       <c r="P14" s="16" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="Q14" s="2">
         <v>21</v>
@@ -4934,22 +4945,22 @@
         <v>155</v>
       </c>
       <c r="AC14" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AD14" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AE14" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AF14" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AG14" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AH14" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AI14" t="s">
         <v>128</v>
@@ -4993,8 +5004,8 @@
       <c r="AV14" s="8">
         <v>-4.5999999999999996</v>
       </c>
-      <c r="AW14" s="19">
-        <v>6</v>
+      <c r="AW14" s="8">
+        <v>5</v>
       </c>
       <c r="AX14" s="8" t="s">
         <v>129</v>
@@ -5006,7 +5017,7 @@
         <v>130</v>
       </c>
       <c r="BA14" s="8" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="BB14" s="8">
         <v>155</v>
@@ -5020,8 +5031,8 @@
       <c r="BE14" s="8">
         <v>-4.5</v>
       </c>
-      <c r="BF14" s="19">
-        <v>15</v>
+      <c r="BF14" s="8">
+        <v>12</v>
       </c>
       <c r="BG14" s="8" t="s">
         <v>129</v>
@@ -5081,10 +5092,10 @@
         <v>155</v>
       </c>
       <c r="EH14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="EI14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="EJ14" t="s">
         <v>131</v>
@@ -5092,10 +5103,10 @@
     </row>
     <row r="15" spans="1:140" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B15" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C15" s="16">
         <v>2023</v>
@@ -5107,25 +5118,25 @@
         <v>143</v>
       </c>
       <c r="G15" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H15" t="s">
         <v>127</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="J15" t="s">
         <v>146</v>
       </c>
       <c r="K15" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="L15">
         <v>73</v>
       </c>
-      <c r="M15" t="s">
-        <v>191</v>
+      <c r="M15">
+        <v>33.200000000000003</v>
       </c>
       <c r="N15">
         <v>19</v>
@@ -5134,55 +5145,55 @@
         <v>4</v>
       </c>
       <c r="P15" s="16" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="Q15" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="R15" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="U15" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="V15" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="W15" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="X15" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="Y15" t="s">
         <v>127</v>
       </c>
       <c r="Z15" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="AA15" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AB15" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="AC15" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AD15" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AE15" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AF15" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AG15" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AH15" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AI15" t="s">
         <v>128</v>
@@ -5203,7 +5214,7 @@
         <v>20.18</v>
       </c>
       <c r="AO15" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AP15" t="s">
         <v>131</v>
@@ -5230,7 +5241,7 @@
         <v>6.64</v>
       </c>
       <c r="AX15" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AY15" t="s">
         <v>131</v>
@@ -5257,7 +5268,7 @@
         <v>5.81</v>
       </c>
       <c r="BG15" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="BH15" t="s">
         <v>131</v>
@@ -5266,7 +5277,7 @@
         <v>131</v>
       </c>
       <c r="CA15" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="CB15">
         <v>54</v>
@@ -5284,7 +5295,7 @@
         <v>4.03</v>
       </c>
       <c r="CG15" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="CH15" t="s">
         <v>131</v>
@@ -5341,10 +5352,10 @@
         <v>72</v>
       </c>
       <c r="EH15" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="EI15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="EJ15" t="s">
         <v>131</v>
@@ -5352,10 +5363,10 @@
     </row>
     <row r="16" spans="1:140" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B16" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C16" s="16">
         <v>2023</v>
@@ -5367,25 +5378,25 @@
         <v>143</v>
       </c>
       <c r="G16" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="H16" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="J16" t="s">
         <v>146</v>
       </c>
       <c r="K16" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="L16">
         <v>71</v>
       </c>
-      <c r="M16" t="s">
-        <v>191</v>
+      <c r="M16">
+        <v>34</v>
       </c>
       <c r="N16">
         <v>19</v>
@@ -5394,55 +5405,55 @@
         <v>4</v>
       </c>
       <c r="P16" s="16" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="Q16" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="R16" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="U16" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="V16" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="W16" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="X16" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="Y16" s="5">
         <v>0</v>
       </c>
       <c r="Z16" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="AA16" s="5">
         <v>2</v>
       </c>
       <c r="AB16" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="AC16" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AD16" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AE16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AF16" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AG16" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AH16" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AI16" t="s">
         <v>128</v>
@@ -5463,7 +5474,7 @@
         <v>17.03</v>
       </c>
       <c r="AO16" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AP16" t="s">
         <v>131</v>
@@ -5490,7 +5501,7 @@
         <v>6.14</v>
       </c>
       <c r="AX16" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AY16" t="s">
         <v>131</v>
@@ -5517,7 +5528,7 @@
         <v>5.85</v>
       </c>
       <c r="BG16" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="BH16" t="s">
         <v>131</v>
@@ -5526,7 +5537,7 @@
         <v>131</v>
       </c>
       <c r="CA16" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="CB16">
         <v>49</v>
@@ -5544,7 +5555,7 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="CG16" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="CH16" t="s">
         <v>131</v>
@@ -5604,7 +5615,7 @@
         <v>137</v>
       </c>
       <c r="EI16" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="EJ16" t="s">
         <v>131</v>
@@ -5612,10 +5623,10 @@
     </row>
     <row r="17" spans="1:140" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B17" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C17" s="16">
         <v>2023</v>
@@ -5627,25 +5638,25 @@
         <v>143</v>
       </c>
       <c r="G17" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="H17" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="J17" t="s">
         <v>146</v>
       </c>
       <c r="K17" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="L17">
         <v>69</v>
       </c>
-      <c r="M17" t="s">
-        <v>191</v>
+      <c r="M17">
+        <v>32.299999999999997</v>
       </c>
       <c r="N17">
         <v>15</v>
@@ -5654,55 +5665,55 @@
         <v>4</v>
       </c>
       <c r="P17" s="16" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="Q17" t="s">
+        <v>148</v>
+      </c>
+      <c r="R17" t="s">
+        <v>200</v>
+      </c>
+      <c r="U17" t="s">
         <v>149</v>
       </c>
-      <c r="R17" t="s">
-        <v>204</v>
-      </c>
-      <c r="U17" t="s">
-        <v>150</v>
-      </c>
       <c r="V17" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="W17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="X17" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="Y17" t="s">
         <v>127</v>
       </c>
       <c r="Z17" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="AA17" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AB17" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="AC17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AD17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AE17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AF17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AG17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AH17" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AI17" t="s">
         <v>128</v>
@@ -5723,7 +5734,7 @@
         <v>17.670000000000002</v>
       </c>
       <c r="AO17" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AP17" t="s">
         <v>131</v>
@@ -5750,7 +5761,7 @@
         <v>6.5</v>
       </c>
       <c r="AX17" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AY17" t="s">
         <v>131</v>
@@ -5777,7 +5788,7 @@
         <v>5.41</v>
       </c>
       <c r="BG17" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="BH17" t="s">
         <v>131</v>
@@ -5786,7 +5797,7 @@
         <v>131</v>
       </c>
       <c r="CA17" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="CB17">
         <v>51</v>
@@ -5804,7 +5815,7 @@
         <v>4.08</v>
       </c>
       <c r="CG17" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="CH17" t="s">
         <v>131</v>
@@ -5864,7 +5875,7 @@
         <v>137</v>
       </c>
       <c r="EI17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="EJ17" t="s">
         <v>131</v>
@@ -5872,10 +5883,10 @@
     </row>
     <row r="18" spans="1:140" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B18" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C18" s="16">
         <v>2023</v>
@@ -5887,25 +5898,25 @@
         <v>143</v>
       </c>
       <c r="G18" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="H18" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="J18" t="s">
         <v>146</v>
       </c>
       <c r="K18" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="L18">
         <v>74</v>
       </c>
-      <c r="M18" t="s">
-        <v>191</v>
+      <c r="M18">
+        <v>32.9</v>
       </c>
       <c r="N18">
         <v>18</v>
@@ -5914,55 +5925,55 @@
         <v>4</v>
       </c>
       <c r="P18" s="16" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="Q18" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="R18" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="U18" t="s">
+        <v>162</v>
+      </c>
+      <c r="V18" t="s">
+        <v>204</v>
+      </c>
+      <c r="W18" t="s">
         <v>163</v>
       </c>
-      <c r="V18" t="s">
-        <v>208</v>
-      </c>
-      <c r="W18" t="s">
-        <v>164</v>
-      </c>
       <c r="X18" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="Y18" t="s">
         <v>127</v>
       </c>
       <c r="Z18" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="AA18" t="s">
         <v>127</v>
       </c>
       <c r="AB18" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="AC18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AD18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AE18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AF18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AG18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AH18" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AI18" t="s">
         <v>128</v>
@@ -5983,7 +5994,7 @@
         <v>15.78</v>
       </c>
       <c r="AO18" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AP18" t="s">
         <v>131</v>
@@ -6010,7 +6021,7 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="AX18" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AY18" t="s">
         <v>131</v>
@@ -6037,7 +6048,7 @@
         <v>5.13</v>
       </c>
       <c r="BG18" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="BH18" t="s">
         <v>131</v>
@@ -6046,7 +6057,7 @@
         <v>131</v>
       </c>
       <c r="CA18" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="CB18">
         <v>56</v>
@@ -6064,7 +6075,7 @@
         <v>4.09</v>
       </c>
       <c r="CG18" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="CH18" t="s">
         <v>131</v>
@@ -6121,10 +6132,10 @@
         <v>71</v>
       </c>
       <c r="EH18" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="EI18" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="EJ18" t="s">
         <v>131</v>
@@ -6132,16 +6143,16 @@
     </row>
     <row r="19" spans="1:140" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B19" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C19" s="16">
         <v>2023</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -6150,22 +6161,22 @@
         <v>143</v>
       </c>
       <c r="G19" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H19" t="s">
         <v>127</v>
       </c>
       <c r="I19" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="K19" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="L19">
         <v>34</v>
       </c>
       <c r="M19" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="N19">
         <v>18</v>
@@ -6174,31 +6185,31 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="P19" s="16" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="U19" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="V19" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="W19" t="s">
         <v>127</v>
       </c>
       <c r="X19" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="Y19" t="s">
         <v>127</v>
       </c>
       <c r="Z19" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="AA19" t="s">
         <v>127</v>
       </c>
       <c r="AB19" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="DB19">
         <v>16</v>
@@ -6243,10 +6254,10 @@
         <v>34</v>
       </c>
       <c r="EH19" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="EI19" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="EJ19" t="s">
         <v>131</v>
@@ -6254,16 +6265,16 @@
     </row>
     <row r="20" spans="1:140" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B20" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C20" s="16">
         <v>2023</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -6275,19 +6286,19 @@
         <v>126</v>
       </c>
       <c r="H20" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="I20" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="K20" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="L20">
         <v>35</v>
       </c>
       <c r="M20" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="N20">
         <v>14</v>
@@ -6296,31 +6307,31 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="P20" s="16" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="U20" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="V20" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="W20" t="s">
         <v>127</v>
       </c>
       <c r="X20" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="Y20" t="s">
         <v>127</v>
       </c>
       <c r="Z20" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AA20" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AB20" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="DB20">
         <v>34</v>
@@ -6368,7 +6379,7 @@
         <v>137</v>
       </c>
       <c r="EI20" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="EJ20" t="s">
         <v>131</v>
@@ -6376,16 +6387,16 @@
     </row>
     <row r="21" spans="1:140" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B21" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C21" s="16">
         <v>2023</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -6394,22 +6405,22 @@
         <v>143</v>
       </c>
       <c r="G21" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="H21" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="I21" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="K21" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="L21">
         <v>36</v>
       </c>
       <c r="M21" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="N21">
         <v>13</v>
@@ -6418,31 +6429,31 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="P21" s="16" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="U21" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="V21" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="W21" t="s">
         <v>127</v>
       </c>
       <c r="X21" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="Y21" t="s">
         <v>127</v>
       </c>
       <c r="Z21" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="AA21" t="s">
         <v>127</v>
       </c>
       <c r="AB21" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="DB21">
         <v>15</v>
@@ -6487,10 +6498,10 @@
         <v>36</v>
       </c>
       <c r="EH21" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="EI21" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="EJ21" t="s">
         <v>131</v>
@@ -6498,43 +6509,43 @@
     </row>
     <row r="22" spans="1:140" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B22" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C22" s="16">
         <v>2023</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="G22" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H22" t="s">
         <v>127</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="J22" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="K22" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="L22">
         <v>68</v>
       </c>
       <c r="M22" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="N22">
         <v>15</v>
@@ -6543,25 +6554,25 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="P22" s="16" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="W22" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="X22" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="Y22" t="s">
         <v>127</v>
       </c>
       <c r="Z22" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="AA22" t="s">
         <v>127</v>
       </c>
       <c r="AB22" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="DB22">
         <v>2</v>
@@ -6594,10 +6605,10 @@
         <v>59</v>
       </c>
       <c r="EH22" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="EI22" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="EJ22" t="s">
         <v>131</v>
@@ -6605,43 +6616,43 @@
     </row>
     <row r="23" spans="1:140" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B23" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C23" s="16">
         <v>2023</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="E23">
         <v>1</v>
       </c>
       <c r="F23" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="G23" t="s">
         <v>126</v>
       </c>
       <c r="H23" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="J23" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="K23" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="L23">
         <v>68</v>
       </c>
       <c r="M23" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="N23">
         <v>15</v>
@@ -6650,31 +6661,31 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="P23" s="16" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="U23" t="s">
         <v>127</v>
       </c>
       <c r="V23" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="W23" t="s">
         <v>127</v>
       </c>
       <c r="X23" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="Y23" t="s">
         <v>127</v>
       </c>
       <c r="Z23" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="AA23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AB23" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="DB23">
         <v>32</v>
@@ -6710,7 +6721,7 @@
         <v>137</v>
       </c>
       <c r="EI23" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="EJ23" t="s">
         <v>131</v>
@@ -6718,40 +6729,40 @@
     </row>
     <row r="24" spans="1:140" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B24" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C24" s="16">
         <v>2021</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="G24" t="s">
         <v>126</v>
       </c>
       <c r="H24" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I24" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="K24" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="L24">
         <v>12</v>
       </c>
       <c r="M24" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="N24">
         <v>0</v>
@@ -6760,7 +6771,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="P24" s="16" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="U24" t="s">
         <v>127</v>
@@ -6820,7 +6831,7 @@
         <v>137</v>
       </c>
       <c r="EI24" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="EJ24" t="s">
         <v>131</v>
@@ -6828,40 +6839,40 @@
     </row>
     <row r="25" spans="1:140" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B25" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C25" s="16">
         <v>2021</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="E25">
         <v>1</v>
       </c>
       <c r="F25" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="G25" t="s">
         <v>126</v>
       </c>
       <c r="H25" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="I25" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="K25" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="L25">
         <v>12</v>
       </c>
       <c r="M25" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="N25">
         <v>0</v>
@@ -6870,7 +6881,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="P25" s="16" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="U25" t="s">
         <v>127</v>
@@ -6930,7 +6941,7 @@
         <v>137</v>
       </c>
       <c r="EI25" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="EJ25" t="s">
         <v>131</v>
@@ -6938,40 +6949,40 @@
     </row>
     <row r="26" spans="1:140" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B26" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C26" s="16">
         <v>2021</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="G26" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H26" t="s">
         <v>127</v>
       </c>
       <c r="I26" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="K26" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="L26">
         <v>24</v>
       </c>
       <c r="M26" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="N26">
         <v>0</v>
@@ -6980,31 +6991,31 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="P26" s="16" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="U26" t="s">
         <v>127</v>
       </c>
       <c r="V26" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="W26" t="s">
         <v>127</v>
       </c>
       <c r="X26" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="Y26" t="s">
         <v>127</v>
       </c>
       <c r="Z26" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="AA26" t="s">
         <v>127</v>
       </c>
       <c r="AB26" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="DB26">
         <v>1</v>
@@ -7037,10 +7048,10 @@
         <v>24</v>
       </c>
       <c r="EH26" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="EI26" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="EJ26" t="s">
         <v>131</v>
@@ -7048,40 +7059,40 @@
     </row>
     <row r="27" spans="1:140" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B27" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C27" s="16">
         <v>2023</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E27">
         <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="G27" t="s">
         <v>126</v>
       </c>
       <c r="H27" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="I27" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="K27" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L27">
         <v>16</v>
       </c>
       <c r="M27" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="N27">
         <v>12</v>
@@ -7090,19 +7101,19 @@
         <v>2</v>
       </c>
       <c r="P27" s="16" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="Y27" t="s">
         <v>127</v>
       </c>
       <c r="Z27" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AA27" t="s">
         <v>127</v>
       </c>
       <c r="AB27" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="DB27" s="6">
         <v>6</v>
@@ -7114,7 +7125,7 @@
         <v>137</v>
       </c>
       <c r="EI27" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="EJ27" t="s">
         <v>131</v>
@@ -7122,22 +7133,22 @@
     </row>
     <row r="28" spans="1:140" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B28" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C28" s="16">
         <v>2023</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E28">
         <v>0</v>
       </c>
       <c r="F28" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="G28" t="s">
         <v>126</v>
@@ -7146,16 +7157,16 @@
         <v>140</v>
       </c>
       <c r="I28" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="K28" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L28">
         <v>16</v>
       </c>
       <c r="M28" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="N28">
         <v>12</v>
@@ -7164,19 +7175,19 @@
         <v>2</v>
       </c>
       <c r="P28" s="16" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="Y28" t="s">
         <v>127</v>
       </c>
       <c r="Z28" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AA28" t="s">
         <v>127</v>
       </c>
       <c r="AB28" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="DB28" s="6">
         <v>1</v>
@@ -7188,7 +7199,7 @@
         <v>137</v>
       </c>
       <c r="EI28" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="EJ28" t="s">
         <v>131</v>
@@ -7196,40 +7207,40 @@
     </row>
     <row r="29" spans="1:140" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B29" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C29" s="16">
         <v>2023</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E29">
         <v>1</v>
       </c>
       <c r="F29" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="G29" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H29" t="s">
         <v>127</v>
       </c>
       <c r="I29" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="K29" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L29">
         <v>16</v>
       </c>
       <c r="M29" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="N29">
         <v>12</v>
@@ -7238,19 +7249,19 @@
         <v>2</v>
       </c>
       <c r="P29" s="16" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="Y29" t="s">
         <v>127</v>
       </c>
       <c r="Z29" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AA29" t="s">
         <v>127</v>
       </c>
       <c r="AB29" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="DB29" s="6">
         <v>2</v>
@@ -7259,10 +7270,10 @@
         <v>14</v>
       </c>
       <c r="EH29" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="EI29" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="EJ29" t="s">
         <v>131</v>
@@ -7273,7 +7284,7 @@
         <v>126</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C30" s="16">
         <v>2024</v>
@@ -7288,13 +7299,13 @@
         <v>126</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="K30" s="11">
         <v>303</v>
@@ -7312,10 +7323,10 @@
         <v>52</v>
       </c>
       <c r="P30" s="16" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="S30" s="8">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="T30" s="10">
         <v>201</v>
@@ -7345,22 +7356,22 @@
         <v>201</v>
       </c>
       <c r="AC30" s="11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AD30" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="AE30" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="AE30" s="8" t="s">
         <v>155</v>
       </c>
       <c r="AF30" s="11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AG30" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="AH30" s="19" t="s">
-        <v>155</v>
+        <v>153</v>
+      </c>
+      <c r="AH30" s="8" t="s">
+        <v>153</v>
       </c>
       <c r="AI30" s="8" t="s">
         <v>128</v>
@@ -7432,10 +7443,10 @@
         <v>129</v>
       </c>
       <c r="CZ30" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="DA30" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="DB30" s="8">
         <v>153</v>
@@ -7450,7 +7461,7 @@
         <v>201</v>
       </c>
       <c r="DF30" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DG30" s="11">
         <v>201</v>
@@ -7498,7 +7509,7 @@
         <v>201</v>
       </c>
       <c r="EF30" s="8">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="EG30" s="8">
         <v>201</v>
@@ -7507,7 +7518,7 @@
         <v>137</v>
       </c>
       <c r="EI30" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="EJ30" t="s">
         <v>131</v>
@@ -7515,10 +7526,10 @@
     </row>
     <row r="31" spans="1:140" x14ac:dyDescent="0.2">
       <c r="A31" s="10" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C31" s="16">
         <v>2024</v>
@@ -7530,16 +7541,16 @@
         <v>143</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="K31" s="11">
         <v>303</v>
@@ -7557,10 +7568,10 @@
         <v>52</v>
       </c>
       <c r="P31" s="16" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="S31" s="8">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="T31" s="10">
         <v>102</v>
@@ -7590,22 +7601,22 @@
         <v>102</v>
       </c>
       <c r="AC31" s="11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AD31" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="AE31" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="AE31" s="8" t="s">
         <v>155</v>
       </c>
       <c r="AF31" s="11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AG31" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="AH31" s="19" t="s">
-        <v>155</v>
+        <v>153</v>
+      </c>
+      <c r="AH31" s="8" t="s">
+        <v>153</v>
       </c>
       <c r="AI31" s="8" t="s">
         <v>128</v>
@@ -7677,10 +7688,10 @@
         <v>129</v>
       </c>
       <c r="CZ31" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="DA31" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="DB31" s="8">
         <v>77</v>
@@ -7749,10 +7760,10 @@
         <v>102</v>
       </c>
       <c r="EH31" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="EI31" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="EJ31" t="s">
         <v>131</v>
@@ -7760,10 +7771,10 @@
     </row>
     <row r="32" spans="1:140" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C32" s="16">
         <v>2024</v>
@@ -7775,16 +7786,16 @@
         <v>143</v>
       </c>
       <c r="G32" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="H32">
         <v>150</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="K32" s="9">
         <v>27</v>
@@ -7802,7 +7813,7 @@
         <v>12</v>
       </c>
       <c r="P32" s="16" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="Q32" s="11">
         <v>0</v>
@@ -7841,22 +7852,22 @@
         <v>12</v>
       </c>
       <c r="AC32" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AD32" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AE32" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="AD32" s="12" t="s">
+      <c r="AF32" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AG32" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AH32" s="12" t="s">
         <v>154</v>
-      </c>
-      <c r="AE32" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="AF32" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="AG32" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="AH32" s="12" t="s">
-        <v>155</v>
       </c>
       <c r="AI32" s="11" t="s">
         <v>128</v>
@@ -7877,7 +7888,7 @@
         <v>6.27</v>
       </c>
       <c r="AO32" s="11" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AP32" s="11" t="s">
         <v>131</v>
@@ -7904,7 +7915,7 @@
         <v>3.61</v>
       </c>
       <c r="AX32" s="11" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AY32" s="11" t="s">
         <v>131</v>
@@ -7913,7 +7924,7 @@
         <v>131</v>
       </c>
       <c r="BA32" s="11" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="BB32" s="11">
         <v>6</v>
@@ -7931,7 +7942,7 @@
         <v>20.440000000000001</v>
       </c>
       <c r="BG32" s="11" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="BH32" s="11" t="s">
         <v>131</v>
@@ -7991,7 +8002,7 @@
         <v>137</v>
       </c>
       <c r="EI32" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="EJ32" t="s">
         <v>131</v>
@@ -7999,10 +8010,10 @@
     </row>
     <row r="33" spans="1:140" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C33" s="16">
         <v>2024</v>
@@ -8014,16 +8025,16 @@
         <v>143</v>
       </c>
       <c r="G33" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H33">
         <v>0</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="K33" s="9">
         <v>27</v>
@@ -8041,7 +8052,7 @@
         <v>12</v>
       </c>
       <c r="P33" s="16" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="Q33" s="11">
         <v>1</v>
@@ -8080,22 +8091,22 @@
         <v>15</v>
       </c>
       <c r="AC33" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AD33" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AE33" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="AD33" s="12" t="s">
+      <c r="AF33" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AG33" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AH33" s="12" t="s">
         <v>154</v>
-      </c>
-      <c r="AE33" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="AF33" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="AG33" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="AH33" s="12" t="s">
-        <v>155</v>
       </c>
       <c r="AI33" s="11" t="s">
         <v>128</v>
@@ -8116,7 +8127,7 @@
         <v>13.92</v>
       </c>
       <c r="AO33" s="11" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AP33" s="11" t="s">
         <v>131</v>
@@ -8143,7 +8154,7 @@
         <v>5.25</v>
       </c>
       <c r="AX33" s="11" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AY33" s="11" t="s">
         <v>131</v>
@@ -8152,7 +8163,7 @@
         <v>131</v>
       </c>
       <c r="BA33" s="11" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="BB33" s="11">
         <v>10</v>
@@ -8170,7 +8181,7 @@
         <v>12.86</v>
       </c>
       <c r="BG33" s="11" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="BH33" s="11" t="s">
         <v>131</v>
@@ -8227,10 +8238,10 @@
         <v>15</v>
       </c>
       <c r="EH33" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="EI33" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="EJ33" t="s">
         <v>131</v>
@@ -8238,10 +8249,10 @@
     </row>
     <row r="34" spans="1:140" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C34" s="16">
         <v>2024</v>
@@ -8253,16 +8264,16 @@
         <v>143</v>
       </c>
       <c r="G34" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="H34" s="9">
         <v>45</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="K34" s="9">
         <v>104</v>
@@ -8280,7 +8291,7 @@
         <v>12</v>
       </c>
       <c r="P34" s="16" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="Q34" s="11">
         <v>0</v>
@@ -8319,22 +8330,22 @@
         <v>5</v>
       </c>
       <c r="AC34" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AD34" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AE34" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="AD34" s="12" t="s">
+      <c r="AF34" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AG34" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AH34" s="12" t="s">
         <v>154</v>
-      </c>
-      <c r="AE34" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="AF34" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="AG34" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="AH34" s="12" t="s">
-        <v>155</v>
       </c>
       <c r="AI34" s="11" t="s">
         <v>128</v>
@@ -8355,7 +8366,7 @@
         <v>7.2</v>
       </c>
       <c r="AO34" s="11" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AP34" s="11" t="s">
         <v>131</v>
@@ -8382,7 +8393,7 @@
         <v>2.6</v>
       </c>
       <c r="AX34" s="11" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AY34" s="11" t="s">
         <v>131</v>
@@ -8391,7 +8402,7 @@
         <v>131</v>
       </c>
       <c r="BA34" s="11" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="BB34" s="11">
         <v>4</v>
@@ -8409,7 +8420,7 @@
         <v>10.6</v>
       </c>
       <c r="BG34" s="11" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="BH34" s="11" t="s">
         <v>131</v>
@@ -8466,10 +8477,10 @@
         <v>5</v>
       </c>
       <c r="EH34" s="13" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="EI34" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="EJ34" t="s">
         <v>131</v>
@@ -8477,10 +8488,10 @@
     </row>
     <row r="35" spans="1:140" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C35" s="16">
         <v>2024</v>
@@ -8492,16 +8503,16 @@
         <v>143</v>
       </c>
       <c r="G35" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="H35" s="9">
         <v>150</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="K35" s="9">
         <v>104</v>
@@ -8519,7 +8530,7 @@
         <v>12</v>
       </c>
       <c r="P35" s="16" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="Q35" s="11">
         <v>4</v>
@@ -8558,22 +8569,22 @@
         <v>30</v>
       </c>
       <c r="AC35" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AD35" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AE35" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="AD35" s="12" t="s">
+      <c r="AF35" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AG35" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AH35" s="12" t="s">
         <v>154</v>
-      </c>
-      <c r="AE35" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="AF35" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="AG35" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="AH35" s="12" t="s">
-        <v>155</v>
       </c>
       <c r="AI35" s="11" t="s">
         <v>128</v>
@@ -8594,7 +8605,7 @@
         <v>11.1</v>
       </c>
       <c r="AO35" s="11" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AP35" s="11" t="s">
         <v>131</v>
@@ -8621,7 +8632,7 @@
         <v>4.7</v>
       </c>
       <c r="AX35" s="11" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AY35" s="11" t="s">
         <v>131</v>
@@ -8630,7 +8641,7 @@
         <v>131</v>
       </c>
       <c r="BA35" s="11" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="BB35" s="11">
         <v>19</v>
@@ -8648,7 +8659,7 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="BG35" s="11" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="BH35" s="11" t="s">
         <v>131</v>
@@ -8705,10 +8716,10 @@
         <v>30</v>
       </c>
       <c r="EH35" s="13" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="EI35" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="EJ35" t="s">
         <v>131</v>
@@ -8716,10 +8727,10 @@
     </row>
     <row r="36" spans="1:140" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C36" s="16">
         <v>2024</v>
@@ -8731,16 +8742,16 @@
         <v>143</v>
       </c>
       <c r="G36" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="H36" s="9">
         <v>300</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="J36" s="9" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="K36" s="9">
         <v>104</v>
@@ -8758,7 +8769,7 @@
         <v>12</v>
       </c>
       <c r="P36" s="16" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="Q36" s="11">
         <v>3</v>
@@ -8797,22 +8808,22 @@
         <v>32</v>
       </c>
       <c r="AC36" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AD36" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AE36" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="AD36" s="12" t="s">
+      <c r="AF36" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AG36" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AH36" s="12" t="s">
         <v>154</v>
-      </c>
-      <c r="AE36" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="AF36" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="AG36" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="AH36" s="12" t="s">
-        <v>155</v>
       </c>
       <c r="AI36" s="11" t="s">
         <v>128</v>
@@ -8833,7 +8844,7 @@
         <v>11.3</v>
       </c>
       <c r="AO36" s="11" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AP36" s="11" t="s">
         <v>131</v>
@@ -8860,7 +8871,7 @@
         <v>4.3</v>
       </c>
       <c r="AX36" s="11" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AY36" s="11" t="s">
         <v>131</v>
@@ -8869,7 +8880,7 @@
         <v>131</v>
       </c>
       <c r="BA36" s="11" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="BB36" s="11">
         <v>21</v>
@@ -8887,7 +8898,7 @@
         <v>12.4</v>
       </c>
       <c r="BG36" s="11" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="BH36" s="11" t="s">
         <v>131</v>
@@ -8944,10 +8955,10 @@
         <v>32</v>
       </c>
       <c r="EH36" s="13" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="EI36" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="EJ36" t="s">
         <v>131</v>
@@ -8955,10 +8966,10 @@
     </row>
     <row r="37" spans="1:140" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C37" s="16">
         <v>2024</v>
@@ -8970,16 +8981,16 @@
         <v>143</v>
       </c>
       <c r="G37" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="H37" s="9">
         <v>0</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="K37" s="9">
         <v>104</v>
@@ -8997,7 +9008,7 @@
         <v>12</v>
       </c>
       <c r="P37" s="16" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="Q37" s="11">
         <v>4</v>
@@ -9036,22 +9047,22 @@
         <v>37</v>
       </c>
       <c r="AC37" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AD37" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AE37" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="AD37" s="12" t="s">
+      <c r="AF37" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AG37" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AH37" s="12" t="s">
         <v>154</v>
-      </c>
-      <c r="AE37" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="AF37" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="AG37" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="AH37" s="12" t="s">
-        <v>155</v>
       </c>
       <c r="AI37" s="11" t="s">
         <v>128</v>
@@ -9072,7 +9083,7 @@
         <v>12.2</v>
       </c>
       <c r="AO37" s="11" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AP37" s="11" t="s">
         <v>131</v>
@@ -9099,7 +9110,7 @@
         <v>4.5</v>
       </c>
       <c r="AX37" s="11" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AY37" s="11" t="s">
         <v>131</v>
@@ -9108,7 +9119,7 @@
         <v>131</v>
       </c>
       <c r="BA37" s="11" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="BB37" s="11">
         <v>31</v>
@@ -9126,7 +9137,7 @@
         <v>13.4</v>
       </c>
       <c r="BG37" s="11" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="BH37" s="11" t="s">
         <v>131</v>
@@ -9183,10 +9194,10 @@
         <v>37</v>
       </c>
       <c r="EH37" s="13" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="EI37" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="EJ37" t="s">
         <v>131</v>
@@ -9197,19 +9208,19 @@
         <v>126</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C38" s="16">
         <v>2024</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="E38" s="10">
         <v>1</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="G38" s="10" t="s">
         <v>126</v>
@@ -9218,10 +9229,10 @@
         <v>150</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="K38" s="11">
         <v>31</v>
@@ -9239,7 +9250,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="P38" s="16" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="Y38" s="11">
         <v>0</v>
@@ -9287,7 +9298,7 @@
         <v>137</v>
       </c>
       <c r="EI38" s="11" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="EJ38" s="11" t="s">
         <v>131</v>
@@ -9295,31 +9306,31 @@
     </row>
     <row r="39" spans="1:140" x14ac:dyDescent="0.2">
       <c r="A39" s="11" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C39" s="16">
         <v>2024</v>
       </c>
       <c r="D39" s="17" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="E39" s="10">
         <v>1</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="K39" s="11">
         <v>31</v>
@@ -9337,7 +9348,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="P39" s="16" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="Y39" s="11">
         <v>0</v>
@@ -9382,10 +9393,10 @@
         <v>26</v>
       </c>
       <c r="EH39" s="14" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="EI39" s="11" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="EJ39" s="11" t="s">
         <v>131</v>

--- a/data_u1/LSR3_H_2025-08-15.xlsx
+++ b/data_u1/LSR3_H_2025-08-15.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sksiafis/Documents/GitHub/LSR3_taar1_H/data_u1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBBD1E01-6C57-854E-8F18-08FB54809119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8B53B3F-F7F4-B048-A292-946683B3F244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16680" yWindow="-21100" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22980" yWindow="-15600" windowWidth="28800" windowHeight="16340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1012,7 +1012,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1073,6 +1073,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1087,7 +1093,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1113,6 +1119,7 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3302,8 +3309,8 @@
       <c r="BI6" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="DB6" s="8">
-        <v>55</v>
+      <c r="DB6" s="19">
+        <v>84</v>
       </c>
       <c r="DC6" s="8">
         <v>144</v>
@@ -3362,8 +3369,8 @@
       <c r="EC6" s="8">
         <v>144</v>
       </c>
-      <c r="EF6" s="8">
-        <v>16</v>
+      <c r="EF6" s="19">
+        <v>20</v>
       </c>
       <c r="EG6" s="8">
         <v>144</v>
@@ -3553,8 +3560,8 @@
       <c r="BI7" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="DB7" s="8">
-        <v>50</v>
+      <c r="DB7" s="19">
+        <v>82</v>
       </c>
       <c r="DC7" s="8">
         <v>145</v>
@@ -3613,8 +3620,8 @@
       <c r="EC7" s="8">
         <v>145</v>
       </c>
-      <c r="EF7" s="8">
-        <v>13</v>
+      <c r="EF7" s="19">
+        <v>18</v>
       </c>
       <c r="EG7" s="8">
         <v>145</v>
@@ -3699,7 +3706,7 @@
       <c r="Z8" s="8">
         <v>146</v>
       </c>
-      <c r="AA8" s="8">
+      <c r="AA8" s="19">
         <v>4</v>
       </c>
       <c r="AB8" s="8">
@@ -3804,8 +3811,8 @@
       <c r="BI8" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="DB8" s="8">
-        <v>41</v>
+      <c r="DB8" s="19">
+        <v>71</v>
       </c>
       <c r="DC8" s="8">
         <v>146</v>
@@ -3864,8 +3871,8 @@
       <c r="EC8" s="8">
         <v>146</v>
       </c>
-      <c r="EF8" s="8">
-        <v>4</v>
+      <c r="EF8" s="19">
+        <v>6</v>
       </c>
       <c r="EG8" s="8">
         <v>146</v>
@@ -4577,8 +4584,8 @@
       <c r="BI12" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="DB12" s="8">
-        <v>53</v>
+      <c r="DB12" s="19">
+        <v>92</v>
       </c>
       <c r="DC12" s="8">
         <v>155</v>
@@ -4619,8 +4626,8 @@
       <c r="EC12" s="8">
         <v>155</v>
       </c>
-      <c r="EF12" s="8">
-        <v>11</v>
+      <c r="EF12" s="19">
+        <v>20</v>
       </c>
       <c r="EG12" s="8">
         <v>155</v>
@@ -4810,8 +4817,8 @@
       <c r="BI13" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="DB13" s="8">
-        <v>52</v>
+      <c r="DB13" s="19">
+        <v>84</v>
       </c>
       <c r="DC13" s="8">
         <v>154</v>
@@ -4852,8 +4859,8 @@
       <c r="EC13" s="8">
         <v>154</v>
       </c>
-      <c r="EF13" s="8">
-        <v>13</v>
+      <c r="EF13" s="19">
+        <v>17</v>
       </c>
       <c r="EG13" s="8">
         <v>154</v>
@@ -5043,8 +5050,8 @@
       <c r="BI14" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="DB14" s="8">
-        <v>36</v>
+      <c r="DB14" s="19">
+        <v>69</v>
       </c>
       <c r="DC14" s="8">
         <v>155</v>
@@ -5085,8 +5092,8 @@
       <c r="EC14" s="8">
         <v>155</v>
       </c>
-      <c r="EF14" s="8">
-        <v>7</v>
+      <c r="EF14" s="19">
+        <v>9</v>
       </c>
       <c r="EG14" s="8">
         <v>155</v>
@@ -5865,8 +5872,8 @@
       <c r="EE17">
         <v>68</v>
       </c>
-      <c r="EF17" s="8">
-        <v>0</v>
+      <c r="EF17" s="19">
+        <v>1</v>
       </c>
       <c r="EG17" s="8">
         <v>68</v>

--- a/data_u1/LSR3_H_2025-08-15.xlsx
+++ b/data_u1/LSR3_H_2025-08-15.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sksiafis/Documents/GitHub/LSR3_taar1_H/data_u1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8B53B3F-F7F4-B048-A292-946683B3F244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69C3CF42-C0B8-BB4B-A82D-5853B15101A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22980" yWindow="-15600" windowWidth="28800" windowHeight="16340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16680" yWindow="-21100" windowWidth="38400" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -103,8 +104,80 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={2ED00687-A945-F748-BE19-CAC328235461}</author>
+    <author>tc={9BF3605B-1293-E74A-A5A5-1FE39E4EE934}</author>
+    <author>tc={22DDF7DD-9209-2244-B5E6-2E2DBEEED244}</author>
+    <author>tc={9AC019B0-83B3-D04A-89A8-E922FD3E7AFF}</author>
+    <author>tc={69D4819B-C601-2B49-B55C-222370BE27F7}</author>
+    <author>tc={D2D7C195-D23D-8446-BE73-FA10F0B26E48}</author>
+    <author>tc={1B7A76EB-EC22-2E44-A101-FD13C045DBDA}</author>
+  </authors>
+  <commentList>
+    <comment ref="EF3" authorId="0" shapeId="0" xr:uid="{2ED00687-A945-F748-BE19-CAC328235461}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    hallucinations</t>
+      </text>
+    </comment>
+    <comment ref="BA4" authorId="1" shapeId="0" xr:uid="{9BF3605B-1293-E74A-A5A5-1FE39E4EE934}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Changed from first version because BNSS total has been recently been show that has a better validity compared to PANSS negative (Weigel et al)</t>
+      </text>
+    </comment>
+    <comment ref="DD6" authorId="2" shapeId="0" xr:uid="{22DDF7DD-9209-2244-B5E6-2E2DBEEED244}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    dry mouth, constipation, dry eye</t>
+      </text>
+    </comment>
+    <comment ref="S30" authorId="3" shapeId="0" xr:uid="{9AC019B0-83B3-D04A-89A8-E922FD3E7AFF}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    imputed as PANSS+12</t>
+      </text>
+    </comment>
+    <comment ref="EF30" authorId="4" shapeId="0" xr:uid="{69D4819B-C601-2B49-B55C-222370BE27F7}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    poster: both SAE and non-SAE</t>
+      </text>
+    </comment>
+    <comment ref="Q32" authorId="5" shapeId="0" xr:uid="{D2D7C195-D23D-8446-BE73-FA10F0B26E48}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Imputed from panss total</t>
+      </text>
+    </comment>
+    <comment ref="S32" authorId="6" shapeId="0" xr:uid="{1B7A76EB-EC22-2E44-A101-FD13C045DBDA}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    same as imputed from PANSS total </t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1201" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2402" uniqueCount="288">
   <si>
     <t>arm_name</t>
   </si>
@@ -974,7 +1047,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1010,6 +1083,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="12">
@@ -1455,6 +1534,32 @@
 </ThreadedComments>
 </file>
 
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="EF3" dT="2025-08-16T12:39:23.35" personId="{9C02175C-AB95-C54D-8A67-708063150B15}" id="{2ED00687-A945-F748-BE19-CAC328235461}">
+    <text>hallucinations</text>
+  </threadedComment>
+  <threadedComment ref="BA4" dT="2025-01-16T13:52:36.05" personId="{9C02175C-AB95-C54D-8A67-708063150B15}" id="{9BF3605B-1293-E74A-A5A5-1FE39E4EE934}">
+    <text>Changed from first version because BNSS total has been recently been show that has a better validity compared to PANSS negative (Weigel et al)</text>
+  </threadedComment>
+  <threadedComment ref="DD6" dT="2025-08-15T21:16:55.84" personId="{9C02175C-AB95-C54D-8A67-708063150B15}" id="{22DDF7DD-9209-2244-B5E6-2E2DBEEED244}">
+    <text>dry mouth, constipation, dry eye</text>
+  </threadedComment>
+  <threadedComment ref="S30" dT="2025-08-18T07:46:21.71" personId="{9C02175C-AB95-C54D-8A67-708063150B15}" id="{9AC019B0-83B3-D04A-89A8-E922FD3E7AFF}">
+    <text>imputed as PANSS+12</text>
+  </threadedComment>
+  <threadedComment ref="EF30" dT="2025-08-18T08:35:15.00" personId="{9C02175C-AB95-C54D-8A67-708063150B15}" id="{69D4819B-C601-2B49-B55C-222370BE27F7}">
+    <text>poster: both SAE and non-SAE</text>
+  </threadedComment>
+  <threadedComment ref="Q32" dT="2025-01-16T13:52:04.57" personId="{9C02175C-AB95-C54D-8A67-708063150B15}" id="{D2D7C195-D23D-8446-BE73-FA10F0B26E48}">
+    <text>Imputed from panss total</text>
+  </threadedComment>
+  <threadedComment ref="S32" dT="2025-08-18T08:01:58.59" personId="{9C02175C-AB95-C54D-8A67-708063150B15}" id="{1B7A76EB-EC22-2E44-A101-FD13C045DBDA}">
+    <text xml:space="preserve">same as imputed from PANSS total </text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:EJ39"/>
@@ -9426,4 +9531,8283 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId12"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94A32EE2-F112-2F4A-AAFF-ECAC5A3AD159}">
+  <dimension ref="A1:EJ39"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:140" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>261</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="P1" s="15" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AK1" s="15" t="s">
+        <v>265</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AT1" s="15" t="s">
+        <v>273</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="BC1" s="15" t="s">
+        <v>274</v>
+      </c>
+      <c r="BD1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BN1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BO1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BP1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BQ1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BR1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BS1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="BT1" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="BU1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="BV1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="BW1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="BX1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="BY1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="BZ1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="CA1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="CB1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="CC1" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="CD1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="CE1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="CF1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="CG1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="CH1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="CI1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="CJ1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="CK1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="CL1" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="CM1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="CN1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="CO1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="CP1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="CQ1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="CR1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="CS1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="CT1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="CU1" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="CV1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="CW1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="CX1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="CY1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="CZ1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="DA1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="DB1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="DC1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="DD1" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="DE1" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="DF1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="DG1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="DH1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="DI1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="DJ1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="DK1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="DL1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="DM1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="DN1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="DO1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="DP1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="DQ1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="DR1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="DS1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="DT1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="DU1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="DV1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="DW1" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="DX1" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="DY1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="DZ1" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="EA1" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="EB1" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="EC1" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="ED1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="EE1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="EF1" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="EG1" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="EH1" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="EI1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="EJ1" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:140" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C2" s="16">
+        <v>2023</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>262</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I2" t="s">
+        <v>145</v>
+      </c>
+      <c r="J2" t="s">
+        <v>146</v>
+      </c>
+      <c r="K2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L2">
+        <v>25</v>
+      </c>
+      <c r="M2" s="8">
+        <v>70.400000000000006</v>
+      </c>
+      <c r="N2">
+        <v>4</v>
+      </c>
+      <c r="O2">
+        <v>6</v>
+      </c>
+      <c r="P2" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>148</v>
+      </c>
+      <c r="R2" t="s">
+        <v>149</v>
+      </c>
+      <c r="U2" t="s">
+        <v>150</v>
+      </c>
+      <c r="V2" t="s">
+        <v>140</v>
+      </c>
+      <c r="W2" t="s">
+        <v>151</v>
+      </c>
+      <c r="X2" t="s">
+        <v>140</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>140</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>152</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>140</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>153</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>153</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>154</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>153</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>153</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>154</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>156</v>
+      </c>
+      <c r="AJ2">
+        <v>23</v>
+      </c>
+      <c r="AK2" s="16"/>
+      <c r="AM2">
+        <v>-11.5</v>
+      </c>
+      <c r="AN2">
+        <v>20.12</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>129</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>130</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>131</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>157</v>
+      </c>
+      <c r="AS2">
+        <v>24</v>
+      </c>
+      <c r="AT2" s="16">
+        <v>24</v>
+      </c>
+      <c r="AU2">
+        <v>13.1</v>
+      </c>
+      <c r="AV2">
+        <v>-2.5</v>
+      </c>
+      <c r="AW2">
+        <v>7.94</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>129</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>130</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>131</v>
+      </c>
+      <c r="BC2" s="16"/>
+      <c r="BR2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BS2">
+        <v>23</v>
+      </c>
+      <c r="BT2" s="16">
+        <v>24</v>
+      </c>
+      <c r="BU2">
+        <v>-25.1</v>
+      </c>
+      <c r="BV2">
+        <v>0.8</v>
+      </c>
+      <c r="BW2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="BX2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BY2" t="s">
+        <v>130</v>
+      </c>
+      <c r="BZ2" t="s">
+        <v>131</v>
+      </c>
+      <c r="CC2" s="16"/>
+      <c r="CL2" s="16"/>
+      <c r="CU2" s="16"/>
+      <c r="DB2">
+        <v>18</v>
+      </c>
+      <c r="DC2">
+        <v>25</v>
+      </c>
+      <c r="DF2" s="9"/>
+      <c r="DG2" s="9"/>
+      <c r="DH2">
+        <v>4</v>
+      </c>
+      <c r="DI2">
+        <v>25</v>
+      </c>
+      <c r="DL2">
+        <v>3</v>
+      </c>
+      <c r="DM2">
+        <v>25</v>
+      </c>
+      <c r="DN2">
+        <v>2</v>
+      </c>
+      <c r="DO2">
+        <v>25</v>
+      </c>
+      <c r="DT2" s="9"/>
+      <c r="DU2" s="9"/>
+      <c r="DV2">
+        <v>13</v>
+      </c>
+      <c r="DW2">
+        <v>25</v>
+      </c>
+      <c r="DX2" s="8">
+        <v>2</v>
+      </c>
+      <c r="DY2" s="8">
+        <v>25</v>
+      </c>
+      <c r="EF2" s="8">
+        <v>6</v>
+      </c>
+      <c r="EG2" s="8">
+        <v>25</v>
+      </c>
+      <c r="EH2" t="s">
+        <v>137</v>
+      </c>
+      <c r="EI2" t="s">
+        <v>159</v>
+      </c>
+      <c r="EJ2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="3" spans="1:140" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C3" s="16">
+        <v>2023</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>262</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>143</v>
+      </c>
+      <c r="G3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H3" t="s">
+        <v>127</v>
+      </c>
+      <c r="I3" t="s">
+        <v>145</v>
+      </c>
+      <c r="J3" t="s">
+        <v>146</v>
+      </c>
+      <c r="K3" t="s">
+        <v>147</v>
+      </c>
+      <c r="L3">
+        <v>14</v>
+      </c>
+      <c r="M3" s="8">
+        <v>71.8</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <v>6</v>
+      </c>
+      <c r="P3" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>161</v>
+      </c>
+      <c r="R3" t="s">
+        <v>141</v>
+      </c>
+      <c r="U3" t="s">
+        <v>161</v>
+      </c>
+      <c r="V3" t="s">
+        <v>162</v>
+      </c>
+      <c r="W3" t="s">
+        <v>163</v>
+      </c>
+      <c r="X3" t="s">
+        <v>162</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>162</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>162</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>153</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>153</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>154</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>153</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>153</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>154</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>156</v>
+      </c>
+      <c r="AJ3">
+        <v>14</v>
+      </c>
+      <c r="AK3" s="16"/>
+      <c r="AM3">
+        <v>-17.3</v>
+      </c>
+      <c r="AN3">
+        <v>19.57</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>129</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>131</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>157</v>
+      </c>
+      <c r="AS3">
+        <v>14</v>
+      </c>
+      <c r="AT3" s="16">
+        <v>14</v>
+      </c>
+      <c r="AU3">
+        <v>14.7</v>
+      </c>
+      <c r="AV3">
+        <v>-1.4</v>
+      </c>
+      <c r="AW3">
+        <v>7.71</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>129</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>131</v>
+      </c>
+      <c r="BC3" s="16"/>
+      <c r="BR3" t="s">
+        <v>158</v>
+      </c>
+      <c r="BS3">
+        <v>14</v>
+      </c>
+      <c r="BT3" s="16">
+        <v>14</v>
+      </c>
+      <c r="BU3">
+        <v>-24.7</v>
+      </c>
+      <c r="BV3">
+        <v>-0.3</v>
+      </c>
+      <c r="BW3">
+        <v>1.99</v>
+      </c>
+      <c r="BX3" t="s">
+        <v>129</v>
+      </c>
+      <c r="BY3" t="s">
+        <v>130</v>
+      </c>
+      <c r="BZ3" t="s">
+        <v>131</v>
+      </c>
+      <c r="CC3" s="16"/>
+      <c r="CL3" s="16"/>
+      <c r="CU3" s="16"/>
+      <c r="DB3">
+        <v>12</v>
+      </c>
+      <c r="DC3">
+        <v>14</v>
+      </c>
+      <c r="DF3">
+        <v>0</v>
+      </c>
+      <c r="DG3">
+        <v>14</v>
+      </c>
+      <c r="DH3">
+        <v>1</v>
+      </c>
+      <c r="DI3">
+        <v>14</v>
+      </c>
+      <c r="DL3">
+        <v>1</v>
+      </c>
+      <c r="DM3">
+        <v>14</v>
+      </c>
+      <c r="DN3">
+        <v>2</v>
+      </c>
+      <c r="DO3">
+        <v>14</v>
+      </c>
+      <c r="DT3">
+        <v>1</v>
+      </c>
+      <c r="DU3">
+        <v>14</v>
+      </c>
+      <c r="DV3">
+        <v>11</v>
+      </c>
+      <c r="DW3">
+        <v>14</v>
+      </c>
+      <c r="DX3">
+        <v>1</v>
+      </c>
+      <c r="DY3">
+        <v>14</v>
+      </c>
+      <c r="EF3" s="8">
+        <v>2</v>
+      </c>
+      <c r="EG3" s="8">
+        <v>14</v>
+      </c>
+      <c r="EH3" t="s">
+        <v>160</v>
+      </c>
+      <c r="EI3" t="s">
+        <v>159</v>
+      </c>
+      <c r="EJ3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="4" spans="1:140" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C4" s="16">
+        <v>2020</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>267</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4" t="s">
+        <v>143</v>
+      </c>
+      <c r="G4" t="s">
+        <v>126</v>
+      </c>
+      <c r="H4" t="s">
+        <v>165</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="J4" t="s">
+        <v>146</v>
+      </c>
+      <c r="K4" t="s">
+        <v>166</v>
+      </c>
+      <c r="L4">
+        <v>120</v>
+      </c>
+      <c r="M4" s="8">
+        <v>30</v>
+      </c>
+      <c r="N4">
+        <v>43</v>
+      </c>
+      <c r="O4">
+        <v>4</v>
+      </c>
+      <c r="P4" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>138</v>
+      </c>
+      <c r="R4" t="s">
+        <v>167</v>
+      </c>
+      <c r="U4" t="s">
+        <v>168</v>
+      </c>
+      <c r="V4" t="s">
+        <v>167</v>
+      </c>
+      <c r="W4" t="s">
+        <v>150</v>
+      </c>
+      <c r="X4" t="s">
+        <v>167</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>163</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>167</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>152</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>167</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>153</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>153</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>155</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>153</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>153</v>
+      </c>
+      <c r="AH4" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ4">
+        <v>120</v>
+      </c>
+      <c r="AK4" s="16">
+        <v>120</v>
+      </c>
+      <c r="AL4">
+        <v>101.4</v>
+      </c>
+      <c r="AM4">
+        <v>-17.2</v>
+      </c>
+      <c r="AN4">
+        <v>18.63</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>129</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>130</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>131</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>132</v>
+      </c>
+      <c r="AS4">
+        <v>120</v>
+      </c>
+      <c r="AT4" s="16">
+        <v>120</v>
+      </c>
+      <c r="AU4">
+        <v>25.8</v>
+      </c>
+      <c r="AV4">
+        <v>-5.5</v>
+      </c>
+      <c r="AW4">
+        <v>5.48</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>129</v>
+      </c>
+      <c r="AY4" t="s">
+        <v>130</v>
+      </c>
+      <c r="AZ4" t="s">
+        <v>131</v>
+      </c>
+      <c r="BA4" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="BB4">
+        <v>120</v>
+      </c>
+      <c r="BC4" s="16">
+        <v>120</v>
+      </c>
+      <c r="BD4" s="9">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="BE4" s="9">
+        <v>-7.1</v>
+      </c>
+      <c r="BF4" s="9">
+        <v>10.95</v>
+      </c>
+      <c r="BG4" t="s">
+        <v>129</v>
+      </c>
+      <c r="BH4" t="s">
+        <v>130</v>
+      </c>
+      <c r="BI4" t="s">
+        <v>131</v>
+      </c>
+      <c r="BT4" s="16"/>
+      <c r="CA4" t="s">
+        <v>134</v>
+      </c>
+      <c r="CB4">
+        <v>120</v>
+      </c>
+      <c r="CC4" s="16">
+        <v>120</v>
+      </c>
+      <c r="CD4">
+        <v>13.1</v>
+      </c>
+      <c r="CE4">
+        <v>-3.3</v>
+      </c>
+      <c r="CF4">
+        <v>6.57</v>
+      </c>
+      <c r="CG4" t="s">
+        <v>129</v>
+      </c>
+      <c r="CH4" t="s">
+        <v>130</v>
+      </c>
+      <c r="CI4" t="s">
+        <v>131</v>
+      </c>
+      <c r="CJ4" t="s">
+        <v>135</v>
+      </c>
+      <c r="CK4">
+        <v>120</v>
+      </c>
+      <c r="CL4" s="16">
+        <v>120</v>
+      </c>
+      <c r="CM4">
+        <v>75.400000000000006</v>
+      </c>
+      <c r="CN4">
+        <v>0.3</v>
+      </c>
+      <c r="CO4">
+        <v>1.9</v>
+      </c>
+      <c r="CP4" t="s">
+        <v>129</v>
+      </c>
+      <c r="CQ4" t="s">
+        <v>130</v>
+      </c>
+      <c r="CR4" t="s">
+        <v>131</v>
+      </c>
+      <c r="CS4" t="s">
+        <v>136</v>
+      </c>
+      <c r="CT4">
+        <v>114</v>
+      </c>
+      <c r="CU4" s="16"/>
+      <c r="CW4">
+        <v>-1.965789473684211</v>
+      </c>
+      <c r="CX4">
+        <v>28</v>
+      </c>
+      <c r="CY4" t="s">
+        <v>129</v>
+      </c>
+      <c r="CZ4" t="s">
+        <v>131</v>
+      </c>
+      <c r="DA4" t="s">
+        <v>130</v>
+      </c>
+      <c r="DB4">
+        <v>55</v>
+      </c>
+      <c r="DC4">
+        <v>120</v>
+      </c>
+      <c r="DF4">
+        <v>2</v>
+      </c>
+      <c r="DG4">
+        <v>120</v>
+      </c>
+      <c r="DJ4">
+        <v>11</v>
+      </c>
+      <c r="DK4">
+        <v>120</v>
+      </c>
+      <c r="DL4">
+        <v>6</v>
+      </c>
+      <c r="DM4">
+        <v>120</v>
+      </c>
+      <c r="DN4">
+        <v>8</v>
+      </c>
+      <c r="DO4">
+        <v>120</v>
+      </c>
+      <c r="DR4">
+        <v>0</v>
+      </c>
+      <c r="DS4">
+        <v>120</v>
+      </c>
+      <c r="DT4">
+        <v>6</v>
+      </c>
+      <c r="DU4">
+        <v>120</v>
+      </c>
+      <c r="DX4">
+        <v>4</v>
+      </c>
+      <c r="DY4">
+        <v>120</v>
+      </c>
+      <c r="DZ4">
+        <v>1</v>
+      </c>
+      <c r="EA4">
+        <v>120</v>
+      </c>
+      <c r="EB4">
+        <v>4</v>
+      </c>
+      <c r="EC4">
+        <v>120</v>
+      </c>
+      <c r="ED4">
+        <v>1</v>
+      </c>
+      <c r="EE4">
+        <v>120</v>
+      </c>
+      <c r="EF4" s="8">
+        <v>7</v>
+      </c>
+      <c r="EG4" s="8">
+        <v>120</v>
+      </c>
+      <c r="EH4" t="s">
+        <v>137</v>
+      </c>
+      <c r="EI4" t="s">
+        <v>159</v>
+      </c>
+      <c r="EJ4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="5" spans="1:140" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>160</v>
+      </c>
+      <c r="B5" t="s">
+        <v>164</v>
+      </c>
+      <c r="C5" s="16">
+        <v>2020</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>267</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>143</v>
+      </c>
+      <c r="G5" t="s">
+        <v>160</v>
+      </c>
+      <c r="H5" t="s">
+        <v>127</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="J5" t="s">
+        <v>146</v>
+      </c>
+      <c r="K5" t="s">
+        <v>166</v>
+      </c>
+      <c r="L5">
+        <v>125</v>
+      </c>
+      <c r="M5" s="8">
+        <v>30.6</v>
+      </c>
+      <c r="N5">
+        <v>46</v>
+      </c>
+      <c r="O5">
+        <v>4</v>
+      </c>
+      <c r="P5" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>169</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="U5" t="s">
+        <v>168</v>
+      </c>
+      <c r="V5" t="s">
+        <v>170</v>
+      </c>
+      <c r="W5" t="s">
+        <v>171</v>
+      </c>
+      <c r="X5" t="s">
+        <v>170</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>170</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>172</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>170</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>153</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>153</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>155</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>153</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>153</v>
+      </c>
+      <c r="AH5" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ5">
+        <v>125</v>
+      </c>
+      <c r="AK5" s="16">
+        <v>125</v>
+      </c>
+      <c r="AL5">
+        <v>99.7</v>
+      </c>
+      <c r="AM5">
+        <v>-9.6999999999999993</v>
+      </c>
+      <c r="AN5">
+        <v>17.89</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>129</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>130</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>131</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>132</v>
+      </c>
+      <c r="AS5">
+        <v>125</v>
+      </c>
+      <c r="AT5" s="16">
+        <v>125</v>
+      </c>
+      <c r="AU5">
+        <v>25.4</v>
+      </c>
+      <c r="AV5">
+        <v>-3.9</v>
+      </c>
+      <c r="AW5">
+        <v>5.59</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>129</v>
+      </c>
+      <c r="AY5" t="s">
+        <v>130</v>
+      </c>
+      <c r="AZ5" t="s">
+        <v>131</v>
+      </c>
+      <c r="BA5" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="BB5">
+        <v>125</v>
+      </c>
+      <c r="BC5" s="16">
+        <v>125</v>
+      </c>
+      <c r="BD5" s="9">
+        <v>37.4</v>
+      </c>
+      <c r="BE5" s="9">
+        <v>-2.7</v>
+      </c>
+      <c r="BF5" s="9">
+        <v>10.06</v>
+      </c>
+      <c r="BG5" t="s">
+        <v>129</v>
+      </c>
+      <c r="BH5" t="s">
+        <v>130</v>
+      </c>
+      <c r="BI5" t="s">
+        <v>131</v>
+      </c>
+      <c r="BT5" s="16"/>
+      <c r="CA5" t="s">
+        <v>134</v>
+      </c>
+      <c r="CB5">
+        <v>125</v>
+      </c>
+      <c r="CC5" s="16">
+        <v>125</v>
+      </c>
+      <c r="CD5">
+        <v>12.6</v>
+      </c>
+      <c r="CE5">
+        <v>-1.6</v>
+      </c>
+      <c r="CF5">
+        <v>6.71</v>
+      </c>
+      <c r="CG5" t="s">
+        <v>129</v>
+      </c>
+      <c r="CH5" t="s">
+        <v>130</v>
+      </c>
+      <c r="CI5" t="s">
+        <v>131</v>
+      </c>
+      <c r="CJ5" t="s">
+        <v>135</v>
+      </c>
+      <c r="CK5">
+        <v>125</v>
+      </c>
+      <c r="CL5" s="16">
+        <v>125</v>
+      </c>
+      <c r="CM5">
+        <v>75.400000000000006</v>
+      </c>
+      <c r="CN5">
+        <v>-0.1</v>
+      </c>
+      <c r="CO5">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="CP5" t="s">
+        <v>129</v>
+      </c>
+      <c r="CQ5" t="s">
+        <v>130</v>
+      </c>
+      <c r="CR5" t="s">
+        <v>131</v>
+      </c>
+      <c r="CS5" t="s">
+        <v>136</v>
+      </c>
+      <c r="CT5">
+        <v>113</v>
+      </c>
+      <c r="CU5" s="16"/>
+      <c r="CW5">
+        <v>-1.3838053097345131</v>
+      </c>
+      <c r="CX5">
+        <v>28</v>
+      </c>
+      <c r="CY5" t="s">
+        <v>129</v>
+      </c>
+      <c r="CZ5" t="s">
+        <v>131</v>
+      </c>
+      <c r="DA5" t="s">
+        <v>130</v>
+      </c>
+      <c r="DB5">
+        <v>63</v>
+      </c>
+      <c r="DC5">
+        <v>125</v>
+      </c>
+      <c r="DF5">
+        <v>9</v>
+      </c>
+      <c r="DG5">
+        <v>125</v>
+      </c>
+      <c r="DJ5">
+        <v>15</v>
+      </c>
+      <c r="DK5">
+        <v>125</v>
+      </c>
+      <c r="DL5">
+        <v>4</v>
+      </c>
+      <c r="DM5">
+        <v>125</v>
+      </c>
+      <c r="DN5">
+        <v>6</v>
+      </c>
+      <c r="DO5">
+        <v>125</v>
+      </c>
+      <c r="DR5">
+        <v>0</v>
+      </c>
+      <c r="DS5">
+        <v>125</v>
+      </c>
+      <c r="DT5">
+        <v>6</v>
+      </c>
+      <c r="DU5">
+        <v>125</v>
+      </c>
+      <c r="DX5">
+        <v>13</v>
+      </c>
+      <c r="DY5">
+        <v>125</v>
+      </c>
+      <c r="DZ5">
+        <v>0</v>
+      </c>
+      <c r="EA5">
+        <v>125</v>
+      </c>
+      <c r="EB5">
+        <v>4</v>
+      </c>
+      <c r="EC5">
+        <v>125</v>
+      </c>
+      <c r="ED5">
+        <v>1</v>
+      </c>
+      <c r="EE5">
+        <v>125</v>
+      </c>
+      <c r="EF5" s="8">
+        <v>7</v>
+      </c>
+      <c r="EG5" s="8">
+        <v>125</v>
+      </c>
+      <c r="EH5" t="s">
+        <v>160</v>
+      </c>
+      <c r="EI5" t="s">
+        <v>159</v>
+      </c>
+      <c r="EJ5" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6" spans="1:140" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>173</v>
+      </c>
+      <c r="B6" t="s">
+        <v>284</v>
+      </c>
+      <c r="C6" s="16">
+        <v>2023</v>
+      </c>
+      <c r="D6" s="16"/>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6" t="s">
+        <v>143</v>
+      </c>
+      <c r="G6" t="s">
+        <v>126</v>
+      </c>
+      <c r="H6" t="s">
+        <v>174</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="J6" t="s">
+        <v>146</v>
+      </c>
+      <c r="K6" s="2">
+        <v>435</v>
+      </c>
+      <c r="L6" s="3">
+        <v>144</v>
+      </c>
+      <c r="M6" s="8">
+        <v>36.1</v>
+      </c>
+      <c r="N6" s="8">
+        <v>46</v>
+      </c>
+      <c r="O6">
+        <v>6</v>
+      </c>
+      <c r="P6" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>22</v>
+      </c>
+      <c r="R6" s="3">
+        <v>144</v>
+      </c>
+      <c r="U6" s="2">
+        <v>34</v>
+      </c>
+      <c r="V6" s="2">
+        <v>144</v>
+      </c>
+      <c r="W6" s="8">
+        <v>18</v>
+      </c>
+      <c r="X6" s="8">
+        <v>144</v>
+      </c>
+      <c r="Y6" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="8">
+        <v>144</v>
+      </c>
+      <c r="AA6" s="8">
+        <v>11</v>
+      </c>
+      <c r="AB6" s="8">
+        <v>144</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>153</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>153</v>
+      </c>
+      <c r="AE6" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>153</v>
+      </c>
+      <c r="AG6" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="AH6" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ6" s="2">
+        <v>142</v>
+      </c>
+      <c r="AK6" s="16">
+        <v>142</v>
+      </c>
+      <c r="AL6" s="8">
+        <v>102.3</v>
+      </c>
+      <c r="AM6">
+        <v>-16.899999999999999</v>
+      </c>
+      <c r="AN6" s="2">
+        <v>19.07</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>129</v>
+      </c>
+      <c r="AP6" t="s">
+        <v>130</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>131</v>
+      </c>
+      <c r="AR6" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="AS6" s="16">
+        <v>142</v>
+      </c>
+      <c r="AT6" s="16">
+        <v>142</v>
+      </c>
+      <c r="AU6" s="8">
+        <v>26.7</v>
+      </c>
+      <c r="AV6" s="8">
+        <v>-5.7</v>
+      </c>
+      <c r="AW6" s="8">
+        <v>5</v>
+      </c>
+      <c r="AX6" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="AY6" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="AZ6" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="BA6" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="BB6" s="16">
+        <v>142</v>
+      </c>
+      <c r="BC6" s="16">
+        <v>142</v>
+      </c>
+      <c r="BD6" s="8">
+        <v>37</v>
+      </c>
+      <c r="BE6" s="8">
+        <v>-5.5</v>
+      </c>
+      <c r="BF6" s="8">
+        <v>12</v>
+      </c>
+      <c r="BG6" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="BH6" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="BI6" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="BT6" s="16"/>
+      <c r="CC6" s="16"/>
+      <c r="CL6" s="16"/>
+      <c r="CU6" s="16"/>
+      <c r="DB6" s="19">
+        <v>84</v>
+      </c>
+      <c r="DC6" s="8">
+        <v>144</v>
+      </c>
+      <c r="DD6" s="8">
+        <v>0</v>
+      </c>
+      <c r="DE6" s="8">
+        <v>144</v>
+      </c>
+      <c r="DF6" s="8">
+        <v>11</v>
+      </c>
+      <c r="DG6" s="8">
+        <v>144</v>
+      </c>
+      <c r="DH6" s="8">
+        <v>0</v>
+      </c>
+      <c r="DI6" s="8">
+        <v>144</v>
+      </c>
+      <c r="DJ6" s="8">
+        <v>17</v>
+      </c>
+      <c r="DK6" s="8">
+        <v>144</v>
+      </c>
+      <c r="DL6" s="8">
+        <v>12</v>
+      </c>
+      <c r="DM6" s="8">
+        <v>144</v>
+      </c>
+      <c r="DN6" s="8">
+        <v>0</v>
+      </c>
+      <c r="DO6" s="8">
+        <v>144</v>
+      </c>
+      <c r="DT6" s="8">
+        <v>8</v>
+      </c>
+      <c r="DU6" s="8">
+        <v>144</v>
+      </c>
+      <c r="DX6" s="8">
+        <v>16</v>
+      </c>
+      <c r="DY6" s="8">
+        <v>144</v>
+      </c>
+      <c r="EB6" s="8">
+        <v>3</v>
+      </c>
+      <c r="EC6" s="8">
+        <v>144</v>
+      </c>
+      <c r="EF6" s="19">
+        <v>20</v>
+      </c>
+      <c r="EG6" s="8">
+        <v>144</v>
+      </c>
+      <c r="EH6" t="s">
+        <v>137</v>
+      </c>
+      <c r="EI6" t="s">
+        <v>159</v>
+      </c>
+      <c r="EJ6" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7" spans="1:140" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>176</v>
+      </c>
+      <c r="B7" t="s">
+        <v>284</v>
+      </c>
+      <c r="C7" s="16">
+        <v>2023</v>
+      </c>
+      <c r="D7" s="16"/>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7" t="s">
+        <v>143</v>
+      </c>
+      <c r="G7" t="s">
+        <v>126</v>
+      </c>
+      <c r="H7" t="s">
+        <v>177</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="J7" t="s">
+        <v>146</v>
+      </c>
+      <c r="K7" s="2">
+        <v>435</v>
+      </c>
+      <c r="L7" s="3">
+        <v>145</v>
+      </c>
+      <c r="M7" s="8">
+        <v>37</v>
+      </c>
+      <c r="N7" s="8">
+        <v>59</v>
+      </c>
+      <c r="O7">
+        <v>6</v>
+      </c>
+      <c r="P7" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>29</v>
+      </c>
+      <c r="R7" s="3">
+        <v>145</v>
+      </c>
+      <c r="U7" s="2">
+        <v>27</v>
+      </c>
+      <c r="V7" s="2">
+        <v>145</v>
+      </c>
+      <c r="W7" s="8">
+        <v>11</v>
+      </c>
+      <c r="X7" s="8">
+        <v>145</v>
+      </c>
+      <c r="Y7" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="8">
+        <v>145</v>
+      </c>
+      <c r="AA7" s="8">
+        <v>12</v>
+      </c>
+      <c r="AB7" s="8">
+        <v>145</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>153</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>153</v>
+      </c>
+      <c r="AE7" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>153</v>
+      </c>
+      <c r="AG7" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="AH7" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ7" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK7" s="16">
+        <v>145</v>
+      </c>
+      <c r="AL7" s="8">
+        <v>101.7</v>
+      </c>
+      <c r="AM7">
+        <v>-19.600000000000001</v>
+      </c>
+      <c r="AN7" s="2">
+        <v>19.27</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>129</v>
+      </c>
+      <c r="AP7" t="s">
+        <v>130</v>
+      </c>
+      <c r="AQ7" t="s">
+        <v>131</v>
+      </c>
+      <c r="AR7" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="AS7" s="16">
+        <v>145</v>
+      </c>
+      <c r="AT7" s="16">
+        <v>145</v>
+      </c>
+      <c r="AU7" s="8">
+        <v>26.5</v>
+      </c>
+      <c r="AV7" s="8">
+        <v>-7</v>
+      </c>
+      <c r="AW7" s="8">
+        <v>5</v>
+      </c>
+      <c r="AX7" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="AY7" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="AZ7" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="BA7" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="BB7" s="16">
+        <v>145</v>
+      </c>
+      <c r="BC7" s="16">
+        <v>145</v>
+      </c>
+      <c r="BD7" s="8">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="BE7" s="8">
+        <v>-7.3</v>
+      </c>
+      <c r="BF7" s="8">
+        <v>12</v>
+      </c>
+      <c r="BG7" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="BH7" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="BI7" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="BT7" s="16"/>
+      <c r="CC7" s="16"/>
+      <c r="CL7" s="16"/>
+      <c r="CU7" s="16"/>
+      <c r="DB7" s="19">
+        <v>82</v>
+      </c>
+      <c r="DC7" s="8">
+        <v>145</v>
+      </c>
+      <c r="DD7" s="8">
+        <v>0</v>
+      </c>
+      <c r="DE7" s="8">
+        <v>145</v>
+      </c>
+      <c r="DF7" s="8">
+        <v>11</v>
+      </c>
+      <c r="DG7" s="8">
+        <v>145</v>
+      </c>
+      <c r="DH7" s="8">
+        <v>0</v>
+      </c>
+      <c r="DI7" s="8">
+        <v>145</v>
+      </c>
+      <c r="DJ7" s="8">
+        <v>17</v>
+      </c>
+      <c r="DK7" s="8">
+        <v>145</v>
+      </c>
+      <c r="DL7" s="8">
+        <v>10</v>
+      </c>
+      <c r="DM7" s="8">
+        <v>145</v>
+      </c>
+      <c r="DN7" s="8">
+        <v>0</v>
+      </c>
+      <c r="DO7" s="8">
+        <v>145</v>
+      </c>
+      <c r="DT7" s="8">
+        <v>11</v>
+      </c>
+      <c r="DU7" s="8">
+        <v>145</v>
+      </c>
+      <c r="DX7" s="8">
+        <v>9</v>
+      </c>
+      <c r="DY7" s="8">
+        <v>145</v>
+      </c>
+      <c r="EB7" s="8">
+        <v>5</v>
+      </c>
+      <c r="EC7" s="8">
+        <v>145</v>
+      </c>
+      <c r="EF7" s="19">
+        <v>18</v>
+      </c>
+      <c r="EG7" s="8">
+        <v>145</v>
+      </c>
+      <c r="EH7" t="s">
+        <v>137</v>
+      </c>
+      <c r="EI7" t="s">
+        <v>159</v>
+      </c>
+      <c r="EJ7" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="8" spans="1:140" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>178</v>
+      </c>
+      <c r="B8" t="s">
+        <v>284</v>
+      </c>
+      <c r="C8" s="16">
+        <v>2023</v>
+      </c>
+      <c r="D8" s="16"/>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8" t="s">
+        <v>143</v>
+      </c>
+      <c r="G8" t="s">
+        <v>160</v>
+      </c>
+      <c r="H8" t="s">
+        <v>127</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="J8" t="s">
+        <v>146</v>
+      </c>
+      <c r="K8" t="s">
+        <v>175</v>
+      </c>
+      <c r="L8" s="3">
+        <v>146</v>
+      </c>
+      <c r="M8" s="8">
+        <v>35.700000000000003</v>
+      </c>
+      <c r="N8" s="8">
+        <v>73</v>
+      </c>
+      <c r="O8">
+        <v>6</v>
+      </c>
+      <c r="P8" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>26</v>
+      </c>
+      <c r="R8" s="3">
+        <v>146</v>
+      </c>
+      <c r="U8" s="2">
+        <v>27</v>
+      </c>
+      <c r="V8" s="2">
+        <v>146</v>
+      </c>
+      <c r="W8" s="8">
+        <v>6</v>
+      </c>
+      <c r="X8" s="8">
+        <v>146</v>
+      </c>
+      <c r="Y8" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="8">
+        <v>146</v>
+      </c>
+      <c r="AA8" s="19">
+        <v>4</v>
+      </c>
+      <c r="AB8" s="8">
+        <v>146</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>153</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>153</v>
+      </c>
+      <c r="AE8" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>153</v>
+      </c>
+      <c r="AG8" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="AH8" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ8">
+        <v>145</v>
+      </c>
+      <c r="AK8" s="16">
+        <v>145</v>
+      </c>
+      <c r="AL8" s="8">
+        <v>101.9</v>
+      </c>
+      <c r="AM8">
+        <v>-19.3</v>
+      </c>
+      <c r="AN8" s="2">
+        <v>18.059999999999999</v>
+      </c>
+      <c r="AO8" t="s">
+        <v>129</v>
+      </c>
+      <c r="AP8" t="s">
+        <v>130</v>
+      </c>
+      <c r="AQ8" t="s">
+        <v>131</v>
+      </c>
+      <c r="AR8" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="AS8" s="16">
+        <v>145</v>
+      </c>
+      <c r="AT8" s="16">
+        <v>145</v>
+      </c>
+      <c r="AU8" s="8">
+        <v>27</v>
+      </c>
+      <c r="AV8" s="8">
+        <v>-6.4</v>
+      </c>
+      <c r="AW8" s="8">
+        <v>5</v>
+      </c>
+      <c r="AX8" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="AY8" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="AZ8" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="BA8" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="BB8" s="16">
+        <v>145</v>
+      </c>
+      <c r="BC8" s="16">
+        <v>145</v>
+      </c>
+      <c r="BD8" s="8">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="BE8" s="8">
+        <v>-6.2</v>
+      </c>
+      <c r="BF8" s="8">
+        <v>12</v>
+      </c>
+      <c r="BG8" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="BH8" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="BI8" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="BT8" s="16"/>
+      <c r="CC8" s="16"/>
+      <c r="CL8" s="16"/>
+      <c r="CU8" s="16"/>
+      <c r="DB8" s="19">
+        <v>71</v>
+      </c>
+      <c r="DC8" s="8">
+        <v>146</v>
+      </c>
+      <c r="DD8" s="8">
+        <v>0</v>
+      </c>
+      <c r="DE8" s="8">
+        <v>146</v>
+      </c>
+      <c r="DF8" s="8">
+        <v>7</v>
+      </c>
+      <c r="DG8" s="8">
+        <v>146</v>
+      </c>
+      <c r="DH8" s="8">
+        <v>0</v>
+      </c>
+      <c r="DI8" s="8">
+        <v>146</v>
+      </c>
+      <c r="DJ8" s="8">
+        <v>9</v>
+      </c>
+      <c r="DK8" s="8">
+        <v>146</v>
+      </c>
+      <c r="DL8" s="8">
+        <v>11</v>
+      </c>
+      <c r="DM8" s="8">
+        <v>146</v>
+      </c>
+      <c r="DN8" s="8">
+        <v>0</v>
+      </c>
+      <c r="DO8" s="8">
+        <v>146</v>
+      </c>
+      <c r="DT8" s="8">
+        <v>7</v>
+      </c>
+      <c r="DU8" s="8">
+        <v>146</v>
+      </c>
+      <c r="DX8" s="8">
+        <v>11</v>
+      </c>
+      <c r="DY8" s="8">
+        <v>146</v>
+      </c>
+      <c r="EB8" s="8">
+        <v>4</v>
+      </c>
+      <c r="EC8" s="8">
+        <v>146</v>
+      </c>
+      <c r="EF8" s="19">
+        <v>6</v>
+      </c>
+      <c r="EG8" s="8">
+        <v>146</v>
+      </c>
+      <c r="EH8" t="s">
+        <v>160</v>
+      </c>
+      <c r="EI8" t="s">
+        <v>159</v>
+      </c>
+      <c r="EJ8" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="9" spans="1:140" x14ac:dyDescent="0.2">
+      <c r="A9" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="B9" t="s">
+        <v>287</v>
+      </c>
+      <c r="C9" s="16">
+        <v>2023</v>
+      </c>
+      <c r="D9" s="16"/>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9" t="s">
+        <v>143</v>
+      </c>
+      <c r="G9" t="s">
+        <v>126</v>
+      </c>
+      <c r="H9" t="s">
+        <v>174</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="K9" s="8">
+        <v>28</v>
+      </c>
+      <c r="L9" s="18">
+        <v>9</v>
+      </c>
+      <c r="M9" s="8">
+        <v>14.8</v>
+      </c>
+      <c r="N9" s="8">
+        <v>5</v>
+      </c>
+      <c r="O9" s="10">
+        <v>6</v>
+      </c>
+      <c r="P9" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="18"/>
+      <c r="S9" s="10"/>
+      <c r="U9" s="8">
+        <v>1</v>
+      </c>
+      <c r="V9" s="18">
+        <v>9</v>
+      </c>
+      <c r="W9" s="8">
+        <v>0</v>
+      </c>
+      <c r="X9" s="18">
+        <v>9</v>
+      </c>
+      <c r="Y9" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="18">
+        <v>9</v>
+      </c>
+      <c r="AA9" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="18">
+        <v>9</v>
+      </c>
+      <c r="AC9" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="AD9" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="AE9" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="AF9" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="AG9" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="AH9" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ9" s="10"/>
+      <c r="AK9" s="18">
+        <v>9</v>
+      </c>
+      <c r="AL9" s="8">
+        <v>104.6</v>
+      </c>
+      <c r="AM9" s="10"/>
+      <c r="AN9" s="10"/>
+      <c r="AO9" s="10"/>
+      <c r="AP9" s="10"/>
+      <c r="AQ9" s="10"/>
+      <c r="AR9" s="8"/>
+      <c r="AS9" s="18"/>
+      <c r="AT9" s="18"/>
+      <c r="AU9" s="10"/>
+      <c r="AV9" s="10"/>
+      <c r="AW9" s="10"/>
+      <c r="AX9" s="10"/>
+      <c r="AY9" s="10"/>
+      <c r="AZ9" s="10"/>
+      <c r="BA9" s="10"/>
+      <c r="BB9" s="10"/>
+      <c r="BC9" s="10"/>
+      <c r="BD9" s="10"/>
+      <c r="BE9" s="10"/>
+      <c r="BF9" s="10"/>
+      <c r="BG9" s="10"/>
+      <c r="BH9" s="10"/>
+      <c r="BI9" s="10"/>
+      <c r="BJ9" s="10"/>
+      <c r="BK9" s="10"/>
+      <c r="BL9" s="10"/>
+      <c r="BM9" s="10"/>
+      <c r="BN9" s="10"/>
+      <c r="BO9" s="10"/>
+      <c r="BP9" s="10"/>
+      <c r="BQ9" s="10"/>
+      <c r="BR9" s="10"/>
+      <c r="BS9" s="10"/>
+      <c r="BT9" s="10"/>
+      <c r="BU9" s="10"/>
+      <c r="BV9" s="10"/>
+      <c r="BW9" s="10"/>
+      <c r="BX9" s="10"/>
+      <c r="BY9" s="10"/>
+      <c r="BZ9" s="10"/>
+      <c r="CA9" s="10"/>
+      <c r="CB9" s="10"/>
+      <c r="CC9" s="10"/>
+      <c r="CD9" s="10"/>
+      <c r="CE9" s="10"/>
+      <c r="CF9" s="10"/>
+      <c r="CG9" s="10"/>
+      <c r="CH9" s="10"/>
+      <c r="CI9" s="10"/>
+      <c r="CJ9" s="10"/>
+      <c r="CK9" s="10"/>
+      <c r="CL9" s="10"/>
+      <c r="CM9" s="10"/>
+      <c r="CN9" s="10"/>
+      <c r="CO9" s="10"/>
+      <c r="CP9" s="10"/>
+      <c r="CQ9" s="10"/>
+      <c r="CR9" s="10"/>
+      <c r="CS9" s="10"/>
+      <c r="CT9" s="10"/>
+      <c r="CU9" s="10"/>
+      <c r="CV9" s="10"/>
+      <c r="CW9" s="10"/>
+      <c r="CX9" s="10"/>
+      <c r="CY9" s="10"/>
+      <c r="CZ9" s="10"/>
+      <c r="DA9" s="10"/>
+      <c r="DB9" s="8">
+        <v>5</v>
+      </c>
+      <c r="DC9" s="8">
+        <v>9</v>
+      </c>
+      <c r="DD9" s="8">
+        <v>0</v>
+      </c>
+      <c r="DE9" s="8">
+        <v>9</v>
+      </c>
+      <c r="DF9" s="8">
+        <v>0</v>
+      </c>
+      <c r="DG9" s="8">
+        <v>9</v>
+      </c>
+      <c r="DH9" s="8">
+        <v>0</v>
+      </c>
+      <c r="DI9" s="8">
+        <v>9</v>
+      </c>
+      <c r="DJ9" s="8">
+        <v>2</v>
+      </c>
+      <c r="DK9" s="8">
+        <v>9</v>
+      </c>
+      <c r="DL9" s="8">
+        <v>2</v>
+      </c>
+      <c r="DM9" s="8">
+        <v>9</v>
+      </c>
+      <c r="DN9" s="8">
+        <v>0</v>
+      </c>
+      <c r="DO9" s="8">
+        <v>9</v>
+      </c>
+      <c r="DP9" s="10"/>
+      <c r="DQ9" s="10"/>
+      <c r="DR9" s="10"/>
+      <c r="DS9" s="10"/>
+      <c r="DT9" s="8">
+        <v>0</v>
+      </c>
+      <c r="DU9" s="8">
+        <v>9</v>
+      </c>
+      <c r="DV9" s="10"/>
+      <c r="DW9" s="10"/>
+      <c r="DX9" s="8">
+        <v>0</v>
+      </c>
+      <c r="DY9" s="8">
+        <v>9</v>
+      </c>
+      <c r="DZ9" s="10"/>
+      <c r="EA9" s="10"/>
+      <c r="EB9" s="10"/>
+      <c r="EC9" s="10"/>
+      <c r="ED9" s="10"/>
+      <c r="EE9" s="10"/>
+      <c r="EF9" s="8">
+        <v>1</v>
+      </c>
+      <c r="EG9" s="8">
+        <v>9</v>
+      </c>
+      <c r="EH9" t="s">
+        <v>137</v>
+      </c>
+      <c r="EI9" t="s">
+        <v>159</v>
+      </c>
+      <c r="EJ9" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="10" spans="1:140" x14ac:dyDescent="0.2">
+      <c r="A10" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="B10" t="s">
+        <v>287</v>
+      </c>
+      <c r="C10" s="16">
+        <v>2023</v>
+      </c>
+      <c r="D10" s="16"/>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10" t="s">
+        <v>143</v>
+      </c>
+      <c r="G10" t="s">
+        <v>126</v>
+      </c>
+      <c r="H10" t="s">
+        <v>177</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="K10" s="8">
+        <v>28</v>
+      </c>
+      <c r="L10" s="18">
+        <v>9</v>
+      </c>
+      <c r="M10" s="8">
+        <v>15</v>
+      </c>
+      <c r="N10" s="8">
+        <v>3</v>
+      </c>
+      <c r="O10" s="10">
+        <v>6</v>
+      </c>
+      <c r="P10" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="18"/>
+      <c r="S10" s="10"/>
+      <c r="U10" s="8">
+        <v>1</v>
+      </c>
+      <c r="V10" s="18">
+        <v>9</v>
+      </c>
+      <c r="W10" s="8">
+        <v>0</v>
+      </c>
+      <c r="X10" s="18">
+        <v>9</v>
+      </c>
+      <c r="Y10" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="18">
+        <v>9</v>
+      </c>
+      <c r="AA10" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="18">
+        <v>9</v>
+      </c>
+      <c r="AC10" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="AD10" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="AE10" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="AF10" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="AG10" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="AH10" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ10" s="10"/>
+      <c r="AK10" s="18">
+        <v>9</v>
+      </c>
+      <c r="AL10" s="8">
+        <v>97.9</v>
+      </c>
+      <c r="AM10" s="10"/>
+      <c r="AN10" s="10"/>
+      <c r="AO10" s="10"/>
+      <c r="AP10" s="10"/>
+      <c r="AQ10" s="10"/>
+      <c r="AR10" s="8"/>
+      <c r="AS10" s="18"/>
+      <c r="AT10" s="18"/>
+      <c r="AU10" s="10"/>
+      <c r="AV10" s="10"/>
+      <c r="AW10" s="10"/>
+      <c r="AX10" s="10"/>
+      <c r="AY10" s="10"/>
+      <c r="AZ10" s="10"/>
+      <c r="BA10" s="10"/>
+      <c r="BB10" s="10"/>
+      <c r="BC10" s="10"/>
+      <c r="BD10" s="10"/>
+      <c r="BE10" s="10"/>
+      <c r="BF10" s="10"/>
+      <c r="BG10" s="10"/>
+      <c r="BH10" s="10"/>
+      <c r="BI10" s="10"/>
+      <c r="BJ10" s="10"/>
+      <c r="BK10" s="10"/>
+      <c r="BL10" s="10"/>
+      <c r="BM10" s="10"/>
+      <c r="BN10" s="10"/>
+      <c r="BO10" s="10"/>
+      <c r="BP10" s="10"/>
+      <c r="BQ10" s="10"/>
+      <c r="BR10" s="10"/>
+      <c r="BS10" s="10"/>
+      <c r="BT10" s="10"/>
+      <c r="BU10" s="10"/>
+      <c r="BV10" s="10"/>
+      <c r="BW10" s="10"/>
+      <c r="BX10" s="10"/>
+      <c r="BY10" s="10"/>
+      <c r="BZ10" s="10"/>
+      <c r="CA10" s="10"/>
+      <c r="CB10" s="10"/>
+      <c r="CC10" s="10"/>
+      <c r="CD10" s="10"/>
+      <c r="CE10" s="10"/>
+      <c r="CF10" s="10"/>
+      <c r="CG10" s="10"/>
+      <c r="CH10" s="10"/>
+      <c r="CI10" s="10"/>
+      <c r="CJ10" s="10"/>
+      <c r="CK10" s="10"/>
+      <c r="CL10" s="10"/>
+      <c r="CM10" s="10"/>
+      <c r="CN10" s="10"/>
+      <c r="CO10" s="10"/>
+      <c r="CP10" s="10"/>
+      <c r="CQ10" s="10"/>
+      <c r="CR10" s="10"/>
+      <c r="CS10" s="10"/>
+      <c r="CT10" s="10"/>
+      <c r="CU10" s="10"/>
+      <c r="CV10" s="10"/>
+      <c r="CW10" s="10"/>
+      <c r="CX10" s="10"/>
+      <c r="CY10" s="10"/>
+      <c r="CZ10" s="10"/>
+      <c r="DA10" s="10"/>
+      <c r="DB10" s="8">
+        <v>6</v>
+      </c>
+      <c r="DC10" s="8">
+        <v>9</v>
+      </c>
+      <c r="DD10" s="8">
+        <v>1</v>
+      </c>
+      <c r="DE10" s="8">
+        <v>9</v>
+      </c>
+      <c r="DF10" s="8">
+        <v>0</v>
+      </c>
+      <c r="DG10" s="8">
+        <v>9</v>
+      </c>
+      <c r="DH10" s="8">
+        <v>1</v>
+      </c>
+      <c r="DI10" s="8">
+        <v>9</v>
+      </c>
+      <c r="DJ10" s="8">
+        <v>2</v>
+      </c>
+      <c r="DK10" s="8">
+        <v>9</v>
+      </c>
+      <c r="DL10" s="8">
+        <v>1</v>
+      </c>
+      <c r="DM10" s="8">
+        <v>9</v>
+      </c>
+      <c r="DN10" s="8">
+        <v>1</v>
+      </c>
+      <c r="DO10" s="8">
+        <v>9</v>
+      </c>
+      <c r="DP10" s="10"/>
+      <c r="DQ10" s="10"/>
+      <c r="DR10" s="10"/>
+      <c r="DS10" s="10"/>
+      <c r="DT10" s="8">
+        <v>1</v>
+      </c>
+      <c r="DU10" s="8">
+        <v>9</v>
+      </c>
+      <c r="DV10" s="10"/>
+      <c r="DW10" s="10"/>
+      <c r="DX10" s="8">
+        <v>0</v>
+      </c>
+      <c r="DY10" s="8">
+        <v>9</v>
+      </c>
+      <c r="DZ10" s="10"/>
+      <c r="EA10" s="10"/>
+      <c r="EB10" s="10"/>
+      <c r="EC10" s="10"/>
+      <c r="ED10" s="10"/>
+      <c r="EE10" s="10"/>
+      <c r="EF10" s="8">
+        <v>1</v>
+      </c>
+      <c r="EG10" s="8">
+        <v>9</v>
+      </c>
+      <c r="EH10" t="s">
+        <v>137</v>
+      </c>
+      <c r="EI10" t="s">
+        <v>159</v>
+      </c>
+      <c r="EJ10" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="11" spans="1:140" x14ac:dyDescent="0.2">
+      <c r="A11" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="B11" t="s">
+        <v>287</v>
+      </c>
+      <c r="C11" s="16">
+        <v>2023</v>
+      </c>
+      <c r="D11" s="16"/>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11" t="s">
+        <v>143</v>
+      </c>
+      <c r="G11" t="s">
+        <v>160</v>
+      </c>
+      <c r="H11" t="s">
+        <v>127</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="K11" s="8">
+        <v>28</v>
+      </c>
+      <c r="L11" s="18">
+        <v>10</v>
+      </c>
+      <c r="M11" s="8">
+        <v>15.5</v>
+      </c>
+      <c r="N11" s="8">
+        <v>4</v>
+      </c>
+      <c r="O11" s="10">
+        <v>6</v>
+      </c>
+      <c r="P11" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q11" s="8"/>
+      <c r="R11" s="18"/>
+      <c r="S11" s="10"/>
+      <c r="U11" s="8">
+        <v>0</v>
+      </c>
+      <c r="V11" s="18">
+        <v>10</v>
+      </c>
+      <c r="W11" s="8">
+        <v>0</v>
+      </c>
+      <c r="X11" s="18">
+        <v>10</v>
+      </c>
+      <c r="Y11" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="18">
+        <v>10</v>
+      </c>
+      <c r="AA11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="18">
+        <v>10</v>
+      </c>
+      <c r="AC11" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="AD11" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="AE11" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="AF11" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="AG11" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="AH11" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ11" s="10"/>
+      <c r="AK11" s="18">
+        <v>10</v>
+      </c>
+      <c r="AL11" s="8">
+        <v>96</v>
+      </c>
+      <c r="AM11" s="10"/>
+      <c r="AN11" s="10"/>
+      <c r="AO11" s="10"/>
+      <c r="AP11" s="10"/>
+      <c r="AQ11" s="10"/>
+      <c r="AR11" s="8"/>
+      <c r="AS11" s="18"/>
+      <c r="AT11" s="18"/>
+      <c r="AU11" s="10"/>
+      <c r="AV11" s="10"/>
+      <c r="AW11" s="10"/>
+      <c r="AX11" s="10"/>
+      <c r="AY11" s="10"/>
+      <c r="AZ11" s="10"/>
+      <c r="BA11" s="10"/>
+      <c r="BB11" s="10"/>
+      <c r="BC11" s="10"/>
+      <c r="BD11" s="10"/>
+      <c r="BE11" s="10"/>
+      <c r="BF11" s="10"/>
+      <c r="BG11" s="10"/>
+      <c r="BH11" s="10"/>
+      <c r="BI11" s="10"/>
+      <c r="BJ11" s="10"/>
+      <c r="BK11" s="10"/>
+      <c r="BL11" s="10"/>
+      <c r="BM11" s="10"/>
+      <c r="BN11" s="10"/>
+      <c r="BO11" s="10"/>
+      <c r="BP11" s="10"/>
+      <c r="BQ11" s="10"/>
+      <c r="BR11" s="10"/>
+      <c r="BS11" s="10"/>
+      <c r="BT11" s="10"/>
+      <c r="BU11" s="10"/>
+      <c r="BV11" s="10"/>
+      <c r="BW11" s="10"/>
+      <c r="BX11" s="10"/>
+      <c r="BY11" s="10"/>
+      <c r="BZ11" s="10"/>
+      <c r="CA11" s="10"/>
+      <c r="CB11" s="10"/>
+      <c r="CC11" s="10"/>
+      <c r="CD11" s="10"/>
+      <c r="CE11" s="10"/>
+      <c r="CF11" s="10"/>
+      <c r="CG11" s="10"/>
+      <c r="CH11" s="10"/>
+      <c r="CI11" s="10"/>
+      <c r="CJ11" s="10"/>
+      <c r="CK11" s="10"/>
+      <c r="CL11" s="10"/>
+      <c r="CM11" s="10"/>
+      <c r="CN11" s="10"/>
+      <c r="CO11" s="10"/>
+      <c r="CP11" s="10"/>
+      <c r="CQ11" s="10"/>
+      <c r="CR11" s="10"/>
+      <c r="CS11" s="10"/>
+      <c r="CT11" s="10"/>
+      <c r="CU11" s="10"/>
+      <c r="CV11" s="10"/>
+      <c r="CW11" s="10"/>
+      <c r="CX11" s="10"/>
+      <c r="CY11" s="10"/>
+      <c r="CZ11" s="10"/>
+      <c r="DA11" s="10"/>
+      <c r="DB11" s="8">
+        <v>3</v>
+      </c>
+      <c r="DC11" s="8">
+        <v>10</v>
+      </c>
+      <c r="DD11" s="8">
+        <v>1</v>
+      </c>
+      <c r="DE11" s="8">
+        <v>10</v>
+      </c>
+      <c r="DF11" s="8">
+        <v>0</v>
+      </c>
+      <c r="DG11" s="8">
+        <v>10</v>
+      </c>
+      <c r="DH11" s="8">
+        <v>0</v>
+      </c>
+      <c r="DI11" s="8">
+        <v>10</v>
+      </c>
+      <c r="DJ11" s="8">
+        <v>1</v>
+      </c>
+      <c r="DK11" s="8">
+        <v>10</v>
+      </c>
+      <c r="DL11" s="8">
+        <v>0</v>
+      </c>
+      <c r="DM11" s="8">
+        <v>10</v>
+      </c>
+      <c r="DN11" s="8">
+        <v>0</v>
+      </c>
+      <c r="DO11" s="8">
+        <v>10</v>
+      </c>
+      <c r="DP11" s="10"/>
+      <c r="DQ11" s="10"/>
+      <c r="DR11" s="10"/>
+      <c r="DS11" s="10"/>
+      <c r="DT11" s="8">
+        <v>0</v>
+      </c>
+      <c r="DU11" s="8">
+        <v>10</v>
+      </c>
+      <c r="DV11" s="10"/>
+      <c r="DW11" s="10"/>
+      <c r="DX11" s="8">
+        <v>0</v>
+      </c>
+      <c r="DY11" s="8">
+        <v>10</v>
+      </c>
+      <c r="DZ11" s="10"/>
+      <c r="EA11" s="10"/>
+      <c r="EB11" s="10"/>
+      <c r="EC11" s="10"/>
+      <c r="ED11" s="10"/>
+      <c r="EE11" s="10"/>
+      <c r="EF11" s="8">
+        <v>0</v>
+      </c>
+      <c r="EG11" s="8">
+        <v>10</v>
+      </c>
+      <c r="EH11" t="s">
+        <v>160</v>
+      </c>
+      <c r="EI11" t="s">
+        <v>159</v>
+      </c>
+      <c r="EJ11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="12" spans="1:140" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>179</v>
+      </c>
+      <c r="B12" t="s">
+        <v>180</v>
+      </c>
+      <c r="C12" s="16">
+        <v>2023</v>
+      </c>
+      <c r="D12" s="16"/>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12" t="s">
+        <v>143</v>
+      </c>
+      <c r="G12" t="s">
+        <v>126</v>
+      </c>
+      <c r="H12" t="s">
+        <v>177</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="J12" t="s">
+        <v>146</v>
+      </c>
+      <c r="K12" t="s">
+        <v>181</v>
+      </c>
+      <c r="L12" s="2">
+        <v>155</v>
+      </c>
+      <c r="M12" s="8">
+        <v>38.5</v>
+      </c>
+      <c r="N12" s="8">
+        <v>71</v>
+      </c>
+      <c r="O12">
+        <v>6</v>
+      </c>
+      <c r="P12" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>23</v>
+      </c>
+      <c r="R12" s="2">
+        <v>155</v>
+      </c>
+      <c r="U12" s="2">
+        <v>34</v>
+      </c>
+      <c r="V12" s="2">
+        <v>155</v>
+      </c>
+      <c r="W12" s="8">
+        <v>14</v>
+      </c>
+      <c r="X12" s="8">
+        <v>155</v>
+      </c>
+      <c r="Y12" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="8">
+        <v>155</v>
+      </c>
+      <c r="AA12" s="8">
+        <v>14</v>
+      </c>
+      <c r="AB12" s="8">
+        <v>155</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AE12" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AG12" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="AH12" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ12" s="2">
+        <v>153</v>
+      </c>
+      <c r="AK12" s="8">
+        <v>155</v>
+      </c>
+      <c r="AL12" s="8">
+        <v>101</v>
+      </c>
+      <c r="AM12">
+        <v>-16.399999999999999</v>
+      </c>
+      <c r="AN12" s="2">
+        <v>18.55</v>
+      </c>
+      <c r="AO12" t="s">
+        <v>129</v>
+      </c>
+      <c r="AP12" t="s">
+        <v>130</v>
+      </c>
+      <c r="AQ12" t="s">
+        <v>131</v>
+      </c>
+      <c r="AR12" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="AS12" s="8">
+        <v>153</v>
+      </c>
+      <c r="AT12" s="8">
+        <v>153</v>
+      </c>
+      <c r="AU12" s="8">
+        <v>26.3</v>
+      </c>
+      <c r="AV12" s="8">
+        <v>-5.2</v>
+      </c>
+      <c r="AW12" s="8">
+        <v>5</v>
+      </c>
+      <c r="AX12" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="AY12" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="AZ12" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="BA12" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="BB12" s="8">
+        <v>153</v>
+      </c>
+      <c r="BC12" s="8">
+        <v>153</v>
+      </c>
+      <c r="BD12" s="8">
+        <v>34.700000000000003</v>
+      </c>
+      <c r="BE12" s="8">
+        <v>-6</v>
+      </c>
+      <c r="BF12" s="8">
+        <v>12</v>
+      </c>
+      <c r="BG12" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="BH12" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="BI12" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="BT12" s="16"/>
+      <c r="CC12" s="16"/>
+      <c r="CL12" s="16"/>
+      <c r="CU12" s="16"/>
+      <c r="DB12" s="19">
+        <v>92</v>
+      </c>
+      <c r="DC12" s="8">
+        <v>155</v>
+      </c>
+      <c r="DF12" s="8">
+        <v>17</v>
+      </c>
+      <c r="DG12" s="8">
+        <v>155</v>
+      </c>
+      <c r="DJ12" s="8">
+        <v>18</v>
+      </c>
+      <c r="DK12" s="8">
+        <v>155</v>
+      </c>
+      <c r="DL12" s="8">
+        <v>6</v>
+      </c>
+      <c r="DM12" s="8">
+        <v>155</v>
+      </c>
+      <c r="DT12" s="8">
+        <v>9</v>
+      </c>
+      <c r="DU12" s="8">
+        <v>155</v>
+      </c>
+      <c r="DX12" s="8">
+        <v>15</v>
+      </c>
+      <c r="DY12" s="8">
+        <v>155</v>
+      </c>
+      <c r="EB12" s="8">
+        <v>4</v>
+      </c>
+      <c r="EC12" s="8">
+        <v>155</v>
+      </c>
+      <c r="EF12" s="19">
+        <v>20</v>
+      </c>
+      <c r="EG12" s="8">
+        <v>155</v>
+      </c>
+      <c r="EH12" t="s">
+        <v>137</v>
+      </c>
+      <c r="EI12" t="s">
+        <v>159</v>
+      </c>
+      <c r="EJ12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="13" spans="1:140" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>182</v>
+      </c>
+      <c r="B13" t="s">
+        <v>180</v>
+      </c>
+      <c r="C13" s="16">
+        <v>2023</v>
+      </c>
+      <c r="D13" s="16"/>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13" t="s">
+        <v>143</v>
+      </c>
+      <c r="G13" t="s">
+        <v>126</v>
+      </c>
+      <c r="H13" t="s">
+        <v>183</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="J13" t="s">
+        <v>146</v>
+      </c>
+      <c r="K13" t="s">
+        <v>181</v>
+      </c>
+      <c r="L13" s="2">
+        <v>154</v>
+      </c>
+      <c r="M13" s="8">
+        <v>37.5</v>
+      </c>
+      <c r="N13" s="8">
+        <v>56</v>
+      </c>
+      <c r="O13">
+        <v>6</v>
+      </c>
+      <c r="P13" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>27</v>
+      </c>
+      <c r="R13" s="2">
+        <v>154</v>
+      </c>
+      <c r="U13" s="2">
+        <v>38</v>
+      </c>
+      <c r="V13" s="2">
+        <v>154</v>
+      </c>
+      <c r="W13" s="8">
+        <v>19</v>
+      </c>
+      <c r="X13" s="8">
+        <v>154</v>
+      </c>
+      <c r="Y13" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="8">
+        <v>154</v>
+      </c>
+      <c r="AA13" s="8">
+        <v>11</v>
+      </c>
+      <c r="AB13" s="8">
+        <v>154</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>153</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>153</v>
+      </c>
+      <c r="AE13" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>153</v>
+      </c>
+      <c r="AG13" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="AH13" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ13" s="2">
+        <v>152</v>
+      </c>
+      <c r="AK13" s="8">
+        <v>154</v>
+      </c>
+      <c r="AL13" s="8">
+        <v>100</v>
+      </c>
+      <c r="AM13">
+        <v>-18.100000000000001</v>
+      </c>
+      <c r="AN13" s="2">
+        <v>18.489999999999998</v>
+      </c>
+      <c r="AO13" t="s">
+        <v>129</v>
+      </c>
+      <c r="AP13" t="s">
+        <v>130</v>
+      </c>
+      <c r="AQ13" t="s">
+        <v>131</v>
+      </c>
+      <c r="AR13" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="AS13" s="8">
+        <v>152</v>
+      </c>
+      <c r="AT13" s="8">
+        <v>152</v>
+      </c>
+      <c r="AU13" s="8">
+        <v>26.1</v>
+      </c>
+      <c r="AV13" s="8">
+        <v>-5.5</v>
+      </c>
+      <c r="AW13" s="8">
+        <v>5</v>
+      </c>
+      <c r="AX13" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="AY13" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="AZ13" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="BA13" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="BB13" s="8">
+        <v>152</v>
+      </c>
+      <c r="BC13" s="8">
+        <v>152</v>
+      </c>
+      <c r="BD13" s="8">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="BE13" s="8">
+        <v>-6.4</v>
+      </c>
+      <c r="BF13" s="8">
+        <v>12</v>
+      </c>
+      <c r="BG13" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="BH13" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="BI13" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="BT13" s="16"/>
+      <c r="CC13" s="16"/>
+      <c r="CL13" s="16"/>
+      <c r="CU13" s="16"/>
+      <c r="DB13" s="19">
+        <v>84</v>
+      </c>
+      <c r="DC13" s="8">
+        <v>154</v>
+      </c>
+      <c r="DF13" s="8">
+        <v>12</v>
+      </c>
+      <c r="DG13" s="8">
+        <v>154</v>
+      </c>
+      <c r="DJ13" s="8">
+        <v>17</v>
+      </c>
+      <c r="DK13" s="8">
+        <v>154</v>
+      </c>
+      <c r="DL13" s="8">
+        <v>5</v>
+      </c>
+      <c r="DM13" s="8">
+        <v>154</v>
+      </c>
+      <c r="DT13" s="8">
+        <v>5</v>
+      </c>
+      <c r="DU13" s="8">
+        <v>154</v>
+      </c>
+      <c r="DX13" s="8">
+        <v>13</v>
+      </c>
+      <c r="DY13" s="8">
+        <v>154</v>
+      </c>
+      <c r="EB13" s="8">
+        <v>4</v>
+      </c>
+      <c r="EC13" s="8">
+        <v>154</v>
+      </c>
+      <c r="EF13" s="19">
+        <v>17</v>
+      </c>
+      <c r="EG13" s="8">
+        <v>154</v>
+      </c>
+      <c r="EH13" t="s">
+        <v>137</v>
+      </c>
+      <c r="EI13" t="s">
+        <v>159</v>
+      </c>
+      <c r="EJ13" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="14" spans="1:140" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>160</v>
+      </c>
+      <c r="B14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C14" s="16">
+        <v>2023</v>
+      </c>
+      <c r="D14" s="16"/>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14" t="s">
+        <v>143</v>
+      </c>
+      <c r="G14" t="s">
+        <v>160</v>
+      </c>
+      <c r="H14" t="s">
+        <v>127</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="J14" t="s">
+        <v>146</v>
+      </c>
+      <c r="K14" t="s">
+        <v>181</v>
+      </c>
+      <c r="L14" s="2">
+        <v>155</v>
+      </c>
+      <c r="M14" s="8">
+        <v>38.6</v>
+      </c>
+      <c r="N14" s="8">
+        <v>65</v>
+      </c>
+      <c r="O14">
+        <v>6</v>
+      </c>
+      <c r="P14" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>21</v>
+      </c>
+      <c r="R14" s="2">
+        <v>155</v>
+      </c>
+      <c r="U14" s="2">
+        <v>27</v>
+      </c>
+      <c r="V14" s="2">
+        <v>155</v>
+      </c>
+      <c r="W14" s="8">
+        <v>10</v>
+      </c>
+      <c r="X14" s="8">
+        <v>155</v>
+      </c>
+      <c r="Y14" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="8">
+        <v>155</v>
+      </c>
+      <c r="AA14" s="8">
+        <v>6</v>
+      </c>
+      <c r="AB14" s="8">
+        <v>155</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>153</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>153</v>
+      </c>
+      <c r="AE14" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>153</v>
+      </c>
+      <c r="AG14" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="AH14" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ14" s="2">
+        <v>155</v>
+      </c>
+      <c r="AK14" s="8">
+        <v>155</v>
+      </c>
+      <c r="AL14" s="8">
+        <v>100.2</v>
+      </c>
+      <c r="AM14">
+        <v>-14.3</v>
+      </c>
+      <c r="AN14" s="2">
+        <v>18.670000000000002</v>
+      </c>
+      <c r="AO14" t="s">
+        <v>129</v>
+      </c>
+      <c r="AP14" t="s">
+        <v>130</v>
+      </c>
+      <c r="AQ14" t="s">
+        <v>131</v>
+      </c>
+      <c r="AR14" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="AS14" s="8">
+        <v>155</v>
+      </c>
+      <c r="AT14" s="8">
+        <v>155</v>
+      </c>
+      <c r="AU14" s="8">
+        <v>26.1</v>
+      </c>
+      <c r="AV14" s="8">
+        <v>-4.5999999999999996</v>
+      </c>
+      <c r="AW14" s="8">
+        <v>5</v>
+      </c>
+      <c r="AX14" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="AY14" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="AZ14" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="BA14" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="BB14" s="8">
+        <v>155</v>
+      </c>
+      <c r="BC14" s="8">
+        <v>155</v>
+      </c>
+      <c r="BD14" s="8">
+        <v>36.4</v>
+      </c>
+      <c r="BE14" s="8">
+        <v>-4.5</v>
+      </c>
+      <c r="BF14" s="8">
+        <v>12</v>
+      </c>
+      <c r="BG14" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="BH14" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="BI14" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="BT14" s="16"/>
+      <c r="CC14" s="16"/>
+      <c r="CL14" s="16"/>
+      <c r="CU14" s="16"/>
+      <c r="DB14" s="19">
+        <v>69</v>
+      </c>
+      <c r="DC14" s="8">
+        <v>155</v>
+      </c>
+      <c r="DF14" s="8">
+        <v>6</v>
+      </c>
+      <c r="DG14" s="8">
+        <v>155</v>
+      </c>
+      <c r="DJ14" s="8">
+        <v>14</v>
+      </c>
+      <c r="DK14" s="8">
+        <v>155</v>
+      </c>
+      <c r="DL14" s="8">
+        <v>2</v>
+      </c>
+      <c r="DM14" s="8">
+        <v>155</v>
+      </c>
+      <c r="DT14" s="8">
+        <v>8</v>
+      </c>
+      <c r="DU14" s="8">
+        <v>155</v>
+      </c>
+      <c r="DX14" s="8">
+        <v>9</v>
+      </c>
+      <c r="DY14" s="8">
+        <v>155</v>
+      </c>
+      <c r="EB14" s="8">
+        <v>4</v>
+      </c>
+      <c r="EC14" s="8">
+        <v>155</v>
+      </c>
+      <c r="EF14" s="19">
+        <v>9</v>
+      </c>
+      <c r="EG14" s="8">
+        <v>155</v>
+      </c>
+      <c r="EH14" t="s">
+        <v>160</v>
+      </c>
+      <c r="EI14" t="s">
+        <v>159</v>
+      </c>
+      <c r="EJ14" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="15" spans="1:140" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>185</v>
+      </c>
+      <c r="B15" t="s">
+        <v>186</v>
+      </c>
+      <c r="C15" s="16">
+        <v>2023</v>
+      </c>
+      <c r="D15" s="16"/>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15" t="s">
+        <v>143</v>
+      </c>
+      <c r="G15" t="s">
+        <v>160</v>
+      </c>
+      <c r="H15" t="s">
+        <v>127</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="J15" t="s">
+        <v>146</v>
+      </c>
+      <c r="K15" t="s">
+        <v>187</v>
+      </c>
+      <c r="L15">
+        <v>73</v>
+      </c>
+      <c r="M15">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="N15">
+        <v>19</v>
+      </c>
+      <c r="O15">
+        <v>4</v>
+      </c>
+      <c r="P15" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>148</v>
+      </c>
+      <c r="R15" t="s">
+        <v>188</v>
+      </c>
+      <c r="U15" t="s">
+        <v>189</v>
+      </c>
+      <c r="V15" t="s">
+        <v>190</v>
+      </c>
+      <c r="W15" t="s">
+        <v>148</v>
+      </c>
+      <c r="X15" t="s">
+        <v>190</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>188</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>163</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>188</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>153</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>153</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>155</v>
+      </c>
+      <c r="AF15" t="s">
+        <v>153</v>
+      </c>
+      <c r="AG15" t="s">
+        <v>153</v>
+      </c>
+      <c r="AH15" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ15">
+        <v>54</v>
+      </c>
+      <c r="AK15" s="16">
+        <v>72</v>
+      </c>
+      <c r="AL15">
+        <v>99.38</v>
+      </c>
+      <c r="AM15">
+        <v>88.69</v>
+      </c>
+      <c r="AN15">
+        <v>20.18</v>
+      </c>
+      <c r="AO15" t="s">
+        <v>191</v>
+      </c>
+      <c r="AP15" t="s">
+        <v>131</v>
+      </c>
+      <c r="AQ15" t="s">
+        <v>131</v>
+      </c>
+      <c r="AR15" t="s">
+        <v>132</v>
+      </c>
+      <c r="AS15">
+        <v>54</v>
+      </c>
+      <c r="AT15" s="16">
+        <v>72</v>
+      </c>
+      <c r="AU15">
+        <v>26.86</v>
+      </c>
+      <c r="AV15">
+        <v>23.61</v>
+      </c>
+      <c r="AW15">
+        <v>6.64</v>
+      </c>
+      <c r="AX15" t="s">
+        <v>191</v>
+      </c>
+      <c r="AY15" t="s">
+        <v>131</v>
+      </c>
+      <c r="AZ15" t="s">
+        <v>131</v>
+      </c>
+      <c r="BA15" t="s">
+        <v>133</v>
+      </c>
+      <c r="BB15">
+        <v>54</v>
+      </c>
+      <c r="BC15" s="16">
+        <v>72</v>
+      </c>
+      <c r="BD15">
+        <v>24.1</v>
+      </c>
+      <c r="BE15">
+        <v>22.65</v>
+      </c>
+      <c r="BF15">
+        <v>5.81</v>
+      </c>
+      <c r="BG15" t="s">
+        <v>191</v>
+      </c>
+      <c r="BH15" t="s">
+        <v>131</v>
+      </c>
+      <c r="BI15" t="s">
+        <v>131</v>
+      </c>
+      <c r="BT15" s="16"/>
+      <c r="CA15" t="s">
+        <v>192</v>
+      </c>
+      <c r="CB15">
+        <v>54</v>
+      </c>
+      <c r="CC15" s="16">
+        <v>72</v>
+      </c>
+      <c r="CD15">
+        <v>11.58</v>
+      </c>
+      <c r="CE15">
+        <v>9.56</v>
+      </c>
+      <c r="CF15">
+        <v>4.03</v>
+      </c>
+      <c r="CG15" t="s">
+        <v>191</v>
+      </c>
+      <c r="CH15" t="s">
+        <v>131</v>
+      </c>
+      <c r="CI15" t="s">
+        <v>131</v>
+      </c>
+      <c r="CL15" s="16"/>
+      <c r="CU15" s="16"/>
+      <c r="DB15">
+        <v>23</v>
+      </c>
+      <c r="DC15">
+        <v>72</v>
+      </c>
+      <c r="DF15">
+        <v>6</v>
+      </c>
+      <c r="DG15">
+        <v>72</v>
+      </c>
+      <c r="DJ15">
+        <v>4</v>
+      </c>
+      <c r="DK15">
+        <v>72</v>
+      </c>
+      <c r="DL15">
+        <v>4</v>
+      </c>
+      <c r="DM15">
+        <v>72</v>
+      </c>
+      <c r="DT15">
+        <v>2</v>
+      </c>
+      <c r="DU15">
+        <v>72</v>
+      </c>
+      <c r="DX15">
+        <v>1</v>
+      </c>
+      <c r="DY15">
+        <v>72</v>
+      </c>
+      <c r="ED15">
+        <v>1</v>
+      </c>
+      <c r="EE15">
+        <v>72</v>
+      </c>
+      <c r="EF15" s="8">
+        <v>3</v>
+      </c>
+      <c r="EG15" s="8">
+        <v>72</v>
+      </c>
+      <c r="EH15" t="s">
+        <v>160</v>
+      </c>
+      <c r="EI15" t="s">
+        <v>159</v>
+      </c>
+      <c r="EJ15" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="16" spans="1:140" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>193</v>
+      </c>
+      <c r="B16" t="s">
+        <v>186</v>
+      </c>
+      <c r="C16" s="16">
+        <v>2023</v>
+      </c>
+      <c r="D16" s="16"/>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16" t="s">
+        <v>143</v>
+      </c>
+      <c r="G16" t="s">
+        <v>194</v>
+      </c>
+      <c r="H16" t="s">
+        <v>195</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="J16" t="s">
+        <v>146</v>
+      </c>
+      <c r="K16" t="s">
+        <v>187</v>
+      </c>
+      <c r="L16">
+        <v>71</v>
+      </c>
+      <c r="M16">
+        <v>34</v>
+      </c>
+      <c r="N16">
+        <v>19</v>
+      </c>
+      <c r="O16">
+        <v>4</v>
+      </c>
+      <c r="P16" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>151</v>
+      </c>
+      <c r="R16" t="s">
+        <v>196</v>
+      </c>
+      <c r="U16" t="s">
+        <v>149</v>
+      </c>
+      <c r="V16" t="s">
+        <v>197</v>
+      </c>
+      <c r="W16" t="s">
+        <v>172</v>
+      </c>
+      <c r="X16" t="s">
+        <v>197</v>
+      </c>
+      <c r="Y16" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA16" s="5">
+        <v>2</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>196</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>153</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>153</v>
+      </c>
+      <c r="AE16" t="s">
+        <v>155</v>
+      </c>
+      <c r="AF16" t="s">
+        <v>153</v>
+      </c>
+      <c r="AG16" t="s">
+        <v>153</v>
+      </c>
+      <c r="AH16" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="AI16" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ16">
+        <v>49</v>
+      </c>
+      <c r="AK16" s="16">
+        <v>65</v>
+      </c>
+      <c r="AL16">
+        <v>98.54</v>
+      </c>
+      <c r="AM16">
+        <v>88.94</v>
+      </c>
+      <c r="AN16">
+        <v>17.03</v>
+      </c>
+      <c r="AO16" t="s">
+        <v>191</v>
+      </c>
+      <c r="AP16" t="s">
+        <v>131</v>
+      </c>
+      <c r="AQ16" t="s">
+        <v>131</v>
+      </c>
+      <c r="AR16" t="s">
+        <v>132</v>
+      </c>
+      <c r="AS16">
+        <v>49</v>
+      </c>
+      <c r="AT16" s="16">
+        <v>65</v>
+      </c>
+      <c r="AU16">
+        <v>26.2</v>
+      </c>
+      <c r="AV16">
+        <v>23.41</v>
+      </c>
+      <c r="AW16">
+        <v>6.14</v>
+      </c>
+      <c r="AX16" t="s">
+        <v>191</v>
+      </c>
+      <c r="AY16" t="s">
+        <v>131</v>
+      </c>
+      <c r="AZ16" t="s">
+        <v>131</v>
+      </c>
+      <c r="BA16" t="s">
+        <v>133</v>
+      </c>
+      <c r="BB16">
+        <v>49</v>
+      </c>
+      <c r="BC16" s="16">
+        <v>65</v>
+      </c>
+      <c r="BD16">
+        <v>23.65</v>
+      </c>
+      <c r="BE16">
+        <v>21.82</v>
+      </c>
+      <c r="BF16">
+        <v>5.85</v>
+      </c>
+      <c r="BG16" t="s">
+        <v>191</v>
+      </c>
+      <c r="BH16" t="s">
+        <v>131</v>
+      </c>
+      <c r="BI16" t="s">
+        <v>131</v>
+      </c>
+      <c r="BT16" s="16"/>
+      <c r="CA16" t="s">
+        <v>192</v>
+      </c>
+      <c r="CB16">
+        <v>49</v>
+      </c>
+      <c r="CC16" s="16">
+        <v>65</v>
+      </c>
+      <c r="CD16">
+        <v>12.91</v>
+      </c>
+      <c r="CE16">
+        <v>9.8800000000000008</v>
+      </c>
+      <c r="CF16">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="CG16" t="s">
+        <v>191</v>
+      </c>
+      <c r="CH16" t="s">
+        <v>131</v>
+      </c>
+      <c r="CI16" t="s">
+        <v>131</v>
+      </c>
+      <c r="CL16" s="16"/>
+      <c r="CU16" s="16"/>
+      <c r="DB16">
+        <v>14</v>
+      </c>
+      <c r="DC16">
+        <v>65</v>
+      </c>
+      <c r="DF16">
+        <v>3</v>
+      </c>
+      <c r="DG16">
+        <v>65</v>
+      </c>
+      <c r="DJ16">
+        <v>4</v>
+      </c>
+      <c r="DK16">
+        <v>65</v>
+      </c>
+      <c r="DL16">
+        <v>0</v>
+      </c>
+      <c r="DM16">
+        <v>65</v>
+      </c>
+      <c r="DT16">
+        <v>0</v>
+      </c>
+      <c r="DU16">
+        <v>65</v>
+      </c>
+      <c r="DX16">
+        <v>3</v>
+      </c>
+      <c r="DY16">
+        <v>65</v>
+      </c>
+      <c r="ED16">
+        <v>2</v>
+      </c>
+      <c r="EE16">
+        <v>65</v>
+      </c>
+      <c r="EF16" s="8">
+        <v>2</v>
+      </c>
+      <c r="EG16" s="8">
+        <v>65</v>
+      </c>
+      <c r="EH16" t="s">
+        <v>137</v>
+      </c>
+      <c r="EI16" t="s">
+        <v>159</v>
+      </c>
+      <c r="EJ16" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="17" spans="1:140" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>198</v>
+      </c>
+      <c r="B17" t="s">
+        <v>186</v>
+      </c>
+      <c r="C17" s="16">
+        <v>2023</v>
+      </c>
+      <c r="D17" s="16"/>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17" t="s">
+        <v>143</v>
+      </c>
+      <c r="G17" t="s">
+        <v>194</v>
+      </c>
+      <c r="H17" t="s">
+        <v>199</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="J17" t="s">
+        <v>146</v>
+      </c>
+      <c r="K17" t="s">
+        <v>187</v>
+      </c>
+      <c r="L17">
+        <v>69</v>
+      </c>
+      <c r="M17">
+        <v>32.299999999999997</v>
+      </c>
+      <c r="N17">
+        <v>15</v>
+      </c>
+      <c r="O17">
+        <v>4</v>
+      </c>
+      <c r="P17" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>148</v>
+      </c>
+      <c r="R17" t="s">
+        <v>200</v>
+      </c>
+      <c r="U17" t="s">
+        <v>149</v>
+      </c>
+      <c r="V17" t="s">
+        <v>201</v>
+      </c>
+      <c r="W17" t="s">
+        <v>151</v>
+      </c>
+      <c r="X17" t="s">
+        <v>201</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>200</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>163</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>200</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>153</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>153</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>155</v>
+      </c>
+      <c r="AF17" t="s">
+        <v>153</v>
+      </c>
+      <c r="AG17" t="s">
+        <v>153</v>
+      </c>
+      <c r="AH17" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="AI17" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ17">
+        <v>51</v>
+      </c>
+      <c r="AK17" s="16">
+        <v>68</v>
+      </c>
+      <c r="AL17">
+        <v>100.53</v>
+      </c>
+      <c r="AM17">
+        <v>85.18</v>
+      </c>
+      <c r="AN17">
+        <v>17.670000000000002</v>
+      </c>
+      <c r="AO17" t="s">
+        <v>191</v>
+      </c>
+      <c r="AP17" t="s">
+        <v>131</v>
+      </c>
+      <c r="AQ17" t="s">
+        <v>131</v>
+      </c>
+      <c r="AR17" t="s">
+        <v>132</v>
+      </c>
+      <c r="AS17">
+        <v>51</v>
+      </c>
+      <c r="AT17" s="16">
+        <v>68</v>
+      </c>
+      <c r="AU17">
+        <v>27.26</v>
+      </c>
+      <c r="AV17">
+        <v>22.22</v>
+      </c>
+      <c r="AW17">
+        <v>6.5</v>
+      </c>
+      <c r="AX17" t="s">
+        <v>191</v>
+      </c>
+      <c r="AY17" t="s">
+        <v>131</v>
+      </c>
+      <c r="AZ17" t="s">
+        <v>131</v>
+      </c>
+      <c r="BA17" t="s">
+        <v>133</v>
+      </c>
+      <c r="BB17">
+        <v>51</v>
+      </c>
+      <c r="BC17" s="16">
+        <v>68</v>
+      </c>
+      <c r="BD17">
+        <v>24.59</v>
+      </c>
+      <c r="BE17">
+        <v>22.53</v>
+      </c>
+      <c r="BF17">
+        <v>5.41</v>
+      </c>
+      <c r="BG17" t="s">
+        <v>191</v>
+      </c>
+      <c r="BH17" t="s">
+        <v>131</v>
+      </c>
+      <c r="BI17" t="s">
+        <v>131</v>
+      </c>
+      <c r="BT17" s="16"/>
+      <c r="CA17" t="s">
+        <v>192</v>
+      </c>
+      <c r="CB17">
+        <v>51</v>
+      </c>
+      <c r="CC17" s="16">
+        <v>68</v>
+      </c>
+      <c r="CD17">
+        <v>11.54</v>
+      </c>
+      <c r="CE17">
+        <v>9.06</v>
+      </c>
+      <c r="CF17">
+        <v>4.08</v>
+      </c>
+      <c r="CG17" t="s">
+        <v>191</v>
+      </c>
+      <c r="CH17" t="s">
+        <v>131</v>
+      </c>
+      <c r="CI17" t="s">
+        <v>131</v>
+      </c>
+      <c r="CL17" s="16"/>
+      <c r="CU17" s="16"/>
+      <c r="DB17">
+        <v>23</v>
+      </c>
+      <c r="DC17">
+        <v>68</v>
+      </c>
+      <c r="DF17">
+        <v>2</v>
+      </c>
+      <c r="DG17">
+        <v>68</v>
+      </c>
+      <c r="DJ17">
+        <v>5</v>
+      </c>
+      <c r="DK17">
+        <v>68</v>
+      </c>
+      <c r="DL17">
+        <v>2</v>
+      </c>
+      <c r="DM17">
+        <v>68</v>
+      </c>
+      <c r="DT17">
+        <v>8</v>
+      </c>
+      <c r="DU17">
+        <v>68</v>
+      </c>
+      <c r="DX17">
+        <v>5</v>
+      </c>
+      <c r="DY17">
+        <v>68</v>
+      </c>
+      <c r="ED17">
+        <v>0</v>
+      </c>
+      <c r="EE17">
+        <v>68</v>
+      </c>
+      <c r="EF17" s="19">
+        <v>1</v>
+      </c>
+      <c r="EG17" s="8">
+        <v>68</v>
+      </c>
+      <c r="EH17" t="s">
+        <v>137</v>
+      </c>
+      <c r="EI17" t="s">
+        <v>159</v>
+      </c>
+      <c r="EJ17" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="18" spans="1:140" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>202</v>
+      </c>
+      <c r="B18" t="s">
+        <v>186</v>
+      </c>
+      <c r="C18" s="16">
+        <v>2023</v>
+      </c>
+      <c r="D18" s="16"/>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18" t="s">
+        <v>143</v>
+      </c>
+      <c r="G18" t="s">
+        <v>203</v>
+      </c>
+      <c r="H18" t="s">
+        <v>172</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="J18" t="s">
+        <v>146</v>
+      </c>
+      <c r="K18" t="s">
+        <v>187</v>
+      </c>
+      <c r="L18">
+        <v>74</v>
+      </c>
+      <c r="M18">
+        <v>32.9</v>
+      </c>
+      <c r="N18">
+        <v>18</v>
+      </c>
+      <c r="O18">
+        <v>4</v>
+      </c>
+      <c r="P18" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>150</v>
+      </c>
+      <c r="R18" t="s">
+        <v>197</v>
+      </c>
+      <c r="U18" t="s">
+        <v>162</v>
+      </c>
+      <c r="V18" t="s">
+        <v>204</v>
+      </c>
+      <c r="W18" t="s">
+        <v>163</v>
+      </c>
+      <c r="X18" t="s">
+        <v>204</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>127</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>197</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>153</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>153</v>
+      </c>
+      <c r="AE18" t="s">
+        <v>155</v>
+      </c>
+      <c r="AF18" t="s">
+        <v>153</v>
+      </c>
+      <c r="AG18" t="s">
+        <v>153</v>
+      </c>
+      <c r="AH18" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="AI18" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ18">
+        <v>56</v>
+      </c>
+      <c r="AK18" s="16">
+        <v>71</v>
+      </c>
+      <c r="AL18">
+        <v>100.03</v>
+      </c>
+      <c r="AM18">
+        <v>78.040000000000006</v>
+      </c>
+      <c r="AN18">
+        <v>15.78</v>
+      </c>
+      <c r="AO18" t="s">
+        <v>191</v>
+      </c>
+      <c r="AP18" t="s">
+        <v>131</v>
+      </c>
+      <c r="AQ18" t="s">
+        <v>131</v>
+      </c>
+      <c r="AR18" t="s">
+        <v>132</v>
+      </c>
+      <c r="AS18">
+        <v>56</v>
+      </c>
+      <c r="AT18" s="16">
+        <v>71</v>
+      </c>
+      <c r="AU18">
+        <v>27.49</v>
+      </c>
+      <c r="AV18">
+        <v>19.52</v>
+      </c>
+      <c r="AW18">
+        <v>5.1100000000000003</v>
+      </c>
+      <c r="AX18" t="s">
+        <v>191</v>
+      </c>
+      <c r="AY18" t="s">
+        <v>131</v>
+      </c>
+      <c r="AZ18" t="s">
+        <v>131</v>
+      </c>
+      <c r="BA18" t="s">
+        <v>133</v>
+      </c>
+      <c r="BB18">
+        <v>56</v>
+      </c>
+      <c r="BC18" s="16">
+        <v>71</v>
+      </c>
+      <c r="BD18">
+        <v>23.65</v>
+      </c>
+      <c r="BE18">
+        <v>21.45</v>
+      </c>
+      <c r="BF18">
+        <v>5.13</v>
+      </c>
+      <c r="BG18" t="s">
+        <v>191</v>
+      </c>
+      <c r="BH18" t="s">
+        <v>131</v>
+      </c>
+      <c r="BI18" t="s">
+        <v>131</v>
+      </c>
+      <c r="BT18" s="16"/>
+      <c r="CA18" t="s">
+        <v>192</v>
+      </c>
+      <c r="CB18">
+        <v>56</v>
+      </c>
+      <c r="CC18" s="16">
+        <v>71</v>
+      </c>
+      <c r="CD18">
+        <v>12.58</v>
+      </c>
+      <c r="CE18">
+        <v>8.5</v>
+      </c>
+      <c r="CF18">
+        <v>4.09</v>
+      </c>
+      <c r="CG18" t="s">
+        <v>191</v>
+      </c>
+      <c r="CH18" t="s">
+        <v>131</v>
+      </c>
+      <c r="CI18" t="s">
+        <v>131</v>
+      </c>
+      <c r="CL18" s="16"/>
+      <c r="CU18" s="16"/>
+      <c r="DB18">
+        <v>36</v>
+      </c>
+      <c r="DC18">
+        <v>71</v>
+      </c>
+      <c r="DF18">
+        <v>5</v>
+      </c>
+      <c r="DG18">
+        <v>71</v>
+      </c>
+      <c r="DJ18">
+        <v>6</v>
+      </c>
+      <c r="DK18">
+        <v>71</v>
+      </c>
+      <c r="DL18">
+        <v>6</v>
+      </c>
+      <c r="DM18">
+        <v>71</v>
+      </c>
+      <c r="DT18">
+        <v>0</v>
+      </c>
+      <c r="DU18">
+        <v>71</v>
+      </c>
+      <c r="DX18">
+        <v>5</v>
+      </c>
+      <c r="DY18">
+        <v>71</v>
+      </c>
+      <c r="ED18">
+        <v>8</v>
+      </c>
+      <c r="EE18">
+        <v>71</v>
+      </c>
+      <c r="EF18" s="8">
+        <v>1</v>
+      </c>
+      <c r="EG18" s="8">
+        <v>71</v>
+      </c>
+      <c r="EH18" t="s">
+        <v>205</v>
+      </c>
+      <c r="EI18" t="s">
+        <v>159</v>
+      </c>
+      <c r="EJ18" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="19" spans="1:140" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>206</v>
+      </c>
+      <c r="B19" t="s">
+        <v>207</v>
+      </c>
+      <c r="C19" s="16">
+        <v>2023</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>268</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19" t="s">
+        <v>143</v>
+      </c>
+      <c r="G19" t="s">
+        <v>160</v>
+      </c>
+      <c r="H19" t="s">
+        <v>127</v>
+      </c>
+      <c r="I19" t="s">
+        <v>208</v>
+      </c>
+      <c r="K19" t="s">
+        <v>209</v>
+      </c>
+      <c r="L19">
+        <v>34</v>
+      </c>
+      <c r="M19" t="s">
+        <v>210</v>
+      </c>
+      <c r="N19">
+        <v>18</v>
+      </c>
+      <c r="O19">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="P19" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="U19" t="s">
+        <v>152</v>
+      </c>
+      <c r="V19" t="s">
+        <v>211</v>
+      </c>
+      <c r="W19" t="s">
+        <v>127</v>
+      </c>
+      <c r="X19" t="s">
+        <v>211</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>211</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>127</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>211</v>
+      </c>
+      <c r="AK19" s="16"/>
+      <c r="AT19" s="16"/>
+      <c r="BC19" s="16"/>
+      <c r="BT19" s="16"/>
+      <c r="CC19" s="16"/>
+      <c r="CL19" s="16"/>
+      <c r="CU19" s="16"/>
+      <c r="DB19">
+        <v>16</v>
+      </c>
+      <c r="DC19">
+        <v>34</v>
+      </c>
+      <c r="DD19">
+        <v>0</v>
+      </c>
+      <c r="DE19">
+        <v>34</v>
+      </c>
+      <c r="DF19">
+        <v>0</v>
+      </c>
+      <c r="DG19">
+        <v>34</v>
+      </c>
+      <c r="DH19">
+        <v>2</v>
+      </c>
+      <c r="DI19">
+        <v>34</v>
+      </c>
+      <c r="DJ19">
+        <v>7</v>
+      </c>
+      <c r="DK19">
+        <v>34</v>
+      </c>
+      <c r="DL19">
+        <v>0</v>
+      </c>
+      <c r="DM19">
+        <v>34</v>
+      </c>
+      <c r="DN19">
+        <v>5</v>
+      </c>
+      <c r="DO19">
+        <v>34</v>
+      </c>
+      <c r="EH19" t="s">
+        <v>160</v>
+      </c>
+      <c r="EI19" t="s">
+        <v>212</v>
+      </c>
+      <c r="EJ19" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="20" spans="1:140" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>213</v>
+      </c>
+      <c r="B20" t="s">
+        <v>207</v>
+      </c>
+      <c r="C20" s="16">
+        <v>2023</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>268</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20" t="s">
+        <v>143</v>
+      </c>
+      <c r="G20" t="s">
+        <v>126</v>
+      </c>
+      <c r="H20" t="s">
+        <v>174</v>
+      </c>
+      <c r="I20" t="s">
+        <v>208</v>
+      </c>
+      <c r="K20" t="s">
+        <v>209</v>
+      </c>
+      <c r="L20">
+        <v>35</v>
+      </c>
+      <c r="M20" t="s">
+        <v>214</v>
+      </c>
+      <c r="N20">
+        <v>14</v>
+      </c>
+      <c r="O20">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="P20" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="U20" t="s">
+        <v>151</v>
+      </c>
+      <c r="V20" t="s">
+        <v>215</v>
+      </c>
+      <c r="W20" t="s">
+        <v>127</v>
+      </c>
+      <c r="X20" t="s">
+        <v>215</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>215</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>163</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>215</v>
+      </c>
+      <c r="AK20" s="16"/>
+      <c r="AT20" s="16"/>
+      <c r="BC20" s="16"/>
+      <c r="BT20" s="16"/>
+      <c r="CC20" s="16"/>
+      <c r="CL20" s="16"/>
+      <c r="CU20" s="16"/>
+      <c r="DB20">
+        <v>34</v>
+      </c>
+      <c r="DC20">
+        <v>35</v>
+      </c>
+      <c r="DD20">
+        <v>5</v>
+      </c>
+      <c r="DE20">
+        <v>35</v>
+      </c>
+      <c r="DF20">
+        <v>0</v>
+      </c>
+      <c r="DG20">
+        <v>35</v>
+      </c>
+      <c r="DH20">
+        <v>10</v>
+      </c>
+      <c r="DI20">
+        <v>35</v>
+      </c>
+      <c r="DJ20">
+        <v>4</v>
+      </c>
+      <c r="DK20">
+        <v>35</v>
+      </c>
+      <c r="DL20">
+        <v>12</v>
+      </c>
+      <c r="DM20">
+        <v>35</v>
+      </c>
+      <c r="DN20">
+        <v>21</v>
+      </c>
+      <c r="DO20">
+        <v>35</v>
+      </c>
+      <c r="EH20" t="s">
+        <v>137</v>
+      </c>
+      <c r="EI20" t="s">
+        <v>212</v>
+      </c>
+      <c r="EJ20" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="21" spans="1:140" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>216</v>
+      </c>
+      <c r="B21" t="s">
+        <v>207</v>
+      </c>
+      <c r="C21" s="16">
+        <v>2023</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>268</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21" t="s">
+        <v>143</v>
+      </c>
+      <c r="G21" t="s">
+        <v>217</v>
+      </c>
+      <c r="H21" t="s">
+        <v>218</v>
+      </c>
+      <c r="I21" t="s">
+        <v>208</v>
+      </c>
+      <c r="K21" t="s">
+        <v>209</v>
+      </c>
+      <c r="L21">
+        <v>36</v>
+      </c>
+      <c r="M21" t="s">
+        <v>219</v>
+      </c>
+      <c r="N21">
+        <v>13</v>
+      </c>
+      <c r="O21">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="P21" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="U21" t="s">
+        <v>152</v>
+      </c>
+      <c r="V21" t="s">
+        <v>220</v>
+      </c>
+      <c r="W21" t="s">
+        <v>127</v>
+      </c>
+      <c r="X21" t="s">
+        <v>220</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>220</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>127</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>220</v>
+      </c>
+      <c r="AK21" s="16"/>
+      <c r="AT21" s="16"/>
+      <c r="BC21" s="16"/>
+      <c r="BT21" s="16"/>
+      <c r="CC21" s="16"/>
+      <c r="CL21" s="16"/>
+      <c r="CU21" s="16"/>
+      <c r="DB21">
+        <v>15</v>
+      </c>
+      <c r="DC21">
+        <v>36</v>
+      </c>
+      <c r="DD21">
+        <v>0</v>
+      </c>
+      <c r="DE21">
+        <v>36</v>
+      </c>
+      <c r="DF21">
+        <v>3</v>
+      </c>
+      <c r="DG21">
+        <v>36</v>
+      </c>
+      <c r="DH21">
+        <v>1</v>
+      </c>
+      <c r="DI21">
+        <v>36</v>
+      </c>
+      <c r="DJ21">
+        <v>1</v>
+      </c>
+      <c r="DK21">
+        <v>36</v>
+      </c>
+      <c r="DL21">
+        <v>0</v>
+      </c>
+      <c r="DM21">
+        <v>36</v>
+      </c>
+      <c r="DN21">
+        <v>5</v>
+      </c>
+      <c r="DO21">
+        <v>36</v>
+      </c>
+      <c r="EH21" t="s">
+        <v>205</v>
+      </c>
+      <c r="EI21" t="s">
+        <v>212</v>
+      </c>
+      <c r="EJ21" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="22" spans="1:140" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>160</v>
+      </c>
+      <c r="B22" t="s">
+        <v>221</v>
+      </c>
+      <c r="C22" s="16">
+        <v>2023</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>269</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22" t="s">
+        <v>222</v>
+      </c>
+      <c r="G22" t="s">
+        <v>160</v>
+      </c>
+      <c r="H22" t="s">
+        <v>127</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="J22" t="s">
+        <v>223</v>
+      </c>
+      <c r="K22" t="s">
+        <v>200</v>
+      </c>
+      <c r="L22">
+        <v>68</v>
+      </c>
+      <c r="M22" t="s">
+        <v>224</v>
+      </c>
+      <c r="N22">
+        <v>15</v>
+      </c>
+      <c r="O22">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="P22" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="W22" t="s">
+        <v>163</v>
+      </c>
+      <c r="X22" t="s">
+        <v>225</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>225</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>127</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>225</v>
+      </c>
+      <c r="AK22" s="16"/>
+      <c r="AT22" s="16"/>
+      <c r="BC22" s="16"/>
+      <c r="BT22" s="16"/>
+      <c r="CC22" s="16"/>
+      <c r="CL22" s="16"/>
+      <c r="CU22" s="16"/>
+      <c r="DB22">
+        <v>2</v>
+      </c>
+      <c r="DC22">
+        <v>63</v>
+      </c>
+      <c r="DH22">
+        <v>1</v>
+      </c>
+      <c r="DI22">
+        <v>63</v>
+      </c>
+      <c r="DL22">
+        <v>1</v>
+      </c>
+      <c r="DM22">
+        <v>63</v>
+      </c>
+      <c r="DN22" s="8">
+        <v>0</v>
+      </c>
+      <c r="DO22">
+        <v>63</v>
+      </c>
+      <c r="DR22">
+        <v>1</v>
+      </c>
+      <c r="DS22">
+        <v>59</v>
+      </c>
+      <c r="EH22" t="s">
+        <v>160</v>
+      </c>
+      <c r="EI22" t="s">
+        <v>212</v>
+      </c>
+      <c r="EJ22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="23" spans="1:140" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>226</v>
+      </c>
+      <c r="B23" t="s">
+        <v>221</v>
+      </c>
+      <c r="C23" s="16">
+        <v>2023</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>269</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23" t="s">
+        <v>222</v>
+      </c>
+      <c r="G23" t="s">
+        <v>126</v>
+      </c>
+      <c r="H23" t="s">
+        <v>199</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="J23" t="s">
+        <v>223</v>
+      </c>
+      <c r="K23" t="s">
+        <v>200</v>
+      </c>
+      <c r="L23">
+        <v>68</v>
+      </c>
+      <c r="M23" t="s">
+        <v>224</v>
+      </c>
+      <c r="N23">
+        <v>15</v>
+      </c>
+      <c r="O23">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="P23" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="U23" t="s">
+        <v>127</v>
+      </c>
+      <c r="V23" t="s">
+        <v>225</v>
+      </c>
+      <c r="W23" t="s">
+        <v>127</v>
+      </c>
+      <c r="X23" t="s">
+        <v>225</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>225</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>163</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>225</v>
+      </c>
+      <c r="AK23" s="16"/>
+      <c r="AT23" s="16"/>
+      <c r="BC23" s="16"/>
+      <c r="BT23" s="16"/>
+      <c r="CC23" s="16"/>
+      <c r="CL23" s="16"/>
+      <c r="CU23" s="16"/>
+      <c r="DB23">
+        <v>32</v>
+      </c>
+      <c r="DC23">
+        <v>63</v>
+      </c>
+      <c r="DH23">
+        <v>7</v>
+      </c>
+      <c r="DI23">
+        <v>63</v>
+      </c>
+      <c r="DL23">
+        <v>16</v>
+      </c>
+      <c r="DM23">
+        <v>63</v>
+      </c>
+      <c r="DN23">
+        <v>16</v>
+      </c>
+      <c r="DO23">
+        <v>63</v>
+      </c>
+      <c r="DR23">
+        <v>5</v>
+      </c>
+      <c r="DS23">
+        <v>62</v>
+      </c>
+      <c r="EH23" t="s">
+        <v>137</v>
+      </c>
+      <c r="EI23" t="s">
+        <v>212</v>
+      </c>
+      <c r="EJ23" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="24" spans="1:140" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>227</v>
+      </c>
+      <c r="B24" t="s">
+        <v>228</v>
+      </c>
+      <c r="C24" s="16">
+        <v>2021</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>264</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24" t="s">
+        <v>222</v>
+      </c>
+      <c r="G24" t="s">
+        <v>126</v>
+      </c>
+      <c r="H24" t="s">
+        <v>150</v>
+      </c>
+      <c r="I24" t="s">
+        <v>208</v>
+      </c>
+      <c r="K24" t="s">
+        <v>184</v>
+      </c>
+      <c r="L24">
+        <v>12</v>
+      </c>
+      <c r="M24" t="s">
+        <v>229</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="P24" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="U24" t="s">
+        <v>127</v>
+      </c>
+      <c r="V24" t="s">
+        <v>139</v>
+      </c>
+      <c r="W24" t="s">
+        <v>127</v>
+      </c>
+      <c r="X24" t="s">
+        <v>139</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>139</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>127</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>139</v>
+      </c>
+      <c r="AK24" s="16"/>
+      <c r="AT24" s="16"/>
+      <c r="BC24" s="16"/>
+      <c r="BT24" s="16"/>
+      <c r="CC24" s="16"/>
+      <c r="CL24" s="16"/>
+      <c r="CU24" s="16"/>
+      <c r="DB24">
+        <v>1</v>
+      </c>
+      <c r="DC24">
+        <v>12</v>
+      </c>
+      <c r="DL24">
+        <v>1</v>
+      </c>
+      <c r="DM24">
+        <v>12</v>
+      </c>
+      <c r="DN24">
+        <v>0</v>
+      </c>
+      <c r="DO24">
+        <v>12</v>
+      </c>
+      <c r="DP24">
+        <v>0</v>
+      </c>
+      <c r="DQ24">
+        <v>12</v>
+      </c>
+      <c r="DR24">
+        <v>0</v>
+      </c>
+      <c r="DS24">
+        <v>12</v>
+      </c>
+      <c r="EH24" t="s">
+        <v>137</v>
+      </c>
+      <c r="EI24" t="s">
+        <v>212</v>
+      </c>
+      <c r="EJ24" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="25" spans="1:140" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>230</v>
+      </c>
+      <c r="B25" t="s">
+        <v>228</v>
+      </c>
+      <c r="C25" s="16">
+        <v>2021</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>264</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25" t="s">
+        <v>222</v>
+      </c>
+      <c r="G25" t="s">
+        <v>126</v>
+      </c>
+      <c r="H25" t="s">
+        <v>174</v>
+      </c>
+      <c r="I25" t="s">
+        <v>208</v>
+      </c>
+      <c r="K25" t="s">
+        <v>184</v>
+      </c>
+      <c r="L25">
+        <v>12</v>
+      </c>
+      <c r="M25" t="s">
+        <v>229</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="P25" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="U25" t="s">
+        <v>127</v>
+      </c>
+      <c r="V25" t="s">
+        <v>139</v>
+      </c>
+      <c r="W25" t="s">
+        <v>127</v>
+      </c>
+      <c r="X25" t="s">
+        <v>139</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>139</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>127</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>139</v>
+      </c>
+      <c r="AK25" s="16"/>
+      <c r="AT25" s="16"/>
+      <c r="BC25" s="16"/>
+      <c r="BT25" s="16"/>
+      <c r="CC25" s="16"/>
+      <c r="CL25" s="16"/>
+      <c r="CU25" s="16"/>
+      <c r="DB25">
+        <v>1</v>
+      </c>
+      <c r="DC25">
+        <v>12</v>
+      </c>
+      <c r="DL25">
+        <v>0</v>
+      </c>
+      <c r="DM25">
+        <v>12</v>
+      </c>
+      <c r="DN25">
+        <v>1</v>
+      </c>
+      <c r="DO25">
+        <v>12</v>
+      </c>
+      <c r="DP25">
+        <v>0</v>
+      </c>
+      <c r="DQ25">
+        <v>12</v>
+      </c>
+      <c r="DR25">
+        <v>0</v>
+      </c>
+      <c r="DS25">
+        <v>12</v>
+      </c>
+      <c r="EH25" t="s">
+        <v>137</v>
+      </c>
+      <c r="EI25" t="s">
+        <v>212</v>
+      </c>
+      <c r="EJ25" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="26" spans="1:140" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>160</v>
+      </c>
+      <c r="B26" t="s">
+        <v>228</v>
+      </c>
+      <c r="C26" s="16">
+        <v>2021</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>264</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26" t="s">
+        <v>222</v>
+      </c>
+      <c r="G26" t="s">
+        <v>160</v>
+      </c>
+      <c r="H26" t="s">
+        <v>127</v>
+      </c>
+      <c r="I26" t="s">
+        <v>208</v>
+      </c>
+      <c r="K26" t="s">
+        <v>184</v>
+      </c>
+      <c r="L26">
+        <v>24</v>
+      </c>
+      <c r="M26" t="s">
+        <v>229</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="P26" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="U26" t="s">
+        <v>127</v>
+      </c>
+      <c r="V26" t="s">
+        <v>184</v>
+      </c>
+      <c r="W26" t="s">
+        <v>127</v>
+      </c>
+      <c r="X26" t="s">
+        <v>184</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA26" t="s">
+        <v>127</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>184</v>
+      </c>
+      <c r="AK26" s="16"/>
+      <c r="AT26" s="16"/>
+      <c r="BC26" s="16"/>
+      <c r="BT26" s="16"/>
+      <c r="CC26" s="16"/>
+      <c r="CL26" s="16"/>
+      <c r="CU26" s="16"/>
+      <c r="DB26">
+        <v>1</v>
+      </c>
+      <c r="DC26">
+        <v>24</v>
+      </c>
+      <c r="DL26">
+        <v>0</v>
+      </c>
+      <c r="DM26">
+        <v>24</v>
+      </c>
+      <c r="DN26">
+        <v>0</v>
+      </c>
+      <c r="DO26">
+        <v>24</v>
+      </c>
+      <c r="DP26">
+        <v>0</v>
+      </c>
+      <c r="DQ26">
+        <v>24</v>
+      </c>
+      <c r="DR26">
+        <v>0</v>
+      </c>
+      <c r="DS26">
+        <v>24</v>
+      </c>
+      <c r="EH26" t="s">
+        <v>160</v>
+      </c>
+      <c r="EI26" t="s">
+        <v>212</v>
+      </c>
+      <c r="EJ26" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="27" spans="1:140" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>230</v>
+      </c>
+      <c r="B27" t="s">
+        <v>231</v>
+      </c>
+      <c r="C27" s="16">
+        <v>2023</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27" t="s">
+        <v>222</v>
+      </c>
+      <c r="G27" t="s">
+        <v>126</v>
+      </c>
+      <c r="H27" t="s">
+        <v>174</v>
+      </c>
+      <c r="I27" t="s">
+        <v>232</v>
+      </c>
+      <c r="K27" t="s">
+        <v>149</v>
+      </c>
+      <c r="L27">
+        <v>16</v>
+      </c>
+      <c r="M27" t="s">
+        <v>233</v>
+      </c>
+      <c r="N27">
+        <v>12</v>
+      </c>
+      <c r="O27">
+        <v>2</v>
+      </c>
+      <c r="P27" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>149</v>
+      </c>
+      <c r="AA27" t="s">
+        <v>127</v>
+      </c>
+      <c r="AB27" t="s">
+        <v>149</v>
+      </c>
+      <c r="AK27" s="16"/>
+      <c r="AT27" s="16"/>
+      <c r="BC27" s="16"/>
+      <c r="BT27" s="16"/>
+      <c r="CC27" s="16"/>
+      <c r="CL27" s="16"/>
+      <c r="CU27" s="16"/>
+      <c r="DB27" s="6">
+        <v>6</v>
+      </c>
+      <c r="DC27" s="6">
+        <v>15</v>
+      </c>
+      <c r="EH27" t="s">
+        <v>137</v>
+      </c>
+      <c r="EI27" t="s">
+        <v>212</v>
+      </c>
+      <c r="EJ27" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="28" spans="1:140" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>234</v>
+      </c>
+      <c r="B28" t="s">
+        <v>231</v>
+      </c>
+      <c r="C28" s="16">
+        <v>2023</v>
+      </c>
+      <c r="D28" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28" t="s">
+        <v>222</v>
+      </c>
+      <c r="G28" t="s">
+        <v>126</v>
+      </c>
+      <c r="H28" t="s">
+        <v>140</v>
+      </c>
+      <c r="I28" t="s">
+        <v>232</v>
+      </c>
+      <c r="K28" t="s">
+        <v>149</v>
+      </c>
+      <c r="L28">
+        <v>16</v>
+      </c>
+      <c r="M28" t="s">
+        <v>233</v>
+      </c>
+      <c r="N28">
+        <v>12</v>
+      </c>
+      <c r="O28">
+        <v>2</v>
+      </c>
+      <c r="P28" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>149</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>127</v>
+      </c>
+      <c r="AB28" t="s">
+        <v>149</v>
+      </c>
+      <c r="AK28" s="16"/>
+      <c r="AT28" s="16"/>
+      <c r="BC28" s="16"/>
+      <c r="BT28" s="16"/>
+      <c r="CC28" s="16"/>
+      <c r="CL28" s="16"/>
+      <c r="CU28" s="16"/>
+      <c r="DB28" s="6">
+        <v>1</v>
+      </c>
+      <c r="DC28" s="6">
+        <v>13</v>
+      </c>
+      <c r="EH28" t="s">
+        <v>137</v>
+      </c>
+      <c r="EI28" t="s">
+        <v>212</v>
+      </c>
+      <c r="EJ28" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="29" spans="1:140" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>160</v>
+      </c>
+      <c r="B29" t="s">
+        <v>231</v>
+      </c>
+      <c r="C29" s="16">
+        <v>2023</v>
+      </c>
+      <c r="D29" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29" t="s">
+        <v>222</v>
+      </c>
+      <c r="G29" t="s">
+        <v>160</v>
+      </c>
+      <c r="H29" t="s">
+        <v>127</v>
+      </c>
+      <c r="I29" t="s">
+        <v>232</v>
+      </c>
+      <c r="K29" t="s">
+        <v>149</v>
+      </c>
+      <c r="L29">
+        <v>16</v>
+      </c>
+      <c r="M29" t="s">
+        <v>233</v>
+      </c>
+      <c r="N29">
+        <v>12</v>
+      </c>
+      <c r="O29">
+        <v>2</v>
+      </c>
+      <c r="P29" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>149</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>127</v>
+      </c>
+      <c r="AB29" t="s">
+        <v>149</v>
+      </c>
+      <c r="AK29" s="16"/>
+      <c r="AT29" s="16"/>
+      <c r="BC29" s="16"/>
+      <c r="BT29" s="16"/>
+      <c r="CC29" s="16"/>
+      <c r="CL29" s="16"/>
+      <c r="CU29" s="16"/>
+      <c r="DB29" s="6">
+        <v>2</v>
+      </c>
+      <c r="DC29" s="6">
+        <v>14</v>
+      </c>
+      <c r="EH29" t="s">
+        <v>160</v>
+      </c>
+      <c r="EI29" t="s">
+        <v>212</v>
+      </c>
+      <c r="EJ29" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="30" spans="1:140" x14ac:dyDescent="0.2">
+      <c r="A30" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="C30" s="16">
+        <v>2024</v>
+      </c>
+      <c r="D30" s="16"/>
+      <c r="E30" s="10">
+        <v>1</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="G30" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="H30" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="I30" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="J30" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="K30" s="11">
+        <v>303</v>
+      </c>
+      <c r="L30" s="10">
+        <v>201</v>
+      </c>
+      <c r="M30" s="8">
+        <v>40.299999999999997</v>
+      </c>
+      <c r="N30" s="8">
+        <v>88</v>
+      </c>
+      <c r="O30" s="10">
+        <v>52</v>
+      </c>
+      <c r="P30" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="S30" s="8">
+        <v>43</v>
+      </c>
+      <c r="T30" s="10">
+        <v>201</v>
+      </c>
+      <c r="U30" s="10">
+        <v>96</v>
+      </c>
+      <c r="V30" s="10">
+        <v>201</v>
+      </c>
+      <c r="W30" s="8">
+        <v>48</v>
+      </c>
+      <c r="X30" s="11">
+        <v>201</v>
+      </c>
+      <c r="Y30" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="8">
+        <v>201</v>
+      </c>
+      <c r="AA30" s="8">
+        <v>16</v>
+      </c>
+      <c r="AB30" s="8">
+        <v>201</v>
+      </c>
+      <c r="AC30" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="AD30" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="AE30" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="AF30" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="AG30" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="AH30" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="AI30" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ30" s="8">
+        <v>201</v>
+      </c>
+      <c r="AK30" s="8">
+        <v>201</v>
+      </c>
+      <c r="AL30" s="8">
+        <v>65.900000000000006</v>
+      </c>
+      <c r="AM30" s="8">
+        <v>-3.8</v>
+      </c>
+      <c r="AN30" s="8">
+        <v>19.5</v>
+      </c>
+      <c r="AO30" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="AP30" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="AQ30" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="AT30" s="16"/>
+      <c r="BC30" s="16"/>
+      <c r="BT30" s="16"/>
+      <c r="CC30" s="16"/>
+      <c r="CJ30" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="CK30" s="10">
+        <v>201</v>
+      </c>
+      <c r="CL30" s="8">
+        <v>201</v>
+      </c>
+      <c r="CM30" s="8">
+        <v>80.7</v>
+      </c>
+      <c r="CN30" s="10">
+        <v>-1.2</v>
+      </c>
+      <c r="CO30" s="11">
+        <v>6.4</v>
+      </c>
+      <c r="CP30" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="CQ30" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="CR30" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="CS30" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="CT30" s="10">
+        <v>201</v>
+      </c>
+      <c r="CU30" s="16"/>
+      <c r="CW30" s="8">
+        <v>-1.7</v>
+      </c>
+      <c r="CX30" s="8">
+        <v>15.07</v>
+      </c>
+      <c r="CY30" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="CZ30" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="DA30" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="DB30" s="8">
+        <v>153</v>
+      </c>
+      <c r="DC30" s="8">
+        <v>201</v>
+      </c>
+      <c r="DD30" s="11">
+        <v>7</v>
+      </c>
+      <c r="DE30" s="11">
+        <v>201</v>
+      </c>
+      <c r="DF30" s="8">
+        <v>28</v>
+      </c>
+      <c r="DG30" s="11">
+        <v>201</v>
+      </c>
+      <c r="DH30" s="8">
+        <v>16</v>
+      </c>
+      <c r="DI30" s="8">
+        <v>201</v>
+      </c>
+      <c r="DJ30" s="8">
+        <v>20</v>
+      </c>
+      <c r="DK30" s="8">
+        <v>201</v>
+      </c>
+      <c r="DL30" s="8">
+        <v>13</v>
+      </c>
+      <c r="DM30" s="8">
+        <v>201</v>
+      </c>
+      <c r="DN30" s="11">
+        <v>12</v>
+      </c>
+      <c r="DO30" s="11">
+        <v>201</v>
+      </c>
+      <c r="DX30" s="10">
+        <v>30</v>
+      </c>
+      <c r="DY30" s="10">
+        <v>201</v>
+      </c>
+      <c r="DZ30" s="8">
+        <v>14</v>
+      </c>
+      <c r="EA30" s="8">
+        <v>201</v>
+      </c>
+      <c r="ED30" s="8">
+        <v>9</v>
+      </c>
+      <c r="EE30" s="10">
+        <v>201</v>
+      </c>
+      <c r="EF30" s="8">
+        <v>29</v>
+      </c>
+      <c r="EG30" s="8">
+        <v>201</v>
+      </c>
+      <c r="EH30" t="s">
+        <v>137</v>
+      </c>
+      <c r="EI30" t="s">
+        <v>256</v>
+      </c>
+      <c r="EJ30" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="31" spans="1:140" x14ac:dyDescent="0.2">
+      <c r="A31" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="C31" s="16">
+        <v>2024</v>
+      </c>
+      <c r="D31" s="16"/>
+      <c r="E31" s="10">
+        <v>1</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="I31" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="J31" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="K31" s="11">
+        <v>303</v>
+      </c>
+      <c r="L31" s="10">
+        <v>102</v>
+      </c>
+      <c r="M31" s="8">
+        <v>38.4</v>
+      </c>
+      <c r="N31" s="8">
+        <v>37</v>
+      </c>
+      <c r="O31" s="10">
+        <v>52</v>
+      </c>
+      <c r="P31" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="S31" s="8">
+        <v>16</v>
+      </c>
+      <c r="T31" s="10">
+        <v>102</v>
+      </c>
+      <c r="U31" s="10">
+        <v>45</v>
+      </c>
+      <c r="V31" s="10">
+        <v>102</v>
+      </c>
+      <c r="W31" s="11">
+        <v>21</v>
+      </c>
+      <c r="X31" s="11">
+        <v>102</v>
+      </c>
+      <c r="Y31" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="8">
+        <v>102</v>
+      </c>
+      <c r="AA31" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="8">
+        <v>102</v>
+      </c>
+      <c r="AC31" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="AD31" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="AE31" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="AF31" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="AG31" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="AH31" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="AI31" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ31" s="8">
+        <v>102</v>
+      </c>
+      <c r="AK31" s="8">
+        <v>102</v>
+      </c>
+      <c r="AL31" s="8">
+        <v>66.5</v>
+      </c>
+      <c r="AM31" s="8">
+        <v>-6.2</v>
+      </c>
+      <c r="AN31" s="8">
+        <v>17.52</v>
+      </c>
+      <c r="AO31" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="AP31" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="AQ31" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="AT31" s="16"/>
+      <c r="BC31" s="16"/>
+      <c r="BT31" s="16"/>
+      <c r="CC31" s="16"/>
+      <c r="CJ31" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="CK31" s="10">
+        <v>102</v>
+      </c>
+      <c r="CL31" s="8">
+        <v>102</v>
+      </c>
+      <c r="CM31" s="8">
+        <v>78.8</v>
+      </c>
+      <c r="CN31" s="10">
+        <v>1.4</v>
+      </c>
+      <c r="CO31" s="11">
+        <v>6.4</v>
+      </c>
+      <c r="CP31" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="CQ31" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="CR31" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="CS31" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="CT31" s="10">
+        <v>102</v>
+      </c>
+      <c r="CU31" s="16"/>
+      <c r="CW31" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="CX31" s="8">
+        <v>27.69</v>
+      </c>
+      <c r="CY31" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="CZ31" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="DA31" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="DB31" s="8">
+        <v>77</v>
+      </c>
+      <c r="DC31" s="8">
+        <v>102</v>
+      </c>
+      <c r="DD31" s="11">
+        <v>12</v>
+      </c>
+      <c r="DE31" s="11">
+        <v>102</v>
+      </c>
+      <c r="DF31" s="11">
+        <v>10</v>
+      </c>
+      <c r="DG31" s="11">
+        <v>102</v>
+      </c>
+      <c r="DH31" s="8">
+        <v>5</v>
+      </c>
+      <c r="DI31" s="8">
+        <v>102</v>
+      </c>
+      <c r="DJ31" s="8">
+        <v>8</v>
+      </c>
+      <c r="DK31" s="8">
+        <v>102</v>
+      </c>
+      <c r="DL31" s="8">
+        <v>4</v>
+      </c>
+      <c r="DM31" s="8">
+        <v>102</v>
+      </c>
+      <c r="DN31" s="11">
+        <v>21</v>
+      </c>
+      <c r="DO31" s="11">
+        <v>102</v>
+      </c>
+      <c r="DX31" s="10">
+        <v>11</v>
+      </c>
+      <c r="DY31" s="10">
+        <v>102</v>
+      </c>
+      <c r="DZ31" s="8">
+        <v>2</v>
+      </c>
+      <c r="EA31" s="8">
+        <v>102</v>
+      </c>
+      <c r="ED31" s="10">
+        <v>11</v>
+      </c>
+      <c r="EE31" s="10">
+        <v>102</v>
+      </c>
+      <c r="EF31" s="8">
+        <v>6</v>
+      </c>
+      <c r="EG31" s="8">
+        <v>102</v>
+      </c>
+      <c r="EH31" t="s">
+        <v>205</v>
+      </c>
+      <c r="EI31" t="s">
+        <v>256</v>
+      </c>
+      <c r="EJ31" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="32" spans="1:140" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>249</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="C32" s="16">
+        <v>2024</v>
+      </c>
+      <c r="D32" s="16"/>
+      <c r="E32">
+        <v>1</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="G32" t="s">
+        <v>194</v>
+      </c>
+      <c r="H32">
+        <v>150</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="J32" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="K32" s="9">
+        <v>27</v>
+      </c>
+      <c r="L32" s="10">
+        <v>12</v>
+      </c>
+      <c r="M32" s="10">
+        <v>43.6</v>
+      </c>
+      <c r="N32" s="10">
+        <v>3</v>
+      </c>
+      <c r="O32" s="10">
+        <v>12</v>
+      </c>
+      <c r="P32" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q32" s="11">
+        <v>0</v>
+      </c>
+      <c r="R32" s="11">
+        <v>6</v>
+      </c>
+      <c r="S32" s="11">
+        <v>0</v>
+      </c>
+      <c r="T32" s="11">
+        <v>12</v>
+      </c>
+      <c r="U32" s="11">
+        <v>5</v>
+      </c>
+      <c r="V32" s="11">
+        <v>12</v>
+      </c>
+      <c r="W32" s="11">
+        <v>1</v>
+      </c>
+      <c r="X32" s="11">
+        <v>12</v>
+      </c>
+      <c r="Y32" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="11">
+        <v>12</v>
+      </c>
+      <c r="AA32" s="11">
+        <v>1</v>
+      </c>
+      <c r="AB32" s="11">
+        <v>12</v>
+      </c>
+      <c r="AC32" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AD32" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AE32" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="AF32" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AG32" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AH32" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="AI32" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ32" s="11">
+        <v>6</v>
+      </c>
+      <c r="AK32" s="16">
+        <v>15</v>
+      </c>
+      <c r="AL32" s="11">
+        <v>67.92</v>
+      </c>
+      <c r="AM32" s="11">
+        <v>59.17</v>
+      </c>
+      <c r="AN32" s="11">
+        <v>6.27</v>
+      </c>
+      <c r="AO32" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="AP32" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AQ32" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AR32" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="AS32" s="11">
+        <v>6</v>
+      </c>
+      <c r="AT32" s="16">
+        <v>15</v>
+      </c>
+      <c r="AU32" s="11">
+        <v>19.75</v>
+      </c>
+      <c r="AV32" s="11">
+        <v>19.670000000000002</v>
+      </c>
+      <c r="AW32" s="11">
+        <v>3.61</v>
+      </c>
+      <c r="AX32" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="AY32" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AZ32" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="BA32" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="BB32" s="11">
+        <v>6</v>
+      </c>
+      <c r="BC32" s="16">
+        <v>15</v>
+      </c>
+      <c r="BD32" s="11">
+        <v>35.17</v>
+      </c>
+      <c r="BE32" s="11">
+        <v>28.17</v>
+      </c>
+      <c r="BF32" s="11">
+        <v>20.440000000000001</v>
+      </c>
+      <c r="BG32" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="BH32" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="BI32" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="BT32" s="16"/>
+      <c r="CC32" s="16"/>
+      <c r="CL32" s="16"/>
+      <c r="CU32" s="16"/>
+      <c r="DB32" s="11">
+        <v>4</v>
+      </c>
+      <c r="DC32" s="11">
+        <v>12</v>
+      </c>
+      <c r="DD32" s="11">
+        <v>1</v>
+      </c>
+      <c r="DE32" s="11">
+        <v>12</v>
+      </c>
+      <c r="DH32" s="11">
+        <v>0</v>
+      </c>
+      <c r="DI32" s="11">
+        <v>12</v>
+      </c>
+      <c r="DJ32" s="11">
+        <v>0</v>
+      </c>
+      <c r="DK32" s="11">
+        <v>12</v>
+      </c>
+      <c r="DL32" s="11">
+        <v>2</v>
+      </c>
+      <c r="DM32" s="11">
+        <v>12</v>
+      </c>
+      <c r="DN32" s="11">
+        <v>0</v>
+      </c>
+      <c r="DO32" s="11">
+        <v>12</v>
+      </c>
+      <c r="DX32" s="11">
+        <v>2</v>
+      </c>
+      <c r="DY32" s="11">
+        <v>12</v>
+      </c>
+      <c r="EF32" s="8">
+        <v>0</v>
+      </c>
+      <c r="EG32" s="8">
+        <v>12</v>
+      </c>
+      <c r="EH32" t="s">
+        <v>137</v>
+      </c>
+      <c r="EI32" t="s">
+        <v>159</v>
+      </c>
+      <c r="EJ32" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="33" spans="1:140" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>242</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="C33" s="16">
+        <v>2024</v>
+      </c>
+      <c r="D33" s="16"/>
+      <c r="E33">
+        <v>1</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="G33" t="s">
+        <v>160</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="J33" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="K33" s="9">
+        <v>27</v>
+      </c>
+      <c r="L33" s="10">
+        <v>15</v>
+      </c>
+      <c r="M33" s="10">
+        <v>42.7</v>
+      </c>
+      <c r="N33" s="10">
+        <v>3</v>
+      </c>
+      <c r="O33" s="10">
+        <v>12</v>
+      </c>
+      <c r="P33" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q33" s="11">
+        <v>1</v>
+      </c>
+      <c r="R33" s="11">
+        <v>10</v>
+      </c>
+      <c r="S33" s="11">
+        <v>1</v>
+      </c>
+      <c r="T33" s="11">
+        <v>15</v>
+      </c>
+      <c r="U33" s="11">
+        <v>5</v>
+      </c>
+      <c r="V33" s="11">
+        <v>15</v>
+      </c>
+      <c r="W33" s="11">
+        <v>2</v>
+      </c>
+      <c r="X33" s="11">
+        <v>15</v>
+      </c>
+      <c r="Y33" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="11">
+        <v>15</v>
+      </c>
+      <c r="AA33" s="11">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="11">
+        <v>15</v>
+      </c>
+      <c r="AC33" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AD33" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AE33" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="AF33" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AG33" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AH33" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="AI33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ33" s="11">
+        <v>10</v>
+      </c>
+      <c r="AK33" s="16">
+        <v>12</v>
+      </c>
+      <c r="AL33" s="11">
+        <v>67.430000000000007</v>
+      </c>
+      <c r="AM33" s="11">
+        <v>64.7</v>
+      </c>
+      <c r="AN33" s="11">
+        <v>13.92</v>
+      </c>
+      <c r="AO33" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="AP33" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AQ33" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AR33" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="AS33" s="11">
+        <v>10</v>
+      </c>
+      <c r="AT33" s="16">
+        <v>12</v>
+      </c>
+      <c r="AU33" s="11">
+        <v>17.93</v>
+      </c>
+      <c r="AV33" s="11">
+        <v>17.7</v>
+      </c>
+      <c r="AW33" s="11">
+        <v>5.25</v>
+      </c>
+      <c r="AX33" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="AY33" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AZ33" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="BA33" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="BB33" s="11">
+        <v>10</v>
+      </c>
+      <c r="BC33" s="16">
+        <v>12</v>
+      </c>
+      <c r="BD33" s="11">
+        <v>34.79</v>
+      </c>
+      <c r="BE33" s="11">
+        <v>30.4</v>
+      </c>
+      <c r="BF33" s="11">
+        <v>12.86</v>
+      </c>
+      <c r="BG33" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="BH33" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="BI33" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="BT33" s="16"/>
+      <c r="CC33" s="16"/>
+      <c r="CL33" s="16"/>
+      <c r="CU33" s="16"/>
+      <c r="DB33" s="11">
+        <v>7</v>
+      </c>
+      <c r="DC33" s="11">
+        <v>15</v>
+      </c>
+      <c r="DD33" s="11">
+        <v>0</v>
+      </c>
+      <c r="DE33" s="11">
+        <v>15</v>
+      </c>
+      <c r="DH33" s="11">
+        <v>0</v>
+      </c>
+      <c r="DI33" s="11">
+        <v>15</v>
+      </c>
+      <c r="DJ33" s="11">
+        <v>0</v>
+      </c>
+      <c r="DK33" s="11">
+        <v>15</v>
+      </c>
+      <c r="DL33" s="11">
+        <v>0</v>
+      </c>
+      <c r="DM33" s="11">
+        <v>15</v>
+      </c>
+      <c r="DN33" s="11">
+        <v>0</v>
+      </c>
+      <c r="DO33" s="11">
+        <v>15</v>
+      </c>
+      <c r="DX33" s="11">
+        <v>1</v>
+      </c>
+      <c r="DY33" s="11">
+        <v>15</v>
+      </c>
+      <c r="EF33" s="8">
+        <v>1</v>
+      </c>
+      <c r="EG33" s="8">
+        <v>15</v>
+      </c>
+      <c r="EH33" t="s">
+        <v>160</v>
+      </c>
+      <c r="EI33" t="s">
+        <v>159</v>
+      </c>
+      <c r="EJ33" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="34" spans="1:140" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>246</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="C34" s="16">
+        <v>2024</v>
+      </c>
+      <c r="D34" s="16"/>
+      <c r="E34">
+        <v>1</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="G34" t="s">
+        <v>257</v>
+      </c>
+      <c r="H34" s="9">
+        <v>45</v>
+      </c>
+      <c r="I34" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="J34" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="K34" s="9">
+        <v>104</v>
+      </c>
+      <c r="L34" s="9">
+        <v>5</v>
+      </c>
+      <c r="M34" s="9">
+        <v>41.6</v>
+      </c>
+      <c r="N34" s="9">
+        <v>0</v>
+      </c>
+      <c r="O34" s="11">
+        <v>12</v>
+      </c>
+      <c r="P34" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q34" s="11">
+        <v>0</v>
+      </c>
+      <c r="R34" s="11">
+        <v>4</v>
+      </c>
+      <c r="S34" s="11">
+        <v>0</v>
+      </c>
+      <c r="T34" s="11">
+        <v>5</v>
+      </c>
+      <c r="U34" s="11">
+        <v>0</v>
+      </c>
+      <c r="V34" s="11">
+        <v>5</v>
+      </c>
+      <c r="W34" s="11">
+        <v>0</v>
+      </c>
+      <c r="X34" s="11">
+        <v>5</v>
+      </c>
+      <c r="Y34" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="11">
+        <v>5</v>
+      </c>
+      <c r="AA34" s="11">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="11">
+        <v>5</v>
+      </c>
+      <c r="AC34" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AD34" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AE34" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="AF34" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AG34" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AH34" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="AI34" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ34" s="11">
+        <v>4</v>
+      </c>
+      <c r="AK34" s="16">
+        <v>5</v>
+      </c>
+      <c r="AL34" s="11">
+        <v>62.8</v>
+      </c>
+      <c r="AM34" s="11">
+        <v>74.8</v>
+      </c>
+      <c r="AN34" s="11">
+        <v>7.2</v>
+      </c>
+      <c r="AO34" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="AP34" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AQ34" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AR34" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="AS34" s="11">
+        <v>4</v>
+      </c>
+      <c r="AT34" s="16">
+        <v>5</v>
+      </c>
+      <c r="AU34" s="11">
+        <v>18</v>
+      </c>
+      <c r="AV34" s="11">
+        <v>21.5</v>
+      </c>
+      <c r="AW34" s="11">
+        <v>2.6</v>
+      </c>
+      <c r="AX34" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="AY34" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AZ34" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="BA34" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="BB34" s="11">
+        <v>4</v>
+      </c>
+      <c r="BC34" s="16">
+        <v>5</v>
+      </c>
+      <c r="BD34" s="11">
+        <v>36.4</v>
+      </c>
+      <c r="BE34" s="11">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="BF34" s="11">
+        <v>10.6</v>
+      </c>
+      <c r="BG34" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="BH34" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="BI34" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="BT34" s="16"/>
+      <c r="CC34" s="16"/>
+      <c r="CL34" s="16"/>
+      <c r="CU34" s="16"/>
+      <c r="DB34" s="11">
+        <v>2</v>
+      </c>
+      <c r="DC34" s="11">
+        <v>5</v>
+      </c>
+      <c r="DD34" s="11">
+        <v>0</v>
+      </c>
+      <c r="DE34" s="11">
+        <v>5</v>
+      </c>
+      <c r="DH34" s="11">
+        <v>1</v>
+      </c>
+      <c r="DI34" s="11">
+        <v>5</v>
+      </c>
+      <c r="DJ34" s="11">
+        <v>0</v>
+      </c>
+      <c r="DK34" s="11">
+        <v>5</v>
+      </c>
+      <c r="DL34" s="11">
+        <v>0</v>
+      </c>
+      <c r="DM34" s="11">
+        <v>5</v>
+      </c>
+      <c r="DN34" s="11">
+        <v>0</v>
+      </c>
+      <c r="DO34" s="11">
+        <v>5</v>
+      </c>
+      <c r="DX34" s="11">
+        <v>0</v>
+      </c>
+      <c r="DY34" s="11">
+        <v>5</v>
+      </c>
+      <c r="EF34" s="8">
+        <v>0</v>
+      </c>
+      <c r="EG34" s="8">
+        <v>5</v>
+      </c>
+      <c r="EH34" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="EI34" t="s">
+        <v>159</v>
+      </c>
+      <c r="EJ34" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="35" spans="1:140" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>247</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="C35" s="16">
+        <v>2024</v>
+      </c>
+      <c r="D35" s="16"/>
+      <c r="E35">
+        <v>1</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="G35" t="s">
+        <v>257</v>
+      </c>
+      <c r="H35" s="9">
+        <v>150</v>
+      </c>
+      <c r="I35" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="J35" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="K35" s="9">
+        <v>104</v>
+      </c>
+      <c r="L35" s="9">
+        <v>30</v>
+      </c>
+      <c r="M35" s="9">
+        <v>40</v>
+      </c>
+      <c r="N35" s="9">
+        <v>11</v>
+      </c>
+      <c r="O35" s="11">
+        <v>12</v>
+      </c>
+      <c r="P35" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q35" s="11">
+        <v>4</v>
+      </c>
+      <c r="R35" s="11">
+        <v>20</v>
+      </c>
+      <c r="S35" s="11">
+        <v>0</v>
+      </c>
+      <c r="T35" s="11">
+        <v>30</v>
+      </c>
+      <c r="U35" s="11">
+        <v>3</v>
+      </c>
+      <c r="V35" s="11">
+        <v>30</v>
+      </c>
+      <c r="W35" s="11">
+        <v>1</v>
+      </c>
+      <c r="X35" s="11">
+        <v>30</v>
+      </c>
+      <c r="Y35" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="11">
+        <v>30</v>
+      </c>
+      <c r="AA35" s="11">
+        <v>2</v>
+      </c>
+      <c r="AB35" s="11">
+        <v>30</v>
+      </c>
+      <c r="AC35" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AD35" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AE35" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="AF35" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AG35" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AH35" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="AI35" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ35" s="11">
+        <v>20</v>
+      </c>
+      <c r="AK35" s="16">
+        <v>30</v>
+      </c>
+      <c r="AL35" s="11">
+        <v>69.599999999999994</v>
+      </c>
+      <c r="AM35" s="11">
+        <v>59</v>
+      </c>
+      <c r="AN35" s="11">
+        <v>11.1</v>
+      </c>
+      <c r="AO35" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="AP35" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AQ35" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AR35" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="AS35" s="11">
+        <v>20</v>
+      </c>
+      <c r="AT35" s="16">
+        <v>30</v>
+      </c>
+      <c r="AU35" s="11">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="AV35" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="AW35" s="11">
+        <v>4.7</v>
+      </c>
+      <c r="AX35" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="AY35" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AZ35" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="BA35" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="BB35" s="11">
+        <v>19</v>
+      </c>
+      <c r="BC35" s="16">
+        <v>30</v>
+      </c>
+      <c r="BD35" s="11">
+        <v>38.1</v>
+      </c>
+      <c r="BE35" s="11">
+        <v>29.6</v>
+      </c>
+      <c r="BF35" s="11">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="BG35" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="BH35" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="BI35" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="BT35" s="16"/>
+      <c r="CC35" s="16"/>
+      <c r="CL35" s="16"/>
+      <c r="CU35" s="16"/>
+      <c r="DB35" s="11">
+        <v>8</v>
+      </c>
+      <c r="DC35" s="11">
+        <v>30</v>
+      </c>
+      <c r="DD35" s="11">
+        <v>1</v>
+      </c>
+      <c r="DE35" s="11">
+        <v>30</v>
+      </c>
+      <c r="DH35" s="11">
+        <v>2</v>
+      </c>
+      <c r="DI35" s="11">
+        <v>30</v>
+      </c>
+      <c r="DJ35" s="11">
+        <v>1</v>
+      </c>
+      <c r="DK35" s="11">
+        <v>30</v>
+      </c>
+      <c r="DL35" s="11">
+        <v>1</v>
+      </c>
+      <c r="DM35" s="11">
+        <v>30</v>
+      </c>
+      <c r="DN35" s="11">
+        <v>2</v>
+      </c>
+      <c r="DO35" s="11">
+        <v>30</v>
+      </c>
+      <c r="DX35" s="11">
+        <v>0</v>
+      </c>
+      <c r="DY35" s="11">
+        <v>30</v>
+      </c>
+      <c r="EF35" s="8">
+        <v>0</v>
+      </c>
+      <c r="EG35" s="8">
+        <v>30</v>
+      </c>
+      <c r="EH35" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="EI35" t="s">
+        <v>159</v>
+      </c>
+      <c r="EJ35" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="36" spans="1:140" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>248</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="C36" s="16">
+        <v>2024</v>
+      </c>
+      <c r="D36" s="16"/>
+      <c r="E36">
+        <v>1</v>
+      </c>
+      <c r="F36" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="G36" t="s">
+        <v>257</v>
+      </c>
+      <c r="H36" s="9">
+        <v>300</v>
+      </c>
+      <c r="I36" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="J36" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="K36" s="9">
+        <v>104</v>
+      </c>
+      <c r="L36" s="9">
+        <v>32</v>
+      </c>
+      <c r="M36" s="9">
+        <v>40.9</v>
+      </c>
+      <c r="N36" s="9">
+        <v>12</v>
+      </c>
+      <c r="O36" s="11">
+        <v>12</v>
+      </c>
+      <c r="P36" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q36" s="11">
+        <v>3</v>
+      </c>
+      <c r="R36" s="11">
+        <v>21</v>
+      </c>
+      <c r="S36" s="11">
+        <v>0</v>
+      </c>
+      <c r="T36" s="11">
+        <v>32</v>
+      </c>
+      <c r="U36" s="11">
+        <v>3</v>
+      </c>
+      <c r="V36" s="11">
+        <v>32</v>
+      </c>
+      <c r="W36" s="11">
+        <v>0</v>
+      </c>
+      <c r="X36" s="11">
+        <v>32</v>
+      </c>
+      <c r="Y36" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="11">
+        <v>32</v>
+      </c>
+      <c r="AA36" s="11">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="11">
+        <v>32</v>
+      </c>
+      <c r="AC36" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AD36" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AE36" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="AF36" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AG36" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AH36" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="AI36" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ36" s="11">
+        <v>21</v>
+      </c>
+      <c r="AK36" s="16">
+        <v>32</v>
+      </c>
+      <c r="AL36" s="11">
+        <v>67.8</v>
+      </c>
+      <c r="AM36" s="11">
+        <v>60.9</v>
+      </c>
+      <c r="AN36" s="11">
+        <v>11.3</v>
+      </c>
+      <c r="AO36" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="AP36" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AQ36" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AR36" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="AS36" s="11">
+        <v>21</v>
+      </c>
+      <c r="AT36" s="16">
+        <v>32</v>
+      </c>
+      <c r="AU36" s="11">
+        <v>17.2</v>
+      </c>
+      <c r="AV36" s="11">
+        <v>15.5</v>
+      </c>
+      <c r="AW36" s="11">
+        <v>4.3</v>
+      </c>
+      <c r="AX36" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="AY36" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AZ36" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="BA36" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="BB36" s="11">
+        <v>21</v>
+      </c>
+      <c r="BC36" s="16">
+        <v>32</v>
+      </c>
+      <c r="BD36" s="11">
+        <v>38.4</v>
+      </c>
+      <c r="BE36" s="11">
+        <v>29.2</v>
+      </c>
+      <c r="BF36" s="11">
+        <v>12.4</v>
+      </c>
+      <c r="BG36" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="BH36" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="BI36" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="BT36" s="16"/>
+      <c r="CC36" s="16"/>
+      <c r="CL36" s="16"/>
+      <c r="CU36" s="16"/>
+      <c r="DB36" s="11">
+        <v>4</v>
+      </c>
+      <c r="DC36" s="11">
+        <v>32</v>
+      </c>
+      <c r="DD36" s="11">
+        <v>0</v>
+      </c>
+      <c r="DE36" s="11">
+        <v>32</v>
+      </c>
+      <c r="DH36" s="11">
+        <v>1</v>
+      </c>
+      <c r="DI36" s="11">
+        <v>32</v>
+      </c>
+      <c r="DJ36" s="11">
+        <v>0</v>
+      </c>
+      <c r="DK36" s="11">
+        <v>32</v>
+      </c>
+      <c r="DL36" s="11">
+        <v>1</v>
+      </c>
+      <c r="DM36" s="11">
+        <v>32</v>
+      </c>
+      <c r="DN36" s="11">
+        <v>0</v>
+      </c>
+      <c r="DO36" s="11">
+        <v>32</v>
+      </c>
+      <c r="DX36" s="11">
+        <v>0</v>
+      </c>
+      <c r="DY36" s="11">
+        <v>32</v>
+      </c>
+      <c r="EF36" s="8">
+        <v>0</v>
+      </c>
+      <c r="EG36" s="8">
+        <v>32</v>
+      </c>
+      <c r="EH36" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="EI36" t="s">
+        <v>159</v>
+      </c>
+      <c r="EJ36" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="37" spans="1:140" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>244</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="C37" s="16">
+        <v>2024</v>
+      </c>
+      <c r="D37" s="16"/>
+      <c r="E37">
+        <v>1</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="G37" t="s">
+        <v>258</v>
+      </c>
+      <c r="H37" s="9">
+        <v>0</v>
+      </c>
+      <c r="I37" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="J37" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="K37" s="9">
+        <v>104</v>
+      </c>
+      <c r="L37" s="9">
+        <v>37</v>
+      </c>
+      <c r="M37" s="9">
+        <v>41.3</v>
+      </c>
+      <c r="N37" s="9">
+        <v>10</v>
+      </c>
+      <c r="O37" s="11">
+        <v>12</v>
+      </c>
+      <c r="P37" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q37" s="11">
+        <v>4</v>
+      </c>
+      <c r="R37" s="11">
+        <v>31</v>
+      </c>
+      <c r="S37" s="11">
+        <v>0</v>
+      </c>
+      <c r="T37" s="11">
+        <v>37</v>
+      </c>
+      <c r="U37" s="11">
+        <v>4</v>
+      </c>
+      <c r="V37" s="11">
+        <v>37</v>
+      </c>
+      <c r="W37" s="11">
+        <v>0</v>
+      </c>
+      <c r="X37" s="11">
+        <v>37</v>
+      </c>
+      <c r="Y37" s="11">
+        <v>1</v>
+      </c>
+      <c r="Z37" s="11">
+        <v>37</v>
+      </c>
+      <c r="AA37" s="11">
+        <v>1</v>
+      </c>
+      <c r="AB37" s="11">
+        <v>37</v>
+      </c>
+      <c r="AC37" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AD37" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AE37" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="AF37" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AG37" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AH37" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="AI37" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ37" s="11">
+        <v>31</v>
+      </c>
+      <c r="AK37" s="16">
+        <v>37</v>
+      </c>
+      <c r="AL37" s="11">
+        <v>71.400000000000006</v>
+      </c>
+      <c r="AM37" s="11">
+        <v>64.400000000000006</v>
+      </c>
+      <c r="AN37" s="11">
+        <v>12.2</v>
+      </c>
+      <c r="AO37" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="AP37" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AQ37" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AR37" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="AS37" s="11">
+        <v>31</v>
+      </c>
+      <c r="AT37" s="16">
+        <v>37</v>
+      </c>
+      <c r="AU37" s="11">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="AV37" s="11">
+        <v>17.3</v>
+      </c>
+      <c r="AW37" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="AX37" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="AY37" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AZ37" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="BA37" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="BB37" s="11">
+        <v>31</v>
+      </c>
+      <c r="BC37" s="16">
+        <v>37</v>
+      </c>
+      <c r="BD37" s="11">
+        <v>36.6</v>
+      </c>
+      <c r="BE37" s="11">
+        <v>32.700000000000003</v>
+      </c>
+      <c r="BF37" s="11">
+        <v>13.4</v>
+      </c>
+      <c r="BG37" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="BH37" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="BI37" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="BT37" s="16"/>
+      <c r="CC37" s="16"/>
+      <c r="CL37" s="16"/>
+      <c r="CU37" s="16"/>
+      <c r="DB37" s="11">
+        <v>9</v>
+      </c>
+      <c r="DC37" s="11">
+        <v>37</v>
+      </c>
+      <c r="DD37" s="11">
+        <v>0</v>
+      </c>
+      <c r="DE37" s="11">
+        <v>37</v>
+      </c>
+      <c r="DH37" s="11">
+        <v>1</v>
+      </c>
+      <c r="DI37" s="11">
+        <v>37</v>
+      </c>
+      <c r="DJ37" s="11">
+        <v>3</v>
+      </c>
+      <c r="DK37" s="11">
+        <v>37</v>
+      </c>
+      <c r="DL37" s="11">
+        <v>2</v>
+      </c>
+      <c r="DM37" s="11">
+        <v>37</v>
+      </c>
+      <c r="DN37" s="11">
+        <v>2</v>
+      </c>
+      <c r="DO37" s="11">
+        <v>37</v>
+      </c>
+      <c r="DX37" s="11">
+        <v>0</v>
+      </c>
+      <c r="DY37" s="11">
+        <v>37</v>
+      </c>
+      <c r="EF37" s="8">
+        <v>0</v>
+      </c>
+      <c r="EG37" s="8">
+        <v>37</v>
+      </c>
+      <c r="EH37" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="EI37" t="s">
+        <v>159</v>
+      </c>
+      <c r="EJ37" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="38" spans="1:140" x14ac:dyDescent="0.2">
+      <c r="A38" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="C38" s="16">
+        <v>2024</v>
+      </c>
+      <c r="D38" s="17" t="s">
+        <v>270</v>
+      </c>
+      <c r="E38" s="10">
+        <v>1</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="G38" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="H38" s="9">
+        <v>150</v>
+      </c>
+      <c r="I38" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="J38" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="K38" s="11">
+        <v>31</v>
+      </c>
+      <c r="L38" s="11">
+        <v>31</v>
+      </c>
+      <c r="M38" s="11">
+        <v>46.2</v>
+      </c>
+      <c r="N38" s="11">
+        <v>6</v>
+      </c>
+      <c r="O38" s="11">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="P38" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="Y38" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="11">
+        <v>29</v>
+      </c>
+      <c r="AA38" s="11">
+        <v>0</v>
+      </c>
+      <c r="AB38" s="11">
+        <v>29</v>
+      </c>
+      <c r="AK38" s="16"/>
+      <c r="AT38" s="16"/>
+      <c r="BC38" s="16"/>
+      <c r="BT38" s="16"/>
+      <c r="CC38" s="16"/>
+      <c r="CL38" s="16"/>
+      <c r="CU38" s="16"/>
+      <c r="DB38" s="10">
+        <v>20</v>
+      </c>
+      <c r="DC38" s="10">
+        <v>29</v>
+      </c>
+      <c r="DH38" s="10">
+        <v>4</v>
+      </c>
+      <c r="DI38" s="10">
+        <v>29</v>
+      </c>
+      <c r="DL38" s="10">
+        <v>8</v>
+      </c>
+      <c r="DM38" s="10">
+        <v>29</v>
+      </c>
+      <c r="DN38" s="10">
+        <v>4</v>
+      </c>
+      <c r="DO38" s="10">
+        <v>29</v>
+      </c>
+      <c r="DR38" s="11">
+        <v>0</v>
+      </c>
+      <c r="DS38" s="11">
+        <v>29</v>
+      </c>
+      <c r="EH38" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="EI38" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="EJ38" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="39" spans="1:140" x14ac:dyDescent="0.2">
+      <c r="A39" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="C39" s="16">
+        <v>2024</v>
+      </c>
+      <c r="D39" s="17" t="s">
+        <v>270</v>
+      </c>
+      <c r="E39" s="10">
+        <v>1</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="I39" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="J39" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="K39" s="11">
+        <v>31</v>
+      </c>
+      <c r="L39" s="11">
+        <v>31</v>
+      </c>
+      <c r="M39" s="11">
+        <v>46.2</v>
+      </c>
+      <c r="N39" s="11">
+        <v>6</v>
+      </c>
+      <c r="O39" s="11">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="P39" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="Y39" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z39" s="11">
+        <v>26</v>
+      </c>
+      <c r="AA39" s="11">
+        <v>0</v>
+      </c>
+      <c r="AB39" s="11">
+        <v>26</v>
+      </c>
+      <c r="AK39" s="16"/>
+      <c r="AT39" s="16"/>
+      <c r="BC39" s="16"/>
+      <c r="BT39" s="16"/>
+      <c r="CC39" s="16"/>
+      <c r="CL39" s="16"/>
+      <c r="CU39" s="16"/>
+      <c r="DB39" s="10">
+        <v>9</v>
+      </c>
+      <c r="DC39" s="10">
+        <v>26</v>
+      </c>
+      <c r="DH39" s="10">
+        <v>0</v>
+      </c>
+      <c r="DI39" s="10">
+        <v>26</v>
+      </c>
+      <c r="DL39" s="10">
+        <v>0</v>
+      </c>
+      <c r="DM39" s="10">
+        <v>26</v>
+      </c>
+      <c r="DN39" s="10">
+        <v>1</v>
+      </c>
+      <c r="DO39" s="10">
+        <v>26</v>
+      </c>
+      <c r="DR39" s="11">
+        <v>0</v>
+      </c>
+      <c r="DS39" s="11">
+        <v>26</v>
+      </c>
+      <c r="EH39" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="EI39" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="EJ39" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D29" r:id="rId1" xr:uid="{5912F96A-B9A5-B04E-AAD6-F0A1D16FF045}"/>
+    <hyperlink ref="D28" r:id="rId2" xr:uid="{F9E74F82-F072-CC40-BD54-B870E05A2432}"/>
+    <hyperlink ref="D27" r:id="rId3" xr:uid="{E7CDAF16-4559-734F-B452-05329445FF36}"/>
+    <hyperlink ref="D4" r:id="rId4" xr:uid="{A51250A9-B803-D446-A614-BD28FEA3E433}"/>
+    <hyperlink ref="D5" r:id="rId5" xr:uid="{93FAFF45-11C9-544A-A46F-9336DDFC7CC3}"/>
+    <hyperlink ref="D19" r:id="rId6" xr:uid="{D247E65C-0A58-284E-9EFE-2BD23FF64AFE}"/>
+    <hyperlink ref="D22" r:id="rId7" xr:uid="{C7DCC5D2-EE2A-754A-83E7-16541ACB5603}"/>
+    <hyperlink ref="D23" r:id="rId8" xr:uid="{21B40A9E-ADED-434B-823B-6E13633AECBC}"/>
+    <hyperlink ref="D38" r:id="rId9" xr:uid="{AEFD8585-9E80-344D-87D8-B0634290DC36}"/>
+    <hyperlink ref="D39" r:id="rId10" xr:uid="{F633023D-4808-9740-992A-E503DFAD176D}"/>
+    <hyperlink ref="D24" r:id="rId11" xr:uid="{26004FD2-DEFE-634E-8E8D-0FAAAB8C6EBD}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId12"/>
+</worksheet>
 </file>